--- a/research/traditional_assets/database/data/slovakia/slovakia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/slovakia/slovakia_hotel_gaming.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0505</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G2">
-        <v>0.4162011173184358</v>
+        <v>-0.1102106969205835</v>
       </c>
       <c r="H2">
-        <v>0.4162011173184358</v>
+        <v>-0.1102106969205835</v>
       </c>
       <c r="I2">
-        <v>-0.5027932960893855</v>
+        <v>-0.0479740680713128</v>
       </c>
       <c r="J2">
-        <v>-0.5027932960893855</v>
+        <v>-0.0479740680713128</v>
       </c>
       <c r="K2">
-        <v>-75.5</v>
+        <v>-4.39</v>
       </c>
       <c r="L2">
-        <v>-1.054469273743017</v>
+        <v>-0.03557536466774716</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.81</v>
+        <v>14.1</v>
       </c>
       <c r="V2">
-        <v>0.03350493350493351</v>
+        <v>0.09173715029277814</v>
       </c>
       <c r="W2">
-        <v>-0.578544061302682</v>
+        <v>-0.06465390279823269</v>
       </c>
       <c r="X2">
-        <v>0.1404549516328256</v>
+        <v>0.2274413341163178</v>
       </c>
       <c r="Y2">
-        <v>-0.7189990129355076</v>
+        <v>-0.2920952369145504</v>
       </c>
       <c r="Z2">
-        <v>0.1323597374988446</v>
+        <v>0.2168755162656637</v>
       </c>
       <c r="AA2">
-        <v>-0.06654958868656993</v>
+        <v>-0.01040440078033006</v>
       </c>
       <c r="AB2">
-        <v>0.06068300832772734</v>
+        <v>0.09039308135249588</v>
       </c>
       <c r="AC2">
-        <v>-0.1272325970142973</v>
+        <v>-0.1007974821328259</v>
       </c>
       <c r="AD2">
-        <v>508.9</v>
+        <v>469.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>508.9</v>
+        <v>469.7</v>
       </c>
       <c r="AG2">
-        <v>501.09</v>
+        <v>455.6</v>
       </c>
       <c r="AH2">
-        <v>0.6858490566037736</v>
+        <v>0.7534488290022457</v>
       </c>
       <c r="AI2">
-        <v>0.8832002776813607</v>
+        <v>0.9003258577726662</v>
       </c>
       <c r="AJ2">
-        <v>0.6825072528909411</v>
+        <v>0.747743311997374</v>
       </c>
       <c r="AK2">
-        <v>0.8815953834515033</v>
+        <v>0.8975571315996848</v>
       </c>
       <c r="AL2">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="AM2">
-        <v>24.279</v>
+        <v>23.986</v>
       </c>
       <c r="AN2">
-        <v>-49.40776699029126</v>
+        <v>28.64024390243902</v>
       </c>
       <c r="AO2">
-        <v>-1.463414634146341</v>
+        <v>-0.2456431535269709</v>
       </c>
       <c r="AP2">
-        <v>-48.64951456310679</v>
+        <v>27.78048780487805</v>
       </c>
       <c r="AQ2">
-        <v>-1.482762881502533</v>
+        <v>-0.2468106395397315</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0505</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G3">
-        <v>0.4162011173184358</v>
+        <v>-0.1102106969205835</v>
       </c>
       <c r="H3">
-        <v>0.4162011173184358</v>
+        <v>-0.1102106969205835</v>
       </c>
       <c r="I3">
-        <v>-0.5027932960893855</v>
+        <v>-0.0479740680713128</v>
       </c>
       <c r="J3">
-        <v>-0.5027932960893855</v>
+        <v>-0.0479740680713128</v>
       </c>
       <c r="K3">
-        <v>-75.5</v>
+        <v>-4.39</v>
       </c>
       <c r="L3">
-        <v>-1.054469273743017</v>
+        <v>-0.03557536466774716</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.81</v>
+        <v>14.1</v>
       </c>
       <c r="V3">
-        <v>0.03350493350493351</v>
+        <v>0.09173715029277814</v>
       </c>
       <c r="W3">
-        <v>-0.578544061302682</v>
+        <v>-0.06465390279823269</v>
       </c>
       <c r="X3">
-        <v>0.1404549516328256</v>
+        <v>0.2274413341163178</v>
       </c>
       <c r="Y3">
-        <v>-0.7189990129355076</v>
+        <v>-0.2920952369145504</v>
       </c>
       <c r="Z3">
-        <v>0.1323597374988446</v>
+        <v>0.2168755162656637</v>
       </c>
       <c r="AA3">
-        <v>-0.06654958868656993</v>
+        <v>-0.01040440078033006</v>
       </c>
       <c r="AB3">
-        <v>0.06068300832772734</v>
+        <v>0.09039308135249588</v>
       </c>
       <c r="AC3">
-        <v>-0.1272325970142973</v>
+        <v>-0.1007974821328259</v>
       </c>
       <c r="AD3">
-        <v>508.9</v>
+        <v>469.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>508.9</v>
+        <v>469.7</v>
       </c>
       <c r="AG3">
-        <v>501.09</v>
+        <v>455.6</v>
       </c>
       <c r="AH3">
-        <v>0.6858490566037736</v>
+        <v>0.7534488290022457</v>
       </c>
       <c r="AI3">
-        <v>0.8832002776813607</v>
+        <v>0.9003258577726662</v>
       </c>
       <c r="AJ3">
-        <v>0.6825072528909411</v>
+        <v>0.747743311997374</v>
       </c>
       <c r="AK3">
-        <v>0.8815953834515033</v>
+        <v>0.8975571315996848</v>
       </c>
       <c r="AL3">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="AM3">
-        <v>24.279</v>
+        <v>23.986</v>
       </c>
       <c r="AN3">
-        <v>-49.40776699029126</v>
+        <v>28.64024390243902</v>
       </c>
       <c r="AO3">
-        <v>-1.463414634146341</v>
+        <v>-0.2456431535269709</v>
       </c>
       <c r="AP3">
-        <v>-48.64951456310679</v>
+        <v>27.78048780487805</v>
       </c>
       <c r="AQ3">
-        <v>-1.482762881502533</v>
+        <v>-0.2468106395397315</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/slovakia/slovakia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/slovakia/slovakia_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bsse_1tmr001e" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06610000000000001</v>
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-0.405</v>
       </c>
       <c r="G2">
-        <v>-0.1102106969205835</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="H2">
-        <v>-0.1102106969205835</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="I2">
-        <v>-0.0479740680713128</v>
+        <v>0.11875</v>
       </c>
       <c r="J2">
-        <v>-0.0479740680713128</v>
+        <v>0.11875</v>
       </c>
       <c r="K2">
-        <v>-4.39</v>
+        <v>0.673</v>
       </c>
       <c r="L2">
-        <v>-0.03557536466774716</v>
+        <v>0.003505208333333334</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.1</v>
+        <v>18.1</v>
       </c>
       <c r="V2">
-        <v>0.09173715029277814</v>
+        <v>0.09741657696447793</v>
       </c>
       <c r="W2">
-        <v>-0.06465390279823269</v>
+        <v>0.01272211720226843</v>
       </c>
       <c r="X2">
-        <v>0.2274413341163178</v>
+        <v>0.1738189549132663</v>
       </c>
       <c r="Y2">
-        <v>-0.2920952369145504</v>
+        <v>-0.1610968377109978</v>
       </c>
       <c r="Z2">
-        <v>0.2168755162656637</v>
+        <v>0.3775811209439528</v>
       </c>
       <c r="AA2">
-        <v>-0.01040440078033006</v>
+        <v>0.04483775811209439</v>
       </c>
       <c r="AB2">
-        <v>0.09039308135249588</v>
+        <v>0.08209679592531528</v>
       </c>
       <c r="AC2">
-        <v>-0.1007974821328259</v>
+        <v>-0.03725903781322089</v>
       </c>
       <c r="AD2">
-        <v>469.7</v>
+        <v>492</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>469.7</v>
+        <v>492</v>
       </c>
       <c r="AG2">
-        <v>455.6</v>
+        <v>473.9</v>
       </c>
       <c r="AH2">
-        <v>0.7534488290022457</v>
+        <v>0.7258778400708173</v>
       </c>
       <c r="AI2">
-        <v>0.9003258577726662</v>
+        <v>0.894708128750682</v>
       </c>
       <c r="AJ2">
-        <v>0.747743311997374</v>
+        <v>0.7183568288616037</v>
       </c>
       <c r="AK2">
-        <v>0.8975571315996848</v>
+        <v>0.8911244828883039</v>
       </c>
       <c r="AL2">
-        <v>24.1</v>
+        <v>27.8</v>
       </c>
       <c r="AM2">
-        <v>23.986</v>
+        <v>27.743</v>
       </c>
       <c r="AN2">
-        <v>28.64024390243902</v>
+        <v>9.859719438877756</v>
       </c>
       <c r="AO2">
-        <v>-0.2456431535269709</v>
+        <v>0.8201438848920863</v>
       </c>
       <c r="AP2">
-        <v>27.78048780487805</v>
+        <v>9.496993987975952</v>
       </c>
       <c r="AQ2">
-        <v>-0.2468106395397315</v>
+        <v>0.8218289298201348</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06610000000000001</v>
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="E3">
+        <v>-0.405</v>
       </c>
       <c r="G3">
-        <v>-0.1102106969205835</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="H3">
-        <v>-0.1102106969205835</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="I3">
-        <v>-0.0479740680713128</v>
+        <v>0.11875</v>
       </c>
       <c r="J3">
-        <v>-0.0479740680713128</v>
+        <v>0.11875</v>
       </c>
       <c r="K3">
-        <v>-4.39</v>
+        <v>0.673</v>
       </c>
       <c r="L3">
-        <v>-0.03557536466774716</v>
+        <v>0.003505208333333334</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.1</v>
+        <v>18.1</v>
       </c>
       <c r="V3">
-        <v>0.09173715029277814</v>
+        <v>0.09741657696447793</v>
       </c>
       <c r="W3">
-        <v>-0.06465390279823269</v>
+        <v>0.01272211720226843</v>
       </c>
       <c r="X3">
-        <v>0.2274413341163178</v>
+        <v>0.1738189549132663</v>
       </c>
       <c r="Y3">
-        <v>-0.2920952369145504</v>
+        <v>-0.1610968377109978</v>
       </c>
       <c r="Z3">
-        <v>0.2168755162656637</v>
+        <v>0.3775811209439528</v>
       </c>
       <c r="AA3">
-        <v>-0.01040440078033006</v>
+        <v>0.04483775811209439</v>
       </c>
       <c r="AB3">
-        <v>0.09039308135249588</v>
+        <v>0.08209679592531528</v>
       </c>
       <c r="AC3">
-        <v>-0.1007974821328259</v>
+        <v>-0.03725903781322089</v>
       </c>
       <c r="AD3">
-        <v>469.7</v>
+        <v>492</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>469.7</v>
+        <v>492</v>
       </c>
       <c r="AG3">
-        <v>455.6</v>
+        <v>473.9</v>
       </c>
       <c r="AH3">
-        <v>0.7534488290022457</v>
+        <v>0.7258778400708173</v>
       </c>
       <c r="AI3">
-        <v>0.9003258577726662</v>
+        <v>0.894708128750682</v>
       </c>
       <c r="AJ3">
-        <v>0.747743311997374</v>
+        <v>0.7183568288616037</v>
       </c>
       <c r="AK3">
-        <v>0.8975571315996848</v>
+        <v>0.8911244828883039</v>
       </c>
       <c r="AL3">
-        <v>24.1</v>
+        <v>27.8</v>
       </c>
       <c r="AM3">
-        <v>23.986</v>
+        <v>27.743</v>
       </c>
       <c r="AN3">
-        <v>28.64024390243902</v>
+        <v>9.859719438877756</v>
       </c>
       <c r="AO3">
-        <v>-0.2456431535269709</v>
+        <v>0.8201438848920863</v>
       </c>
       <c r="AP3">
-        <v>27.78048780487805</v>
+        <v>9.496993987975952</v>
       </c>
       <c r="AQ3">
-        <v>-0.2468106395397315</v>
+        <v>0.8218289298201348</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tatry mountain resorts, a.s. (BSSE:1TMR001E)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BSSE:1TMR001E</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.564748201438849</v>
+      </c>
+      <c r="F2">
+        <v>4.57846080226365</v>
+      </c>
+      <c r="G2">
+        <v>9.85971943887775</v>
+      </c>
+      <c r="H2">
+        <v>4.21078156312625</v>
+      </c>
+      <c r="I2">
+        <v>0.725877840070817</v>
+      </c>
+      <c r="J2">
+        <v>0.31</v>
+      </c>
+      <c r="K2">
+        <v>185.8</v>
+      </c>
+      <c r="L2">
+        <v>500.200490526266</v>
+      </c>
+      <c r="M2">
+        <v>659.7</v>
+      </c>
+      <c r="N2">
+        <v>692.218490526266</v>
+      </c>
+      <c r="O2">
+        <v>492</v>
+      </c>
+      <c r="P2">
+        <v>210.118</v>
+      </c>
+      <c r="Q2">
+        <v>0.0820967959253153</v>
+      </c>
+      <c r="R2">
+        <v>0.0800628334302588</v>
+      </c>
+      <c r="S2">
+        <v>0.0474586310066948</v>
+      </c>
+      <c r="T2">
+        <v>0.040211</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.173818954913266</v>
+      </c>
+      <c r="X2">
+        <v>0.0979672803337084</v>
+      </c>
+      <c r="Y2">
+        <v>2.31290936642324</v>
+      </c>
+      <c r="Z2">
+        <v>1.01355070447355</v>
+      </c>
+      <c r="AA2">
+        <v>491.9999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.06007421646417059</v>
+      </c>
+      <c r="AC2">
+        <v>0.5647482014388487</v>
+      </c>
+      <c r="AD2">
+        <v>491.9999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>27.8</v>
+      </c>
+      <c r="AF2">
+        <v>34.2</v>
+      </c>
+      <c r="AG2">
+        <v>49.9</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>185.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.0583762411417202</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.21</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>26.55</v>
+      </c>
+      <c r="AR2">
+        <v>27.8</v>
+      </c>
+      <c r="AS2">
+        <v>492</v>
+      </c>
+      <c r="AT2">
+        <v>18.1</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08246822486924676</v>
+      </c>
+      <c r="C2">
+        <v>672.1887878418396</v>
+      </c>
+      <c r="D2">
+        <v>654.0887878418396</v>
+      </c>
+      <c r="E2">
+        <v>-491.9999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>18.1</v>
+      </c>
+      <c r="H2">
+        <v>185.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K2">
+        <v>34.2</v>
+      </c>
+      <c r="L2">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="O2">
+        <v>10.283</v>
+      </c>
+      <c r="P2">
+        <v>38.68366666666667</v>
+      </c>
+      <c r="Q2">
+        <v>72.88366666666667</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08246822486924676</v>
+      </c>
+      <c r="T2">
+        <v>0.7480479046815169</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.21</v>
+      </c>
+      <c r="W2">
+        <v>0.035313</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08234165159702132</v>
+      </c>
+      <c r="C3">
+        <v>667.3121892624687</v>
+      </c>
+      <c r="D3">
+        <v>655.9901892624687</v>
+      </c>
+      <c r="E3">
+        <v>-485.2219999999999</v>
+      </c>
+      <c r="F3">
+        <v>6.778</v>
+      </c>
+      <c r="G3">
+        <v>18.1</v>
+      </c>
+      <c r="H3">
+        <v>185.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K3">
+        <v>34.2</v>
+      </c>
+      <c r="L3">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M3">
+        <v>0.3029766</v>
+      </c>
+      <c r="N3">
+        <v>48.66369006666667</v>
+      </c>
+      <c r="O3">
+        <v>10.219374914</v>
+      </c>
+      <c r="P3">
+        <v>38.44431515266667</v>
+      </c>
+      <c r="Q3">
+        <v>72.64431515266668</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08281668848183973</v>
+      </c>
+      <c r="T3">
+        <v>0.7540171758400867</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.21</v>
+      </c>
+      <c r="W3">
+        <v>0.035313</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>161.6186420557451</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08221507832479594</v>
+      </c>
+      <c r="C4">
+        <v>662.4466774579645</v>
+      </c>
+      <c r="D4">
+        <v>657.9026774579645</v>
+      </c>
+      <c r="E4">
+        <v>-478.444</v>
+      </c>
+      <c r="F4">
+        <v>13.556</v>
+      </c>
+      <c r="G4">
+        <v>18.1</v>
+      </c>
+      <c r="H4">
+        <v>185.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K4">
+        <v>34.2</v>
+      </c>
+      <c r="L4">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M4">
+        <v>0.6059532</v>
+      </c>
+      <c r="N4">
+        <v>48.36071346666667</v>
+      </c>
+      <c r="O4">
+        <v>10.155749828</v>
+      </c>
+      <c r="P4">
+        <v>38.20496363866667</v>
+      </c>
+      <c r="Q4">
+        <v>72.40496363866667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08317226359673055</v>
+      </c>
+      <c r="T4">
+        <v>0.7601082688590354</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.21</v>
+      </c>
+      <c r="W4">
+        <v>0.035313</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>80.80932102787257</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.0820885050525705</v>
+      </c>
+      <c r="C5">
+        <v>657.5923496797383</v>
+      </c>
+      <c r="D5">
+        <v>659.8263496797382</v>
+      </c>
+      <c r="E5">
+        <v>-471.6659999999999</v>
+      </c>
+      <c r="F5">
+        <v>20.334</v>
+      </c>
+      <c r="G5">
+        <v>18.1</v>
+      </c>
+      <c r="H5">
+        <v>185.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K5">
+        <v>34.2</v>
+      </c>
+      <c r="L5">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M5">
+        <v>0.9089298</v>
+      </c>
+      <c r="N5">
+        <v>48.05773686666667</v>
+      </c>
+      <c r="O5">
+        <v>10.092124742</v>
+      </c>
+      <c r="P5">
+        <v>37.96561212466666</v>
+      </c>
+      <c r="Q5">
+        <v>72.16561212466667</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08353517015728917</v>
+      </c>
+      <c r="T5">
+        <v>0.7663249514247663</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.21</v>
+      </c>
+      <c r="W5">
+        <v>0.035313</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>53.87288068524837</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08196193178034508</v>
+      </c>
+      <c r="C6">
+        <v>652.7493043199646</v>
+      </c>
+      <c r="D6">
+        <v>661.7613043199646</v>
+      </c>
+      <c r="E6">
+        <v>-464.8879999999999</v>
+      </c>
+      <c r="F6">
+        <v>27.112</v>
+      </c>
+      <c r="G6">
+        <v>18.1</v>
+      </c>
+      <c r="H6">
+        <v>185.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K6">
+        <v>34.2</v>
+      </c>
+      <c r="L6">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M6">
+        <v>1.2119064</v>
+      </c>
+      <c r="N6">
+        <v>47.75476026666667</v>
+      </c>
+      <c r="O6">
+        <v>10.028499656</v>
+      </c>
+      <c r="P6">
+        <v>37.72626061066667</v>
+      </c>
+      <c r="Q6">
+        <v>71.92626061066667</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0839056372711928</v>
+      </c>
+      <c r="T6">
+        <v>0.7726711482106169</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.21</v>
+      </c>
+      <c r="W6">
+        <v>0.035313</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>40.40466051393629</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08183535850811967</v>
+      </c>
+      <c r="C7">
+        <v>647.9176409283637</v>
+      </c>
+      <c r="D7">
+        <v>663.7076409283636</v>
+      </c>
+      <c r="E7">
+        <v>-458.11</v>
+      </c>
+      <c r="F7">
+        <v>33.89</v>
+      </c>
+      <c r="G7">
+        <v>18.1</v>
+      </c>
+      <c r="H7">
+        <v>185.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K7">
+        <v>34.2</v>
+      </c>
+      <c r="L7">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M7">
+        <v>1.514883</v>
+      </c>
+      <c r="N7">
+        <v>47.45178366666667</v>
+      </c>
+      <c r="O7">
+        <v>9.964874570000001</v>
+      </c>
+      <c r="P7">
+        <v>37.48690909666667</v>
+      </c>
+      <c r="Q7">
+        <v>71.68690909666668</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08428390369275755</v>
+      </c>
+      <c r="T7">
+        <v>0.7791509491393275</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.21</v>
+      </c>
+      <c r="W7">
+        <v>0.035313</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>32.32372841114902</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08170878523589425</v>
+      </c>
+      <c r="C8">
+        <v>643.0974602292707</v>
+      </c>
+      <c r="D8">
+        <v>665.6654602292707</v>
+      </c>
+      <c r="E8">
+        <v>-451.3319999999999</v>
+      </c>
+      <c r="F8">
+        <v>40.668</v>
+      </c>
+      <c r="G8">
+        <v>18.1</v>
+      </c>
+      <c r="H8">
+        <v>185.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K8">
+        <v>34.2</v>
+      </c>
+      <c r="L8">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M8">
+        <v>1.8178596</v>
+      </c>
+      <c r="N8">
+        <v>47.14880706666667</v>
+      </c>
+      <c r="O8">
+        <v>9.901249484000001</v>
+      </c>
+      <c r="P8">
+        <v>37.24755758266667</v>
+      </c>
+      <c r="Q8">
+        <v>71.44755758266668</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08467021833605771</v>
+      </c>
+      <c r="T8">
+        <v>0.7857686181729041</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.21</v>
+      </c>
+      <c r="W8">
+        <v>0.035313</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>26.93644034262419</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08158221196366883</v>
+      </c>
+      <c r="C9">
+        <v>638.2888641390128</v>
+      </c>
+      <c r="D9">
+        <v>667.6348641390128</v>
+      </c>
+      <c r="E9">
+        <v>-444.554</v>
+      </c>
+      <c r="F9">
+        <v>47.446</v>
+      </c>
+      <c r="G9">
+        <v>18.1</v>
+      </c>
+      <c r="H9">
+        <v>185.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K9">
+        <v>34.2</v>
+      </c>
+      <c r="L9">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M9">
+        <v>2.1208362</v>
+      </c>
+      <c r="N9">
+        <v>46.84583046666667</v>
+      </c>
+      <c r="O9">
+        <v>9.837624398000001</v>
+      </c>
+      <c r="P9">
+        <v>37.00820606866667</v>
+      </c>
+      <c r="Q9">
+        <v>71.20820606866667</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08506484082114929</v>
+      </c>
+      <c r="T9">
+        <v>0.7925286026695685</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.21</v>
+      </c>
+      <c r="W9">
+        <v>0.035313</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.08837743653502</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08145563869144343</v>
+      </c>
+      <c r="C10">
+        <v>633.4919557835926</v>
+      </c>
+      <c r="D10">
+        <v>669.6159557835927</v>
+      </c>
+      <c r="E10">
+        <v>-437.776</v>
+      </c>
+      <c r="F10">
+        <v>54.224</v>
+      </c>
+      <c r="G10">
+        <v>18.1</v>
+      </c>
+      <c r="H10">
+        <v>185.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K10">
+        <v>34.2</v>
+      </c>
+      <c r="L10">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M10">
+        <v>2.4238128</v>
+      </c>
+      <c r="N10">
+        <v>46.54285386666667</v>
+      </c>
+      <c r="O10">
+        <v>9.773999312000001</v>
+      </c>
+      <c r="P10">
+        <v>36.76885455466667</v>
+      </c>
+      <c r="Q10">
+        <v>70.96885455466668</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08546804205591677</v>
+      </c>
+      <c r="T10">
+        <v>0.7994355433509429</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.21</v>
+      </c>
+      <c r="W10">
+        <v>0.035313</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.20233025696814</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.081329065419218</v>
+      </c>
+      <c r="C11">
+        <v>628.7068395166923</v>
+      </c>
+      <c r="D11">
+        <v>671.6088395166922</v>
+      </c>
+      <c r="E11">
+        <v>-430.9979999999999</v>
+      </c>
+      <c r="F11">
+        <v>61.002</v>
+      </c>
+      <c r="G11">
+        <v>18.1</v>
+      </c>
+      <c r="H11">
+        <v>185.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K11">
+        <v>34.2</v>
+      </c>
+      <c r="L11">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M11">
+        <v>2.7267894</v>
+      </c>
+      <c r="N11">
+        <v>46.23987726666667</v>
+      </c>
+      <c r="O11">
+        <v>9.710374225999999</v>
+      </c>
+      <c r="P11">
+        <v>36.52950304066667</v>
+      </c>
+      <c r="Q11">
+        <v>70.72950304066667</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08588010485628352</v>
+      </c>
+      <c r="T11">
+        <v>0.8064942849264135</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.21</v>
+      </c>
+      <c r="W11">
+        <v>0.035313</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>17.95762689508279</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08120249214699259</v>
+      </c>
+      <c r="C12">
+        <v>623.9336209379931</v>
+      </c>
+      <c r="D12">
+        <v>673.613620937993</v>
+      </c>
+      <c r="E12">
+        <v>-424.2199999999999</v>
+      </c>
+      <c r="F12">
+        <v>67.78</v>
+      </c>
+      <c r="G12">
+        <v>18.1</v>
+      </c>
+      <c r="H12">
+        <v>185.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K12">
+        <v>34.2</v>
+      </c>
+      <c r="L12">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M12">
+        <v>3.029766</v>
+      </c>
+      <c r="N12">
+        <v>45.93690066666667</v>
+      </c>
+      <c r="O12">
+        <v>9.646749139999999</v>
+      </c>
+      <c r="P12">
+        <v>36.29015152666667</v>
+      </c>
+      <c r="Q12">
+        <v>70.49015152666666</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08630132460776954</v>
+      </c>
+      <c r="T12">
+        <v>0.8137098874257834</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.21</v>
+      </c>
+      <c r="W12">
+        <v>0.035313</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.16186420557451</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08107591887476714</v>
+      </c>
+      <c r="C13">
+        <v>619.1724069118312</v>
+      </c>
+      <c r="D13">
+        <v>675.6304069118312</v>
+      </c>
+      <c r="E13">
+        <v>-417.442</v>
+      </c>
+      <c r="F13">
+        <v>74.55799999999999</v>
+      </c>
+      <c r="G13">
+        <v>18.1</v>
+      </c>
+      <c r="H13">
+        <v>185.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K13">
+        <v>34.2</v>
+      </c>
+      <c r="L13">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M13">
+        <v>3.3327426</v>
+      </c>
+      <c r="N13">
+        <v>45.63392406666667</v>
+      </c>
+      <c r="O13">
+        <v>9.583124053999999</v>
+      </c>
+      <c r="P13">
+        <v>36.05080001266667</v>
+      </c>
+      <c r="Q13">
+        <v>70.25080001266667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08673200997164848</v>
+      </c>
+      <c r="T13">
+        <v>0.8210876382959257</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.21</v>
+      </c>
+      <c r="W13">
+        <v>0.035313</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>14.69260382324956</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08094934560254174</v>
+      </c>
+      <c r="C14">
+        <v>614.4233055861833</v>
+      </c>
+      <c r="D14">
+        <v>677.6593055861833</v>
+      </c>
+      <c r="E14">
+        <v>-410.6639999999999</v>
+      </c>
+      <c r="F14">
+        <v>81.336</v>
+      </c>
+      <c r="G14">
+        <v>18.1</v>
+      </c>
+      <c r="H14">
+        <v>185.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K14">
+        <v>34.2</v>
+      </c>
+      <c r="L14">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M14">
+        <v>3.6357192</v>
+      </c>
+      <c r="N14">
+        <v>45.33094746666667</v>
+      </c>
+      <c r="O14">
+        <v>9.519498968000001</v>
+      </c>
+      <c r="P14">
+        <v>35.81144849866667</v>
+      </c>
+      <c r="Q14">
+        <v>70.01144849866668</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08717248363925198</v>
+      </c>
+      <c r="T14">
+        <v>0.8286330653222076</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.21</v>
+      </c>
+      <c r="W14">
+        <v>0.035313</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.46822017131209</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08093574233031632</v>
+      </c>
+      <c r="C15">
+        <v>607.8640838371447</v>
+      </c>
+      <c r="D15">
+        <v>677.8780838371447</v>
+      </c>
+      <c r="E15">
+        <v>-403.886</v>
+      </c>
+      <c r="F15">
+        <v>88.11399999999999</v>
+      </c>
+      <c r="G15">
+        <v>18.1</v>
+      </c>
+      <c r="H15">
+        <v>185.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K15">
+        <v>34.2</v>
+      </c>
+      <c r="L15">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M15">
+        <v>4.0356212</v>
+      </c>
+      <c r="N15">
+        <v>44.93104546666667</v>
+      </c>
+      <c r="O15">
+        <v>9.435519548</v>
+      </c>
+      <c r="P15">
+        <v>35.49552591866667</v>
+      </c>
+      <c r="Q15">
+        <v>69.69552591866668</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08762308313829463</v>
+      </c>
+      <c r="T15">
+        <v>0.8363519504410478</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.21</v>
+      </c>
+      <c r="W15">
+        <v>0.036182</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.13361320102756</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08081785905809091</v>
+      </c>
+      <c r="C16">
+        <v>602.9879057881901</v>
+      </c>
+      <c r="D16">
+        <v>679.77990578819</v>
+      </c>
+      <c r="E16">
+        <v>-397.1079999999999</v>
+      </c>
+      <c r="F16">
+        <v>94.892</v>
+      </c>
+      <c r="G16">
+        <v>18.1</v>
+      </c>
+      <c r="H16">
+        <v>185.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K16">
+        <v>34.2</v>
+      </c>
+      <c r="L16">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M16">
+        <v>4.3460536</v>
+      </c>
+      <c r="N16">
+        <v>44.62061306666667</v>
+      </c>
+      <c r="O16">
+        <v>9.370328744</v>
+      </c>
+      <c r="P16">
+        <v>35.25028432266667</v>
+      </c>
+      <c r="Q16">
+        <v>69.45028432266668</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08808416169545455</v>
+      </c>
+      <c r="T16">
+        <v>0.84425034451614</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.21</v>
+      </c>
+      <c r="W16">
+        <v>0.036182</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.2669265438113</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08069997578586549</v>
+      </c>
+      <c r="C17">
+        <v>598.1224290816865</v>
+      </c>
+      <c r="D17">
+        <v>681.6924290816864</v>
+      </c>
+      <c r="E17">
+        <v>-390.3299999999999</v>
+      </c>
+      <c r="F17">
+        <v>101.67</v>
+      </c>
+      <c r="G17">
+        <v>18.1</v>
+      </c>
+      <c r="H17">
+        <v>185.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K17">
+        <v>34.2</v>
+      </c>
+      <c r="L17">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M17">
+        <v>4.656485999999999</v>
+      </c>
+      <c r="N17">
+        <v>44.31018066666667</v>
+      </c>
+      <c r="O17">
+        <v>9.30513794</v>
+      </c>
+      <c r="P17">
+        <v>35.00504272666667</v>
+      </c>
+      <c r="Q17">
+        <v>69.20504272666668</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08855608915984176</v>
+      </c>
+      <c r="T17">
+        <v>0.8523345831577049</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.21</v>
+      </c>
+      <c r="W17">
+        <v>0.036182</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.51579810755722</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08086017251364006</v>
+      </c>
+      <c r="C18">
+        <v>588.7480323015219</v>
+      </c>
+      <c r="D18">
+        <v>679.0960323015219</v>
+      </c>
+      <c r="E18">
+        <v>-383.552</v>
+      </c>
+      <c r="F18">
+        <v>108.448</v>
+      </c>
+      <c r="G18">
+        <v>18.1</v>
+      </c>
+      <c r="H18">
+        <v>185.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K18">
+        <v>34.2</v>
+      </c>
+      <c r="L18">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M18">
+        <v>5.205503999999999</v>
+      </c>
+      <c r="N18">
+        <v>43.76116266666667</v>
+      </c>
+      <c r="O18">
+        <v>9.18984416</v>
+      </c>
+      <c r="P18">
+        <v>34.57131850666667</v>
+      </c>
+      <c r="Q18">
+        <v>68.77131850666667</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08903925299242865</v>
+      </c>
+      <c r="T18">
+        <v>0.860611303671688</v>
+      </c>
+      <c r="U18">
+        <v>0.048</v>
+      </c>
+      <c r="V18">
+        <v>0.21</v>
+      </c>
+      <c r="W18">
+        <v>0.03792</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>9.406710025900791</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08075966924141464</v>
+      </c>
+      <c r="C19">
+        <v>583.5966269490849</v>
+      </c>
+      <c r="D19">
+        <v>680.7226269490849</v>
+      </c>
+      <c r="E19">
+        <v>-376.7739999999999</v>
+      </c>
+      <c r="F19">
+        <v>115.226</v>
+      </c>
+      <c r="G19">
+        <v>18.1</v>
+      </c>
+      <c r="H19">
+        <v>185.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K19">
+        <v>34.2</v>
+      </c>
+      <c r="L19">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M19">
+        <v>5.530848</v>
+      </c>
+      <c r="N19">
+        <v>43.43581866666667</v>
+      </c>
+      <c r="O19">
+        <v>9.121521920000001</v>
+      </c>
+      <c r="P19">
+        <v>34.31429674666667</v>
+      </c>
+      <c r="Q19">
+        <v>68.51429674666667</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.0895340593270056</v>
+      </c>
+      <c r="T19">
+        <v>0.8690874632342009</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.21</v>
+      </c>
+      <c r="W19">
+        <v>0.03792</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>8.853374142024274</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08065916596918923</v>
+      </c>
+      <c r="C20">
+        <v>578.4530324586599</v>
+      </c>
+      <c r="D20">
+        <v>682.3570324586599</v>
+      </c>
+      <c r="E20">
+        <v>-369.996</v>
+      </c>
+      <c r="F20">
+        <v>122.004</v>
+      </c>
+      <c r="G20">
+        <v>18.1</v>
+      </c>
+      <c r="H20">
+        <v>185.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K20">
+        <v>34.2</v>
+      </c>
+      <c r="L20">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M20">
+        <v>5.856192</v>
+      </c>
+      <c r="N20">
+        <v>43.11047466666667</v>
+      </c>
+      <c r="O20">
+        <v>9.053199680000001</v>
+      </c>
+      <c r="P20">
+        <v>34.05727498666667</v>
+      </c>
+      <c r="Q20">
+        <v>68.25727498666667</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09004093410876735</v>
+      </c>
+      <c r="T20">
+        <v>0.8777703583957994</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.21</v>
+      </c>
+      <c r="W20">
+        <v>0.03792</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.361520023022925</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08055866269696382</v>
+      </c>
+      <c r="C21">
+        <v>573.3173052269663</v>
+      </c>
+      <c r="D21">
+        <v>683.9993052269663</v>
+      </c>
+      <c r="E21">
+        <v>-363.218</v>
+      </c>
+      <c r="F21">
+        <v>128.782</v>
+      </c>
+      <c r="G21">
+        <v>18.1</v>
+      </c>
+      <c r="H21">
+        <v>185.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K21">
+        <v>34.2</v>
+      </c>
+      <c r="L21">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M21">
+        <v>6.181535999999999</v>
+      </c>
+      <c r="N21">
+        <v>42.78513066666667</v>
+      </c>
+      <c r="O21">
+        <v>8.98487744</v>
+      </c>
+      <c r="P21">
+        <v>33.80025322666667</v>
+      </c>
+      <c r="Q21">
+        <v>68.00025322666667</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09056032431723929</v>
+      </c>
+      <c r="T21">
+        <v>0.8866676460305241</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.21</v>
+      </c>
+      <c r="W21">
+        <v>0.03792</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>7.921440021811192</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08069515942473839</v>
+      </c>
+      <c r="C22">
+        <v>564.3107979663298</v>
+      </c>
+      <c r="D22">
+        <v>681.7707979663297</v>
+      </c>
+      <c r="E22">
+        <v>-356.4399999999999</v>
+      </c>
+      <c r="F22">
+        <v>135.56</v>
+      </c>
+      <c r="G22">
+        <v>18.1</v>
+      </c>
+      <c r="H22">
+        <v>185.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K22">
+        <v>34.2</v>
+      </c>
+      <c r="L22">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M22">
+        <v>6.710220000000001</v>
+      </c>
+      <c r="N22">
+        <v>42.25644666666667</v>
+      </c>
+      <c r="O22">
+        <v>8.873853800000001</v>
+      </c>
+      <c r="P22">
+        <v>33.38259286666667</v>
+      </c>
+      <c r="Q22">
+        <v>67.58259286666667</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09109269928092299</v>
+      </c>
+      <c r="T22">
+        <v>0.8957873658561165</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.21</v>
+      </c>
+      <c r="W22">
+        <v>0.039105</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.297326565547279</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08060650615251298</v>
+      </c>
+      <c r="C23">
+        <v>558.9785349510696</v>
+      </c>
+      <c r="D23">
+        <v>683.2165349510695</v>
+      </c>
+      <c r="E23">
+        <v>-349.6619999999999</v>
+      </c>
+      <c r="F23">
+        <v>142.338</v>
+      </c>
+      <c r="G23">
+        <v>18.1</v>
+      </c>
+      <c r="H23">
+        <v>185.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K23">
+        <v>34.2</v>
+      </c>
+      <c r="L23">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M23">
+        <v>7.045731</v>
+      </c>
+      <c r="N23">
+        <v>41.92093566666667</v>
+      </c>
+      <c r="O23">
+        <v>8.803396489999999</v>
+      </c>
+      <c r="P23">
+        <v>33.11753917666667</v>
+      </c>
+      <c r="Q23">
+        <v>67.31753917666667</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09163855209178859</v>
+      </c>
+      <c r="T23">
+        <v>0.9051379646646355</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.21</v>
+      </c>
+      <c r="W23">
+        <v>0.039105</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>6.949834824330742</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08051785288028757</v>
+      </c>
+      <c r="C24">
+        <v>553.6524165144792</v>
+      </c>
+      <c r="D24">
+        <v>684.6684165144792</v>
+      </c>
+      <c r="E24">
+        <v>-342.884</v>
+      </c>
+      <c r="F24">
+        <v>149.116</v>
+      </c>
+      <c r="G24">
+        <v>18.1</v>
+      </c>
+      <c r="H24">
+        <v>185.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K24">
+        <v>34.2</v>
+      </c>
+      <c r="L24">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M24">
+        <v>7.381241999999999</v>
+      </c>
+      <c r="N24">
+        <v>41.58542466666667</v>
+      </c>
+      <c r="O24">
+        <v>8.732939180000001</v>
+      </c>
+      <c r="P24">
+        <v>32.85248548666667</v>
+      </c>
+      <c r="Q24">
+        <v>67.05248548666667</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09219840112857379</v>
+      </c>
+      <c r="T24">
+        <v>0.9147283224169626</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.21</v>
+      </c>
+      <c r="W24">
+        <v>0.039105</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.633933241406618</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08042919960806215</v>
+      </c>
+      <c r="C25">
+        <v>548.3324819129224</v>
+      </c>
+      <c r="D25">
+        <v>686.1264819129224</v>
+      </c>
+      <c r="E25">
+        <v>-336.1059999999999</v>
+      </c>
+      <c r="F25">
+        <v>155.894</v>
+      </c>
+      <c r="G25">
+        <v>18.1</v>
+      </c>
+      <c r="H25">
+        <v>185.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K25">
+        <v>34.2</v>
+      </c>
+      <c r="L25">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M25">
+        <v>7.716753000000001</v>
+      </c>
+      <c r="N25">
+        <v>41.24991366666667</v>
+      </c>
+      <c r="O25">
+        <v>8.662481870000001</v>
+      </c>
+      <c r="P25">
+        <v>32.58743179666667</v>
+      </c>
+      <c r="Q25">
+        <v>66.78743179666668</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.092772791698782</v>
+      </c>
+      <c r="T25">
+        <v>0.9245677803706489</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.21</v>
+      </c>
+      <c r="W25">
+        <v>0.039105</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.345501361345461</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08060598633583672</v>
+      </c>
+      <c r="C26">
+        <v>538.6530300824967</v>
+      </c>
+      <c r="D26">
+        <v>683.2250300824967</v>
+      </c>
+      <c r="E26">
+        <v>-329.328</v>
+      </c>
+      <c r="F26">
+        <v>162.672</v>
+      </c>
+      <c r="G26">
+        <v>18.1</v>
+      </c>
+      <c r="H26">
+        <v>185.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K26">
+        <v>34.2</v>
+      </c>
+      <c r="L26">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M26">
+        <v>8.2800048</v>
+      </c>
+      <c r="N26">
+        <v>40.68666186666667</v>
+      </c>
+      <c r="O26">
+        <v>8.544198992</v>
+      </c>
+      <c r="P26">
+        <v>32.14246287466667</v>
+      </c>
+      <c r="Q26">
+        <v>66.34246287466667</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09336229781031148</v>
+      </c>
+      <c r="T26">
+        <v>0.9346661714283796</v>
+      </c>
+      <c r="U26">
+        <v>0.0509</v>
+      </c>
+      <c r="V26">
+        <v>0.21</v>
+      </c>
+      <c r="W26">
+        <v>0.040211</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.913845202923876</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.0805283930636113</v>
+      </c>
+      <c r="C27">
+        <v>533.1454759793612</v>
+      </c>
+      <c r="D27">
+        <v>684.4954759793611</v>
+      </c>
+      <c r="E27">
+        <v>-322.55</v>
+      </c>
+      <c r="F27">
+        <v>169.45</v>
+      </c>
+      <c r="G27">
+        <v>18.1</v>
+      </c>
+      <c r="H27">
+        <v>185.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K27">
+        <v>34.2</v>
+      </c>
+      <c r="L27">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M27">
+        <v>8.625005</v>
+      </c>
+      <c r="N27">
+        <v>40.34166166666667</v>
+      </c>
+      <c r="O27">
+        <v>8.47174895</v>
+      </c>
+      <c r="P27">
+        <v>31.86991271666667</v>
+      </c>
+      <c r="Q27">
+        <v>66.06991271666666</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09396752408481507</v>
+      </c>
+      <c r="T27">
+        <v>0.9450338529143163</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.21</v>
+      </c>
+      <c r="W27">
+        <v>0.040211</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.677291394806921</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.08045079979138588</v>
+      </c>
+      <c r="C28">
+        <v>527.6426554253924</v>
+      </c>
+      <c r="D28">
+        <v>685.7706554253923</v>
+      </c>
+      <c r="E28">
+        <v>-315.7719999999999</v>
+      </c>
+      <c r="F28">
+        <v>176.228</v>
+      </c>
+      <c r="G28">
+        <v>18.1</v>
+      </c>
+      <c r="H28">
+        <v>185.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K28">
+        <v>34.2</v>
+      </c>
+      <c r="L28">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M28">
+        <v>8.970005199999999</v>
+      </c>
+      <c r="N28">
+        <v>39.99666146666667</v>
+      </c>
+      <c r="O28">
+        <v>8.399298907999999</v>
+      </c>
+      <c r="P28">
+        <v>31.59736255866667</v>
+      </c>
+      <c r="Q28">
+        <v>65.79736255866666</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09458910782619714</v>
+      </c>
+      <c r="T28">
+        <v>0.9556817420079812</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.21</v>
+      </c>
+      <c r="W28">
+        <v>0.040211</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.458934033468194</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08037320651916048</v>
+      </c>
+      <c r="C29">
+        <v>522.1445949250336</v>
+      </c>
+      <c r="D29">
+        <v>687.0505949250336</v>
+      </c>
+      <c r="E29">
+        <v>-308.9939999999999</v>
+      </c>
+      <c r="F29">
+        <v>183.006</v>
+      </c>
+      <c r="G29">
+        <v>18.1</v>
+      </c>
+      <c r="H29">
+        <v>185.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K29">
+        <v>34.2</v>
+      </c>
+      <c r="L29">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M29">
+        <v>9.3150054</v>
+      </c>
+      <c r="N29">
+        <v>39.65166126666666</v>
+      </c>
+      <c r="O29">
+        <v>8.326848865999999</v>
+      </c>
+      <c r="P29">
+        <v>31.32481240066667</v>
+      </c>
+      <c r="Q29">
+        <v>65.52481240066666</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09522772125912393</v>
+      </c>
+      <c r="T29">
+        <v>0.9666213540905136</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.21</v>
+      </c>
+      <c r="W29">
+        <v>0.040211</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.256751291487889</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08029561324693506</v>
+      </c>
+      <c r="C30">
+        <v>516.6513211809734</v>
+      </c>
+      <c r="D30">
+        <v>688.3353211809733</v>
+      </c>
+      <c r="E30">
+        <v>-302.216</v>
+      </c>
+      <c r="F30">
+        <v>189.784</v>
+      </c>
+      <c r="G30">
+        <v>18.1</v>
+      </c>
+      <c r="H30">
+        <v>185.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K30">
+        <v>34.2</v>
+      </c>
+      <c r="L30">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M30">
+        <v>9.6600056</v>
+      </c>
+      <c r="N30">
+        <v>39.30666106666667</v>
+      </c>
+      <c r="O30">
+        <v>8.254398824000001</v>
+      </c>
+      <c r="P30">
+        <v>31.05226224266667</v>
+      </c>
+      <c r="Q30">
+        <v>65.25226224266667</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09588407395407647</v>
+      </c>
+      <c r="T30">
+        <v>0.9778648442864497</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.21</v>
+      </c>
+      <c r="W30">
+        <v>0.040211</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.069010173934752</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08021801997470963</v>
+      </c>
+      <c r="C31">
+        <v>511.1628610960001</v>
+      </c>
+      <c r="D31">
+        <v>689.6248610960001</v>
+      </c>
+      <c r="E31">
+        <v>-295.438</v>
+      </c>
+      <c r="F31">
+        <v>196.562</v>
+      </c>
+      <c r="G31">
+        <v>18.1</v>
+      </c>
+      <c r="H31">
+        <v>185.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K31">
+        <v>34.2</v>
+      </c>
+      <c r="L31">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M31">
+        <v>10.0050058</v>
+      </c>
+      <c r="N31">
+        <v>38.96166086666667</v>
+      </c>
+      <c r="O31">
+        <v>8.181948782000001</v>
+      </c>
+      <c r="P31">
+        <v>30.77971208466667</v>
+      </c>
+      <c r="Q31">
+        <v>64.97971208466667</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09655891545733751</v>
+      </c>
+      <c r="T31">
+        <v>0.989425052516074</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.21</v>
+      </c>
+      <c r="W31">
+        <v>0.040211</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>4.89421671966114</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.0801404267024842</v>
+      </c>
+      <c r="C32">
+        <v>505.6792417748827</v>
+      </c>
+      <c r="D32">
+        <v>690.9192417748826</v>
+      </c>
+      <c r="E32">
+        <v>-288.66</v>
+      </c>
+      <c r="F32">
+        <v>203.34</v>
+      </c>
+      <c r="G32">
+        <v>18.1</v>
+      </c>
+      <c r="H32">
+        <v>185.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K32">
+        <v>34.2</v>
+      </c>
+      <c r="L32">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M32">
+        <v>10.350006</v>
+      </c>
+      <c r="N32">
+        <v>38.61666066666667</v>
+      </c>
+      <c r="O32">
+        <v>8.109498739999999</v>
+      </c>
+      <c r="P32">
+        <v>30.50716192666667</v>
+      </c>
+      <c r="Q32">
+        <v>64.70716192666667</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09725303814640601</v>
+      </c>
+      <c r="T32">
+        <v>1.001315552409402</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.21</v>
+      </c>
+      <c r="W32">
+        <v>0.040211</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.731076162339102</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.0800628334302588</v>
+      </c>
+      <c r="C33">
+        <v>500.2004905262659</v>
+      </c>
+      <c r="D33">
+        <v>692.2184905262659</v>
+      </c>
+      <c r="E33">
+        <v>-281.8819999999999</v>
+      </c>
+      <c r="F33">
+        <v>210.118</v>
+      </c>
+      <c r="G33">
+        <v>18.1</v>
+      </c>
+      <c r="H33">
+        <v>185.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K33">
+        <v>34.2</v>
+      </c>
+      <c r="L33">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M33">
+        <v>10.6950062</v>
+      </c>
+      <c r="N33">
+        <v>38.27166046666667</v>
+      </c>
+      <c r="O33">
+        <v>8.037048698</v>
+      </c>
+      <c r="P33">
+        <v>30.23461176866667</v>
+      </c>
+      <c r="Q33">
+        <v>64.43461176866667</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09796728033370841</v>
+      </c>
+      <c r="T33">
+        <v>1.013550704473551</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.21</v>
+      </c>
+      <c r="W33">
+        <v>0.040211</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.578460802263645</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08064252015803337</v>
+      </c>
+      <c r="C34">
+        <v>483.8324880559873</v>
+      </c>
+      <c r="D34">
+        <v>682.6284880559872</v>
+      </c>
+      <c r="E34">
+        <v>-275.1039999999999</v>
+      </c>
+      <c r="F34">
+        <v>216.896</v>
+      </c>
+      <c r="G34">
+        <v>18.1</v>
+      </c>
+      <c r="H34">
+        <v>185.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K34">
+        <v>34.2</v>
+      </c>
+      <c r="L34">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M34">
+        <v>11.603936</v>
+      </c>
+      <c r="N34">
+        <v>37.36273066666667</v>
+      </c>
+      <c r="O34">
+        <v>7.84617344</v>
+      </c>
+      <c r="P34">
+        <v>29.51655722666667</v>
+      </c>
+      <c r="Q34">
+        <v>63.71655722666667</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09870252964416673</v>
+      </c>
+      <c r="T34">
+        <v>1.026145713951351</v>
+      </c>
+      <c r="U34">
+        <v>0.0535</v>
+      </c>
+      <c r="V34">
+        <v>0.21</v>
+      </c>
+      <c r="W34">
+        <v>0.042265</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.219832534983533</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08058546688580796</v>
+      </c>
+      <c r="C35">
+        <v>477.9865391220748</v>
+      </c>
+      <c r="D35">
+        <v>683.5605391220747</v>
+      </c>
+      <c r="E35">
+        <v>-268.3259999999999</v>
+      </c>
+      <c r="F35">
+        <v>223.674</v>
+      </c>
+      <c r="G35">
+        <v>18.1</v>
+      </c>
+      <c r="H35">
+        <v>185.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K35">
+        <v>34.2</v>
+      </c>
+      <c r="L35">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M35">
+        <v>11.966559</v>
+      </c>
+      <c r="N35">
+        <v>37.00010766666666</v>
+      </c>
+      <c r="O35">
+        <v>7.770022609999999</v>
+      </c>
+      <c r="P35">
+        <v>29.23008505666667</v>
+      </c>
+      <c r="Q35">
+        <v>63.43008505666667</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09945972669523577</v>
+      </c>
+      <c r="T35">
+        <v>1.039116693861325</v>
+      </c>
+      <c r="U35">
+        <v>0.0535</v>
+      </c>
+      <c r="V35">
+        <v>0.21</v>
+      </c>
+      <c r="W35">
+        <v>0.042265</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.091958821802212</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08125363361358254</v>
+      </c>
+      <c r="C36">
+        <v>460.4501570995075</v>
+      </c>
+      <c r="D36">
+        <v>672.8021570995074</v>
+      </c>
+      <c r="E36">
+        <v>-261.5479999999999</v>
+      </c>
+      <c r="F36">
+        <v>230.452</v>
+      </c>
+      <c r="G36">
+        <v>18.1</v>
+      </c>
+      <c r="H36">
+        <v>185.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K36">
+        <v>34.2</v>
+      </c>
+      <c r="L36">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M36">
+        <v>12.9514024</v>
+      </c>
+      <c r="N36">
+        <v>36.01526426666667</v>
+      </c>
+      <c r="O36">
+        <v>7.563205496</v>
+      </c>
+      <c r="P36">
+        <v>28.45205877066667</v>
+      </c>
+      <c r="Q36">
+        <v>62.65205877066667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1002398691114887</v>
+      </c>
+      <c r="T36">
+        <v>1.052480733768571</v>
+      </c>
+      <c r="U36">
+        <v>0.0562</v>
+      </c>
+      <c r="V36">
+        <v>0.21</v>
+      </c>
+      <c r="W36">
+        <v>0.044398</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>3.780800345348444</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08121791034135711</v>
+      </c>
+      <c r="C37">
+        <v>454.23877375786</v>
+      </c>
+      <c r="D37">
+        <v>673.36877375786</v>
+      </c>
+      <c r="E37">
+        <v>-254.7699999999999</v>
+      </c>
+      <c r="F37">
+        <v>237.23</v>
+      </c>
+      <c r="G37">
+        <v>18.1</v>
+      </c>
+      <c r="H37">
+        <v>185.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K37">
+        <v>34.2</v>
+      </c>
+      <c r="L37">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M37">
+        <v>13.332326</v>
+      </c>
+      <c r="N37">
+        <v>35.63434066666667</v>
+      </c>
+      <c r="O37">
+        <v>7.48321154</v>
+      </c>
+      <c r="P37">
+        <v>28.15112912666667</v>
+      </c>
+      <c r="Q37">
+        <v>62.35112912666667</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1010440159097802</v>
+      </c>
+      <c r="T37">
+        <v>1.066255974903731</v>
+      </c>
+      <c r="U37">
+        <v>0.0562</v>
+      </c>
+      <c r="V37">
+        <v>0.21</v>
+      </c>
+      <c r="W37">
+        <v>0.044398</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.672777478338488</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.0811821870691317</v>
+      </c>
+      <c r="C38">
+        <v>448.0283456005733</v>
+      </c>
+      <c r="D38">
+        <v>673.9363456005733</v>
+      </c>
+      <c r="E38">
+        <v>-247.992</v>
+      </c>
+      <c r="F38">
+        <v>244.008</v>
+      </c>
+      <c r="G38">
+        <v>18.1</v>
+      </c>
+      <c r="H38">
+        <v>185.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K38">
+        <v>34.2</v>
+      </c>
+      <c r="L38">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M38">
+        <v>13.7132496</v>
+      </c>
+      <c r="N38">
+        <v>35.25341706666667</v>
+      </c>
+      <c r="O38">
+        <v>7.403217584000001</v>
+      </c>
+      <c r="P38">
+        <v>27.85019948266667</v>
+      </c>
+      <c r="Q38">
+        <v>62.05019948266667</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1018732922955183</v>
+      </c>
+      <c r="T38">
+        <v>1.080461692324366</v>
+      </c>
+      <c r="U38">
+        <v>0.0562</v>
+      </c>
+      <c r="V38">
+        <v>0.21</v>
+      </c>
+      <c r="W38">
+        <v>0.044398</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.570755881717975</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08252027379690628</v>
+      </c>
+      <c r="C39">
+        <v>420.6240960120623</v>
+      </c>
+      <c r="D39">
+        <v>653.3100960120622</v>
+      </c>
+      <c r="E39">
+        <v>-241.214</v>
+      </c>
+      <c r="F39">
+        <v>250.786</v>
+      </c>
+      <c r="G39">
+        <v>18.1</v>
+      </c>
+      <c r="H39">
+        <v>185.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K39">
+        <v>34.2</v>
+      </c>
+      <c r="L39">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M39">
+        <v>15.2728674</v>
+      </c>
+      <c r="N39">
+        <v>33.69379926666667</v>
+      </c>
+      <c r="O39">
+        <v>7.075697846000002</v>
+      </c>
+      <c r="P39">
+        <v>26.61810142066667</v>
+      </c>
+      <c r="Q39">
+        <v>60.81810142066668</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1027288949157243</v>
+      </c>
+      <c r="T39">
+        <v>1.095118384901211</v>
+      </c>
+      <c r="U39">
+        <v>0.0609</v>
+      </c>
+      <c r="V39">
+        <v>0.21</v>
+      </c>
+      <c r="W39">
+        <v>0.048111</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.206121377487156</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08252168052468087</v>
+      </c>
+      <c r="C40">
+        <v>413.8250760181726</v>
+      </c>
+      <c r="D40">
+        <v>653.2890760181725</v>
+      </c>
+      <c r="E40">
+        <v>-234.436</v>
+      </c>
+      <c r="F40">
+        <v>257.564</v>
+      </c>
+      <c r="G40">
+        <v>18.1</v>
+      </c>
+      <c r="H40">
+        <v>185.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K40">
+        <v>34.2</v>
+      </c>
+      <c r="L40">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M40">
+        <v>15.6856476</v>
+      </c>
+      <c r="N40">
+        <v>33.28101906666667</v>
+      </c>
+      <c r="O40">
+        <v>6.989014004000001</v>
+      </c>
+      <c r="P40">
+        <v>26.29200506266667</v>
+      </c>
+      <c r="Q40">
+        <v>60.49200506266668</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.103612097620453</v>
+      </c>
+      <c r="T40">
+        <v>1.110247874012793</v>
+      </c>
+      <c r="U40">
+        <v>0.0609</v>
+      </c>
+      <c r="V40">
+        <v>0.21</v>
+      </c>
+      <c r="W40">
+        <v>0.048111</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.121749762290125</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08252308725245545</v>
+      </c>
+      <c r="C41">
+        <v>407.0260573768592</v>
+      </c>
+      <c r="D41">
+        <v>653.2680573768591</v>
+      </c>
+      <c r="E41">
+        <v>-227.658</v>
+      </c>
+      <c r="F41">
+        <v>264.342</v>
+      </c>
+      <c r="G41">
+        <v>18.1</v>
+      </c>
+      <c r="H41">
+        <v>185.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K41">
+        <v>34.2</v>
+      </c>
+      <c r="L41">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M41">
+        <v>16.0984278</v>
+      </c>
+      <c r="N41">
+        <v>32.86823886666667</v>
+      </c>
+      <c r="O41">
+        <v>6.902330162000001</v>
+      </c>
+      <c r="P41">
+        <v>25.96590870466667</v>
+      </c>
+      <c r="Q41">
+        <v>60.16590870466668</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1045242577909106</v>
+      </c>
+      <c r="T41">
+        <v>1.125873411947706</v>
+      </c>
+      <c r="U41">
+        <v>0.0609</v>
+      </c>
+      <c r="V41">
+        <v>0.21</v>
+      </c>
+      <c r="W41">
+        <v>0.048111</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.041704896590379</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08546329398023003</v>
+      </c>
+      <c r="C42">
+        <v>359.0863010260658</v>
+      </c>
+      <c r="D42">
+        <v>612.1063010260658</v>
+      </c>
+      <c r="E42">
+        <v>-220.8799999999999</v>
+      </c>
+      <c r="F42">
+        <v>271.12</v>
+      </c>
+      <c r="G42">
+        <v>18.1</v>
+      </c>
+      <c r="H42">
+        <v>185.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K42">
+        <v>34.2</v>
+      </c>
+      <c r="L42">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M42">
+        <v>19.032624</v>
+      </c>
+      <c r="N42">
+        <v>29.93404266666667</v>
+      </c>
+      <c r="O42">
+        <v>6.28614896</v>
+      </c>
+      <c r="P42">
+        <v>23.64789370666667</v>
+      </c>
+      <c r="Q42">
+        <v>57.84789370666667</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1054668233003834</v>
+      </c>
+      <c r="T42">
+        <v>1.142019801147116</v>
+      </c>
+      <c r="U42">
+        <v>0.0702</v>
+      </c>
+      <c r="V42">
+        <v>0.21</v>
+      </c>
+      <c r="W42">
+        <v>0.055458</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>2.572775391699362</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08553817070800461</v>
+      </c>
+      <c r="C43">
+        <v>351.3276782037186</v>
+      </c>
+      <c r="D43">
+        <v>611.1256782037186</v>
+      </c>
+      <c r="E43">
+        <v>-214.1019999999999</v>
+      </c>
+      <c r="F43">
+        <v>277.898</v>
+      </c>
+      <c r="G43">
+        <v>18.1</v>
+      </c>
+      <c r="H43">
+        <v>185.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K43">
+        <v>34.2</v>
+      </c>
+      <c r="L43">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M43">
+        <v>19.5084396</v>
+      </c>
+      <c r="N43">
+        <v>29.45822706666667</v>
+      </c>
+      <c r="O43">
+        <v>6.186227683999999</v>
+      </c>
+      <c r="P43">
+        <v>23.27199938266667</v>
+      </c>
+      <c r="Q43">
+        <v>57.47199938266667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1064413401830587</v>
+      </c>
+      <c r="T43">
+        <v>1.158713525573624</v>
+      </c>
+      <c r="U43">
+        <v>0.0702</v>
+      </c>
+      <c r="V43">
+        <v>0.21</v>
+      </c>
+      <c r="W43">
+        <v>0.055458</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.510024772389621</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.0871725074357792</v>
+      </c>
+      <c r="C44">
+        <v>323.9018930439249</v>
+      </c>
+      <c r="D44">
+        <v>590.4778930439248</v>
+      </c>
+      <c r="E44">
+        <v>-207.324</v>
+      </c>
+      <c r="F44">
+        <v>284.676</v>
+      </c>
+      <c r="G44">
+        <v>18.1</v>
+      </c>
+      <c r="H44">
+        <v>185.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K44">
+        <v>34.2</v>
+      </c>
+      <c r="L44">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M44">
+        <v>21.3222324</v>
+      </c>
+      <c r="N44">
+        <v>27.64443426666667</v>
+      </c>
+      <c r="O44">
+        <v>5.805331196000001</v>
+      </c>
+      <c r="P44">
+        <v>21.83910307066667</v>
+      </c>
+      <c r="Q44">
+        <v>56.03910307066667</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.107449461096171</v>
+      </c>
+      <c r="T44">
+        <v>1.175982895670012</v>
+      </c>
+      <c r="U44">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V44">
+        <v>0.21</v>
+      </c>
+      <c r="W44">
+        <v>0.059171</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.296507502031854</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08728451416355378</v>
+      </c>
+      <c r="C45">
+        <v>315.7597977701232</v>
+      </c>
+      <c r="D45">
+        <v>589.1137977701231</v>
+      </c>
+      <c r="E45">
+        <v>-200.546</v>
+      </c>
+      <c r="F45">
+        <v>291.454</v>
+      </c>
+      <c r="G45">
+        <v>18.1</v>
+      </c>
+      <c r="H45">
+        <v>185.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K45">
+        <v>34.2</v>
+      </c>
+      <c r="L45">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M45">
+        <v>21.8299046</v>
+      </c>
+      <c r="N45">
+        <v>27.13676206666667</v>
+      </c>
+      <c r="O45">
+        <v>5.698720034000001</v>
+      </c>
+      <c r="P45">
+        <v>21.43804203266667</v>
+      </c>
+      <c r="Q45">
+        <v>55.63804203266668</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1084929546729013</v>
+      </c>
+      <c r="T45">
+        <v>1.1938582085768</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.21</v>
+      </c>
+      <c r="W45">
+        <v>0.059171</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.243100350821812</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08739652089132838</v>
+      </c>
+      <c r="C46">
+        <v>307.6239905122197</v>
+      </c>
+      <c r="D46">
+        <v>587.7559905122197</v>
+      </c>
+      <c r="E46">
+        <v>-193.768</v>
+      </c>
+      <c r="F46">
+        <v>298.232</v>
+      </c>
+      <c r="G46">
+        <v>18.1</v>
+      </c>
+      <c r="H46">
+        <v>185.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K46">
+        <v>34.2</v>
+      </c>
+      <c r="L46">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M46">
+        <v>22.3375768</v>
+      </c>
+      <c r="N46">
+        <v>26.62908986666667</v>
+      </c>
+      <c r="O46">
+        <v>5.592108872000001</v>
+      </c>
+      <c r="P46">
+        <v>21.03698099466667</v>
+      </c>
+      <c r="Q46">
+        <v>55.23698099466667</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1095737158773721</v>
+      </c>
+      <c r="T46">
+        <v>1.212371925515973</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.21</v>
+      </c>
+      <c r="W46">
+        <v>0.059171</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.192120797394043</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08750852761910295</v>
+      </c>
+      <c r="C47">
+        <v>299.4944278917689</v>
+      </c>
+      <c r="D47">
+        <v>586.4044278917688</v>
+      </c>
+      <c r="E47">
+        <v>-186.99</v>
+      </c>
+      <c r="F47">
+        <v>305.01</v>
+      </c>
+      <c r="G47">
+        <v>18.1</v>
+      </c>
+      <c r="H47">
+        <v>185.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K47">
+        <v>34.2</v>
+      </c>
+      <c r="L47">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M47">
+        <v>22.845249</v>
+      </c>
+      <c r="N47">
+        <v>26.12141766666667</v>
+      </c>
+      <c r="O47">
+        <v>5.485497710000001</v>
+      </c>
+      <c r="P47">
+        <v>20.63591995666667</v>
+      </c>
+      <c r="Q47">
+        <v>54.83591995666667</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1106937774892781</v>
+      </c>
+      <c r="T47">
+        <v>1.231558868525661</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0.21</v>
+      </c>
+      <c r="W47">
+        <v>0.059171</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.143407001896398</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08762053434687753</v>
+      </c>
+      <c r="C48">
+        <v>291.3710669284086</v>
+      </c>
+      <c r="D48">
+        <v>585.0590669284086</v>
+      </c>
+      <c r="E48">
+        <v>-180.2119999999999</v>
+      </c>
+      <c r="F48">
+        <v>311.788</v>
+      </c>
+      <c r="G48">
+        <v>18.1</v>
+      </c>
+      <c r="H48">
+        <v>185.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K48">
+        <v>34.2</v>
+      </c>
+      <c r="L48">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M48">
+        <v>23.3529212</v>
+      </c>
+      <c r="N48">
+        <v>25.61374546666667</v>
+      </c>
+      <c r="O48">
+        <v>5.378886548</v>
+      </c>
+      <c r="P48">
+        <v>20.23485891866667</v>
+      </c>
+      <c r="Q48">
+        <v>54.43485891866667</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.111855322864588</v>
+      </c>
+      <c r="T48">
+        <v>1.251456439054227</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.21</v>
+      </c>
+      <c r="W48">
+        <v>0.059171</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.096811197507345</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08773254107465212</v>
+      </c>
+      <c r="C49">
+        <v>283.2538650353059</v>
+      </c>
+      <c r="D49">
+        <v>583.7198650353058</v>
+      </c>
+      <c r="E49">
+        <v>-173.434</v>
+      </c>
+      <c r="F49">
+        <v>318.566</v>
+      </c>
+      <c r="G49">
+        <v>18.1</v>
+      </c>
+      <c r="H49">
+        <v>185.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K49">
+        <v>34.2</v>
+      </c>
+      <c r="L49">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M49">
+        <v>23.8605934</v>
+      </c>
+      <c r="N49">
+        <v>25.10607326666667</v>
+      </c>
+      <c r="O49">
+        <v>5.272275386000001</v>
+      </c>
+      <c r="P49">
+        <v>19.83379788066667</v>
+      </c>
+      <c r="Q49">
+        <v>54.03379788066668</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.113060700140853</v>
+      </c>
+      <c r="T49">
+        <v>1.272104861300851</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.21</v>
+      </c>
+      <c r="W49">
+        <v>0.059171</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.052198193305061</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08784454780242669</v>
+      </c>
+      <c r="C50">
+        <v>275.1427800146629</v>
+      </c>
+      <c r="D50">
+        <v>582.3867800146629</v>
+      </c>
+      <c r="E50">
+        <v>-166.6559999999999</v>
+      </c>
+      <c r="F50">
+        <v>325.344</v>
+      </c>
+      <c r="G50">
+        <v>18.1</v>
+      </c>
+      <c r="H50">
+        <v>185.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K50">
+        <v>34.2</v>
+      </c>
+      <c r="L50">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M50">
+        <v>24.3682656</v>
+      </c>
+      <c r="N50">
+        <v>24.59840106666667</v>
+      </c>
+      <c r="O50">
+        <v>5.165664224</v>
+      </c>
+      <c r="P50">
+        <v>19.43273684266667</v>
+      </c>
+      <c r="Q50">
+        <v>53.63273684266667</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1143124380815898</v>
+      </c>
+      <c r="T50">
+        <v>1.293547453633885</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.21</v>
+      </c>
+      <c r="W50">
+        <v>0.059171</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.009444064277873</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09426628453020126</v>
+      </c>
+      <c r="C51">
+        <v>200.9376103986028</v>
+      </c>
+      <c r="D51">
+        <v>514.9596103986028</v>
+      </c>
+      <c r="E51">
+        <v>-159.878</v>
+      </c>
+      <c r="F51">
+        <v>332.122</v>
+      </c>
+      <c r="G51">
+        <v>18.1</v>
+      </c>
+      <c r="H51">
+        <v>185.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K51">
+        <v>34.2</v>
+      </c>
+      <c r="L51">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M51">
+        <v>30.2895264</v>
+      </c>
+      <c r="N51">
+        <v>18.67714026666667</v>
+      </c>
+      <c r="O51">
+        <v>3.922199456000001</v>
+      </c>
+      <c r="P51">
+        <v>14.75494081066667</v>
+      </c>
+      <c r="Q51">
+        <v>48.95494081066667</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1156132637847084</v>
+      </c>
+      <c r="T51">
+        <v>1.315830931940762</v>
+      </c>
+      <c r="U51">
+        <v>0.0912</v>
+      </c>
+      <c r="V51">
+        <v>0.21</v>
+      </c>
+      <c r="W51">
+        <v>0.072048</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.616620412614529</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09450706125797585</v>
+      </c>
+      <c r="C52">
+        <v>191.9338550432151</v>
+      </c>
+      <c r="D52">
+        <v>512.733855043215</v>
+      </c>
+      <c r="E52">
+        <v>-153.1</v>
+      </c>
+      <c r="F52">
+        <v>338.9</v>
+      </c>
+      <c r="G52">
+        <v>18.1</v>
+      </c>
+      <c r="H52">
+        <v>185.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K52">
+        <v>34.2</v>
+      </c>
+      <c r="L52">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M52">
+        <v>30.90768</v>
+      </c>
+      <c r="N52">
+        <v>18.05898666666667</v>
+      </c>
+      <c r="O52">
+        <v>3.7923872</v>
+      </c>
+      <c r="P52">
+        <v>14.26659946666667</v>
+      </c>
+      <c r="Q52">
+        <v>48.46659946666667</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1169661225159517</v>
+      </c>
+      <c r="T52">
+        <v>1.339005749379915</v>
+      </c>
+      <c r="U52">
+        <v>0.0912</v>
+      </c>
+      <c r="V52">
+        <v>0.21</v>
+      </c>
+      <c r="W52">
+        <v>0.072048</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.584288004362238</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09474783798575044</v>
+      </c>
+      <c r="C53">
+        <v>182.9492571784682</v>
+      </c>
+      <c r="D53">
+        <v>510.5272571784682</v>
+      </c>
+      <c r="E53">
+        <v>-146.3219999999999</v>
+      </c>
+      <c r="F53">
+        <v>345.678</v>
+      </c>
+      <c r="G53">
+        <v>18.1</v>
+      </c>
+      <c r="H53">
+        <v>185.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K53">
+        <v>34.2</v>
+      </c>
+      <c r="L53">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M53">
+        <v>31.5258336</v>
+      </c>
+      <c r="N53">
+        <v>17.44083306666667</v>
+      </c>
+      <c r="O53">
+        <v>3.662574944</v>
+      </c>
+      <c r="P53">
+        <v>13.77825812266667</v>
+      </c>
+      <c r="Q53">
+        <v>47.97825812266667</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1183741999709193</v>
+      </c>
+      <c r="T53">
+        <v>1.363126477734952</v>
+      </c>
+      <c r="U53">
+        <v>0.0912</v>
+      </c>
+      <c r="V53">
+        <v>0.21</v>
+      </c>
+      <c r="W53">
+        <v>0.072048</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.553223533688469</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.09498861471352502</v>
+      </c>
+      <c r="C54">
+        <v>173.9835705261121</v>
+      </c>
+      <c r="D54">
+        <v>508.3395705261121</v>
+      </c>
+      <c r="E54">
+        <v>-139.544</v>
+      </c>
+      <c r="F54">
+        <v>352.456</v>
+      </c>
+      <c r="G54">
+        <v>18.1</v>
+      </c>
+      <c r="H54">
+        <v>185.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K54">
+        <v>34.2</v>
+      </c>
+      <c r="L54">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M54">
+        <v>32.1439872</v>
+      </c>
+      <c r="N54">
+        <v>16.82267946666667</v>
+      </c>
+      <c r="O54">
+        <v>3.532762688</v>
+      </c>
+      <c r="P54">
+        <v>13.28991677866667</v>
+      </c>
+      <c r="Q54">
+        <v>47.48991677866668</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1198409473198438</v>
+      </c>
+      <c r="T54">
+        <v>1.388252236438115</v>
+      </c>
+      <c r="U54">
+        <v>0.0912</v>
+      </c>
+      <c r="V54">
+        <v>0.21</v>
+      </c>
+      <c r="W54">
+        <v>0.072048</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.523353850348306</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1255005795083592</v>
+      </c>
+      <c r="C55">
+        <v>-11.6910316381032</v>
+      </c>
+      <c r="D55">
+        <v>329.4429683618968</v>
+      </c>
+      <c r="E55">
+        <v>-132.766</v>
+      </c>
+      <c r="F55">
+        <v>359.234</v>
+      </c>
+      <c r="G55">
+        <v>18.1</v>
+      </c>
+      <c r="H55">
+        <v>185.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K55">
+        <v>34.2</v>
+      </c>
+      <c r="L55">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M55">
+        <v>56.2560444</v>
+      </c>
+      <c r="N55">
+        <v>-7.289377733333332</v>
+      </c>
+      <c r="O55">
+        <v>-1.530769324</v>
+      </c>
+      <c r="P55">
+        <v>-5.758608409333332</v>
+      </c>
+      <c r="Q55">
+        <v>28.44139159066667</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1227100456130468</v>
+      </c>
+      <c r="T55">
+        <v>1.437400626897817</v>
+      </c>
+      <c r="U55">
+        <v>0.1566</v>
+      </c>
+      <c r="V55">
+        <v>0.1827892470875538</v>
+      </c>
+      <c r="W55">
+        <v>0.1279752039060891</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8704249861312088</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1266785795083592</v>
+      </c>
+      <c r="C56">
+        <v>-22.88516829963629</v>
+      </c>
+      <c r="D56">
+        <v>325.0268317003637</v>
+      </c>
+      <c r="E56">
+        <v>-125.9879999999999</v>
+      </c>
+      <c r="F56">
+        <v>366.012</v>
+      </c>
+      <c r="G56">
+        <v>18.1</v>
+      </c>
+      <c r="H56">
+        <v>185.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K56">
+        <v>34.2</v>
+      </c>
+      <c r="L56">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M56">
+        <v>57.31747920000001</v>
+      </c>
+      <c r="N56">
+        <v>-8.35081253333334</v>
+      </c>
+      <c r="O56">
+        <v>-1.753670632000001</v>
+      </c>
+      <c r="P56">
+        <v>-6.597141901333338</v>
+      </c>
+      <c r="Q56">
+        <v>27.60285809866667</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1245341770394173</v>
+      </c>
+      <c r="T56">
+        <v>1.468648466612987</v>
+      </c>
+      <c r="U56">
+        <v>0.1566</v>
+      </c>
+      <c r="V56">
+        <v>0.1794042610303769</v>
+      </c>
+      <c r="W56">
+        <v>0.128505292722643</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.8543060049065567</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1278565795083592</v>
+      </c>
+      <c r="C57">
+        <v>-33.96247565970731</v>
+      </c>
+      <c r="D57">
+        <v>320.7275243402927</v>
+      </c>
+      <c r="E57">
+        <v>-119.2099999999999</v>
+      </c>
+      <c r="F57">
+        <v>372.79</v>
+      </c>
+      <c r="G57">
+        <v>18.1</v>
+      </c>
+      <c r="H57">
+        <v>185.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K57">
+        <v>34.2</v>
+      </c>
+      <c r="L57">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M57">
+        <v>58.37891400000001</v>
+      </c>
+      <c r="N57">
+        <v>-9.41224733333334</v>
+      </c>
+      <c r="O57">
+        <v>-1.976571940000001</v>
+      </c>
+      <c r="P57">
+        <v>-7.435675393333339</v>
+      </c>
+      <c r="Q57">
+        <v>26.76432460666666</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1264393809736266</v>
+      </c>
+      <c r="T57">
+        <v>1.501285099204387</v>
+      </c>
+      <c r="U57">
+        <v>0.1566</v>
+      </c>
+      <c r="V57">
+        <v>0.1761423653752791</v>
+      </c>
+      <c r="W57">
+        <v>0.1290161055822313</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.8387731684537102</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1290345795083592</v>
+      </c>
+      <c r="C58">
+        <v>-44.9275292896059</v>
+      </c>
+      <c r="D58">
+        <v>316.5404707103941</v>
+      </c>
+      <c r="E58">
+        <v>-112.432</v>
+      </c>
+      <c r="F58">
+        <v>379.568</v>
+      </c>
+      <c r="G58">
+        <v>18.1</v>
+      </c>
+      <c r="H58">
+        <v>185.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K58">
+        <v>34.2</v>
+      </c>
+      <c r="L58">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M58">
+        <v>59.4403488</v>
+      </c>
+      <c r="N58">
+        <v>-10.47368213333333</v>
+      </c>
+      <c r="O58">
+        <v>-2.199473248</v>
+      </c>
+      <c r="P58">
+        <v>-8.274208885333334</v>
+      </c>
+      <c r="Q58">
+        <v>25.92579111466667</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1284311850866636</v>
+      </c>
+      <c r="T58">
+        <v>1.535405215095396</v>
+      </c>
+      <c r="U58">
+        <v>0.1566</v>
+      </c>
+      <c r="V58">
+        <v>0.1729969659935777</v>
+      </c>
+      <c r="W58">
+        <v>0.1295086751254057</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.823795076159894</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1302125795083592</v>
+      </c>
+      <c r="C59">
+        <v>-55.78466890586361</v>
+      </c>
+      <c r="D59">
+        <v>312.4613310941364</v>
+      </c>
+      <c r="E59">
+        <v>-105.6539999999999</v>
+      </c>
+      <c r="F59">
+        <v>386.346</v>
+      </c>
+      <c r="G59">
+        <v>18.1</v>
+      </c>
+      <c r="H59">
+        <v>185.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K59">
+        <v>34.2</v>
+      </c>
+      <c r="L59">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M59">
+        <v>60.50178360000001</v>
+      </c>
+      <c r="N59">
+        <v>-11.53511693333334</v>
+      </c>
+      <c r="O59">
+        <v>-2.422374556000002</v>
+      </c>
+      <c r="P59">
+        <v>-9.11274237733334</v>
+      </c>
+      <c r="Q59">
+        <v>25.08725762266666</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1305156312514697</v>
+      </c>
+      <c r="T59">
+        <v>1.57111231312087</v>
+      </c>
+      <c r="U59">
+        <v>0.1566</v>
+      </c>
+      <c r="V59">
+        <v>0.1699619315024623</v>
+      </c>
+      <c r="W59">
+        <v>0.1299839615267144</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.8093425309641064</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1627242053661379</v>
+      </c>
+      <c r="C60">
+        <v>-144.5371779337173</v>
+      </c>
+      <c r="D60">
+        <v>230.4868220662827</v>
+      </c>
+      <c r="E60">
+        <v>-98.87599999999998</v>
+      </c>
+      <c r="F60">
+        <v>393.124</v>
+      </c>
+      <c r="G60">
+        <v>18.1</v>
+      </c>
+      <c r="H60">
+        <v>185.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K60">
+        <v>34.2</v>
+      </c>
+      <c r="L60">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M60">
+        <v>82.0842912</v>
+      </c>
+      <c r="N60">
+        <v>-33.11762453333333</v>
+      </c>
+      <c r="O60">
+        <v>-6.954701151999998</v>
+      </c>
+      <c r="P60">
+        <v>-26.16292338133333</v>
+      </c>
+      <c r="Q60">
+        <v>8.037076618666674</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.135217493561692</v>
+      </c>
+      <c r="T60">
+        <v>1.651656421790142</v>
+      </c>
+      <c r="U60">
+        <v>0.2088</v>
+      </c>
+      <c r="V60">
+        <v>0.1252736650298322</v>
+      </c>
+      <c r="W60">
+        <v>0.1826428587417711</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5965412620468199</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1644242053661379</v>
+      </c>
+      <c r="C61">
+        <v>-154.4342233149055</v>
+      </c>
+      <c r="D61">
+        <v>227.3677766850945</v>
+      </c>
+      <c r="E61">
+        <v>-92.09800000000001</v>
+      </c>
+      <c r="F61">
+        <v>399.9019999999999</v>
+      </c>
+      <c r="G61">
+        <v>18.1</v>
+      </c>
+      <c r="H61">
+        <v>185.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K61">
+        <v>34.2</v>
+      </c>
+      <c r="L61">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M61">
+        <v>83.4995376</v>
+      </c>
+      <c r="N61">
+        <v>-34.53287093333333</v>
+      </c>
+      <c r="O61">
+        <v>-7.251902895999999</v>
+      </c>
+      <c r="P61">
+        <v>-27.28096803733333</v>
+      </c>
+      <c r="Q61">
+        <v>6.919031962666672</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1375691397461236</v>
+      </c>
+      <c r="T61">
+        <v>1.691940724760633</v>
+      </c>
+      <c r="U61">
+        <v>0.2088</v>
+      </c>
+      <c r="V61">
+        <v>0.1231503825716994</v>
+      </c>
+      <c r="W61">
+        <v>0.1830862001190292</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5864303931985687</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1661242053661379</v>
+      </c>
+      <c r="C62">
+        <v>-164.2479793147419</v>
+      </c>
+      <c r="D62">
+        <v>224.3320206852581</v>
+      </c>
+      <c r="E62">
+        <v>-85.31999999999999</v>
+      </c>
+      <c r="F62">
+        <v>406.6799999999999</v>
+      </c>
+      <c r="G62">
+        <v>18.1</v>
+      </c>
+      <c r="H62">
+        <v>185.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K62">
+        <v>34.2</v>
+      </c>
+      <c r="L62">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M62">
+        <v>84.914784</v>
+      </c>
+      <c r="N62">
+        <v>-35.94811733333333</v>
+      </c>
+      <c r="O62">
+        <v>-7.549104639999999</v>
+      </c>
+      <c r="P62">
+        <v>-28.39901269333333</v>
+      </c>
+      <c r="Q62">
+        <v>5.800987306666674</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1400383682397767</v>
+      </c>
+      <c r="T62">
+        <v>1.734239242879649</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.1210978761955044</v>
+      </c>
+      <c r="W62">
+        <v>0.1835147634503787</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5766565533119259</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1678242053661379</v>
+      </c>
+      <c r="C63">
+        <v>-173.9817381514867</v>
+      </c>
+      <c r="D63">
+        <v>221.3762618485133</v>
+      </c>
+      <c r="E63">
+        <v>-78.54199999999997</v>
+      </c>
+      <c r="F63">
+        <v>413.458</v>
+      </c>
+      <c r="G63">
+        <v>18.1</v>
+      </c>
+      <c r="H63">
+        <v>185.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K63">
+        <v>34.2</v>
+      </c>
+      <c r="L63">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M63">
+        <v>86.3300304</v>
+      </c>
+      <c r="N63">
+        <v>-37.36336373333333</v>
+      </c>
+      <c r="O63">
+        <v>-7.846306383999999</v>
+      </c>
+      <c r="P63">
+        <v>-29.51705734933333</v>
+      </c>
+      <c r="Q63">
+        <v>4.682942650666671</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1426342238356684</v>
+      </c>
+      <c r="T63">
+        <v>1.778706915773999</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.1191126651103322</v>
+      </c>
+      <c r="W63">
+        <v>0.1839292755249626</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5672031671920582</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1695242053661379</v>
+      </c>
+      <c r="C64">
+        <v>-183.6386207890856</v>
+      </c>
+      <c r="D64">
+        <v>218.4973792109144</v>
+      </c>
+      <c r="E64">
+        <v>-71.76399999999995</v>
+      </c>
+      <c r="F64">
+        <v>420.236</v>
+      </c>
+      <c r="G64">
+        <v>18.1</v>
+      </c>
+      <c r="H64">
+        <v>185.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K64">
+        <v>34.2</v>
+      </c>
+      <c r="L64">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M64">
+        <v>87.7452768</v>
+      </c>
+      <c r="N64">
+        <v>-38.77861013333333</v>
+      </c>
+      <c r="O64">
+        <v>-8.143508127999999</v>
+      </c>
+      <c r="P64">
+        <v>-30.63510200533333</v>
+      </c>
+      <c r="Q64">
+        <v>3.564897994666673</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1453667034102912</v>
+      </c>
+      <c r="T64">
+        <v>1.825514992504894</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.1171914930924236</v>
+      </c>
+      <c r="W64">
+        <v>0.184330416242302</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5580547290115412</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1712242053661379</v>
+      </c>
+      <c r="C65">
+        <v>-193.2215879295833</v>
+      </c>
+      <c r="D65">
+        <v>215.6924120704167</v>
+      </c>
+      <c r="E65">
+        <v>-64.98599999999999</v>
+      </c>
+      <c r="F65">
+        <v>427.014</v>
+      </c>
+      <c r="G65">
+        <v>18.1</v>
+      </c>
+      <c r="H65">
+        <v>185.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K65">
+        <v>34.2</v>
+      </c>
+      <c r="L65">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M65">
+        <v>89.1605232</v>
+      </c>
+      <c r="N65">
+        <v>-40.19385653333333</v>
+      </c>
+      <c r="O65">
+        <v>-8.440709871999999</v>
+      </c>
+      <c r="P65">
+        <v>-31.75314666133333</v>
+      </c>
+      <c r="Q65">
+        <v>2.446853338666671</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1482468845835423</v>
+      </c>
+      <c r="T65">
+        <v>1.874853235545566</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.1153313106623852</v>
+      </c>
+      <c r="W65">
+        <v>0.184718822333694</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5491967174399294</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1729242053661379</v>
+      </c>
+      <c r="C66">
+        <v>-202.7334501695775</v>
+      </c>
+      <c r="D66">
+        <v>212.9585498304224</v>
+      </c>
+      <c r="E66">
+        <v>-58.20799999999997</v>
+      </c>
+      <c r="F66">
+        <v>433.792</v>
+      </c>
+      <c r="G66">
+        <v>18.1</v>
+      </c>
+      <c r="H66">
+        <v>185.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K66">
+        <v>34.2</v>
+      </c>
+      <c r="L66">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M66">
+        <v>90.5757696</v>
+      </c>
+      <c r="N66">
+        <v>-41.60910293333333</v>
+      </c>
+      <c r="O66">
+        <v>-8.737911616</v>
+      </c>
+      <c r="P66">
+        <v>-32.87119131733333</v>
+      </c>
+      <c r="Q66">
+        <v>1.328808682666669</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1512870758219741</v>
+      </c>
+      <c r="T66">
+        <v>1.926932492088499</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1135292589332854</v>
+      </c>
+      <c r="W66">
+        <v>0.18509509073473</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5406155187299304</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1746242053661379</v>
+      </c>
+      <c r="C67">
+        <v>-212.1768773939504</v>
+      </c>
+      <c r="D67">
+        <v>210.2931226060496</v>
+      </c>
+      <c r="E67">
+        <v>-51.42999999999995</v>
+      </c>
+      <c r="F67">
+        <v>440.57</v>
+      </c>
+      <c r="G67">
+        <v>18.1</v>
+      </c>
+      <c r="H67">
+        <v>185.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K67">
+        <v>34.2</v>
+      </c>
+      <c r="L67">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M67">
+        <v>91.991016</v>
+      </c>
+      <c r="N67">
+        <v>-43.02434933333333</v>
+      </c>
+      <c r="O67">
+        <v>-9.03511336</v>
+      </c>
+      <c r="P67">
+        <v>-33.98923597333334</v>
+      </c>
+      <c r="Q67">
+        <v>0.2107640266666664</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1545009922740305</v>
+      </c>
+      <c r="T67">
+        <v>1.981987706148171</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1117826549496964</v>
+      </c>
+      <c r="W67">
+        <v>0.1854597816465034</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5322983569033162</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1763242053661379</v>
+      </c>
+      <c r="C68">
+        <v>-221.5544074728809</v>
+      </c>
+      <c r="D68">
+        <v>207.6935925271191</v>
+      </c>
+      <c r="E68">
+        <v>-44.65199999999993</v>
+      </c>
+      <c r="F68">
+        <v>447.348</v>
+      </c>
+      <c r="G68">
+        <v>18.1</v>
+      </c>
+      <c r="H68">
+        <v>185.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K68">
+        <v>34.2</v>
+      </c>
+      <c r="L68">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M68">
+        <v>93.4062624</v>
+      </c>
+      <c r="N68">
+        <v>-44.43959573333333</v>
+      </c>
+      <c r="O68">
+        <v>-9.332315103999999</v>
+      </c>
+      <c r="P68">
+        <v>-35.10728062933333</v>
+      </c>
+      <c r="Q68">
+        <v>-0.9072806293333286</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1579039626350314</v>
+      </c>
+      <c r="T68">
+        <v>2.040281462211352</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1100889783595495</v>
+      </c>
+      <c r="W68">
+        <v>0.1858134213185261</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5242332302835689</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1780242053661379</v>
+      </c>
+      <c r="C69">
+        <v>-230.8684543216854</v>
+      </c>
+      <c r="D69">
+        <v>205.1575456783146</v>
+      </c>
+      <c r="E69">
+        <v>-37.87399999999997</v>
+      </c>
+      <c r="F69">
+        <v>454.126</v>
+      </c>
+      <c r="G69">
+        <v>18.1</v>
+      </c>
+      <c r="H69">
+        <v>185.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K69">
+        <v>34.2</v>
+      </c>
+      <c r="L69">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M69">
+        <v>94.8215088</v>
+      </c>
+      <c r="N69">
+        <v>-45.85484213333334</v>
+      </c>
+      <c r="O69">
+        <v>-9.629516848</v>
+      </c>
+      <c r="P69">
+        <v>-36.22532528533333</v>
+      </c>
+      <c r="Q69">
+        <v>-2.025325285333331</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1615131736239717</v>
+      </c>
+      <c r="T69">
+        <v>2.102108173187454</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1084458592795562</v>
+      </c>
+      <c r="W69">
+        <v>0.1861565045824287</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5164088537121724</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1797242053661379</v>
+      </c>
+      <c r="C70">
+        <v>-240.1213153772932</v>
+      </c>
+      <c r="D70">
+        <v>202.6826846227068</v>
+      </c>
+      <c r="E70">
+        <v>-31.09599999999995</v>
+      </c>
+      <c r="F70">
+        <v>460.904</v>
+      </c>
+      <c r="G70">
+        <v>18.1</v>
+      </c>
+      <c r="H70">
+        <v>185.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K70">
+        <v>34.2</v>
+      </c>
+      <c r="L70">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M70">
+        <v>96.2367552</v>
+      </c>
+      <c r="N70">
+        <v>-47.27008853333334</v>
+      </c>
+      <c r="O70">
+        <v>-9.926718592</v>
+      </c>
+      <c r="P70">
+        <v>-37.34336994133334</v>
+      </c>
+      <c r="Q70">
+        <v>-3.143369941333333</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1653479602997208</v>
+      </c>
+      <c r="T70">
+        <v>2.167799053599562</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.1068510672313274</v>
+      </c>
+      <c r="W70">
+        <v>0.1864894971620988</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5088146058634639</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1814242053661379</v>
+      </c>
+      <c r="C71">
+        <v>-249.3151785400296</v>
+      </c>
+      <c r="D71">
+        <v>200.2668214599704</v>
+      </c>
+      <c r="E71">
+        <v>-24.31799999999993</v>
+      </c>
+      <c r="F71">
+        <v>467.682</v>
+      </c>
+      <c r="G71">
+        <v>18.1</v>
+      </c>
+      <c r="H71">
+        <v>185.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K71">
+        <v>34.2</v>
+      </c>
+      <c r="L71">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M71">
+        <v>97.65200160000001</v>
+      </c>
+      <c r="N71">
+        <v>-48.68533493333334</v>
+      </c>
+      <c r="O71">
+        <v>-10.223920336</v>
+      </c>
+      <c r="P71">
+        <v>-38.46141459733334</v>
+      </c>
+      <c r="Q71">
+        <v>-4.261414597333335</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1694301525674538</v>
+      </c>
+      <c r="T71">
+        <v>2.23772805532858</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.1053025010395691</v>
+      </c>
+      <c r="W71">
+        <v>0.186812837782938</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5014404811408051</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.204522808076356</v>
+      </c>
+      <c r="C72">
+        <v>-284.0065587116393</v>
+      </c>
+      <c r="D72">
+        <v>172.3534412883607</v>
+      </c>
+      <c r="E72">
+        <v>-17.53999999999991</v>
+      </c>
+      <c r="F72">
+        <v>474.46</v>
+      </c>
+      <c r="G72">
+        <v>18.1</v>
+      </c>
+      <c r="H72">
+        <v>185.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K72">
+        <v>34.2</v>
+      </c>
+      <c r="L72">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M72">
+        <v>113.301048</v>
+      </c>
+      <c r="N72">
+        <v>-64.33438133333334</v>
+      </c>
+      <c r="O72">
+        <v>-13.51022008</v>
+      </c>
+      <c r="P72">
+        <v>-50.82416125333334</v>
+      </c>
+      <c r="Q72">
+        <v>-16.62416125333333</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1751131666870959</v>
+      </c>
+      <c r="T72">
+        <v>2.335079546423141</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.09075820728507294</v>
+      </c>
+      <c r="W72">
+        <v>0.2171269401003246</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.4321819394527283</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.206522808076356</v>
+      </c>
+      <c r="C73">
+        <v>-292.8397764040344</v>
+      </c>
+      <c r="D73">
+        <v>170.2982235959655</v>
+      </c>
+      <c r="E73">
+        <v>-10.762</v>
+      </c>
+      <c r="F73">
+        <v>481.2379999999999</v>
+      </c>
+      <c r="G73">
+        <v>18.1</v>
+      </c>
+      <c r="H73">
+        <v>185.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K73">
+        <v>34.2</v>
+      </c>
+      <c r="L73">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M73">
+        <v>114.9196344</v>
+      </c>
+      <c r="N73">
+        <v>-65.95296773333332</v>
+      </c>
+      <c r="O73">
+        <v>-13.850123224</v>
+      </c>
+      <c r="P73">
+        <v>-52.10284450933332</v>
+      </c>
+      <c r="Q73">
+        <v>-17.90284450933332</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1798136207107888</v>
+      </c>
+      <c r="T73">
+        <v>2.415599530782559</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.08947992267542404</v>
+      </c>
+      <c r="W73">
+        <v>0.2174321944651088</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4260948698829716</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.208522808076356</v>
+      </c>
+      <c r="C74">
+        <v>-301.6245570545094</v>
+      </c>
+      <c r="D74">
+        <v>168.2914429454906</v>
+      </c>
+      <c r="E74">
+        <v>-3.98399999999998</v>
+      </c>
+      <c r="F74">
+        <v>488.016</v>
+      </c>
+      <c r="G74">
+        <v>18.1</v>
+      </c>
+      <c r="H74">
+        <v>185.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K74">
+        <v>34.2</v>
+      </c>
+      <c r="L74">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M74">
+        <v>116.5382208</v>
+      </c>
+      <c r="N74">
+        <v>-67.57155413333332</v>
+      </c>
+      <c r="O74">
+        <v>-14.190026368</v>
+      </c>
+      <c r="P74">
+        <v>-53.38152776533332</v>
+      </c>
+      <c r="Q74">
+        <v>-19.18152776533332</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1848498214504599</v>
+      </c>
+      <c r="T74">
+        <v>2.501870942596222</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08823714597159871</v>
+      </c>
+      <c r="W74">
+        <v>0.2177289695419822</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4201768855790415</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.210522808076356</v>
+      </c>
+      <c r="C75">
+        <v>-310.3625930547439</v>
+      </c>
+      <c r="D75">
+        <v>166.3314069452561</v>
+      </c>
+      <c r="E75">
+        <v>2.79400000000004</v>
+      </c>
+      <c r="F75">
+        <v>494.794</v>
+      </c>
+      <c r="G75">
+        <v>18.1</v>
+      </c>
+      <c r="H75">
+        <v>185.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K75">
+        <v>34.2</v>
+      </c>
+      <c r="L75">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M75">
+        <v>118.1568072</v>
+      </c>
+      <c r="N75">
+        <v>-69.19014053333333</v>
+      </c>
+      <c r="O75">
+        <v>-14.529929512</v>
+      </c>
+      <c r="P75">
+        <v>-54.66021102133334</v>
+      </c>
+      <c r="Q75">
+        <v>-20.46021102133334</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1902590740967732</v>
+      </c>
+      <c r="T75">
+        <v>2.594532829359045</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.0870284179445905</v>
+      </c>
+      <c r="W75">
+        <v>0.2180176137948318</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4144210378313833</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.212522808076356</v>
+      </c>
+      <c r="C76">
+        <v>-319.0554988611494</v>
+      </c>
+      <c r="D76">
+        <v>164.4165011388506</v>
+      </c>
+      <c r="E76">
+        <v>9.572000000000003</v>
+      </c>
+      <c r="F76">
+        <v>501.5719999999999</v>
+      </c>
+      <c r="G76">
+        <v>18.1</v>
+      </c>
+      <c r="H76">
+        <v>185.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K76">
+        <v>34.2</v>
+      </c>
+      <c r="L76">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M76">
+        <v>119.7753936</v>
+      </c>
+      <c r="N76">
+        <v>-70.80872693333332</v>
+      </c>
+      <c r="O76">
+        <v>-14.869832656</v>
+      </c>
+      <c r="P76">
+        <v>-55.93889427733332</v>
+      </c>
+      <c r="Q76">
+        <v>-21.73889427733332</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1960844231004953</v>
+      </c>
+      <c r="T76">
+        <v>2.694322553565162</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.08585235824263658</v>
+      </c>
+      <c r="W76">
+        <v>0.2182984568516584</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4088207535363647</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.214522808076356</v>
+      </c>
+      <c r="C77">
+        <v>-327.704815429997</v>
+      </c>
+      <c r="D77">
+        <v>162.545184570003</v>
+      </c>
+      <c r="E77">
+        <v>16.35000000000002</v>
+      </c>
+      <c r="F77">
+        <v>508.35</v>
+      </c>
+      <c r="G77">
+        <v>18.1</v>
+      </c>
+      <c r="H77">
+        <v>185.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K77">
+        <v>34.2</v>
+      </c>
+      <c r="L77">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M77">
+        <v>121.39398</v>
+      </c>
+      <c r="N77">
+        <v>-72.42731333333333</v>
+      </c>
+      <c r="O77">
+        <v>-15.2097358</v>
+      </c>
+      <c r="P77">
+        <v>-57.21757753333333</v>
+      </c>
+      <c r="Q77">
+        <v>-23.01757753333333</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2023758000245151</v>
+      </c>
+      <c r="T77">
+        <v>2.802095455707769</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.08470766013273476</v>
+      </c>
+      <c r="W77">
+        <v>0.2185718107603029</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.4033698101558798</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.216522808076356</v>
+      </c>
+      <c r="C78">
+        <v>-336.312014353077</v>
+      </c>
+      <c r="D78">
+        <v>160.715985646923</v>
+      </c>
+      <c r="E78">
+        <v>23.12799999999999</v>
+      </c>
+      <c r="F78">
+        <v>515.1279999999999</v>
+      </c>
+      <c r="G78">
+        <v>18.1</v>
+      </c>
+      <c r="H78">
+        <v>185.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K78">
+        <v>34.2</v>
+      </c>
+      <c r="L78">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M78">
+        <v>123.0125664</v>
+      </c>
+      <c r="N78">
+        <v>-74.04589973333331</v>
+      </c>
+      <c r="O78">
+        <v>-15.549638944</v>
+      </c>
+      <c r="P78">
+        <v>-58.49626078933332</v>
+      </c>
+      <c r="Q78">
+        <v>-24.29626078933332</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2091914583588699</v>
+      </c>
+      <c r="T78">
+        <v>2.918849433028926</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.08359308565730404</v>
+      </c>
+      <c r="W78">
+        <v>0.2188379711450358</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3980623126538289</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.218522808076356</v>
+      </c>
+      <c r="C79">
+        <v>-344.8785017172254</v>
+      </c>
+      <c r="D79">
+        <v>158.9274982827745</v>
+      </c>
+      <c r="E79">
+        <v>29.90600000000001</v>
+      </c>
+      <c r="F79">
+        <v>521.9059999999999</v>
+      </c>
+      <c r="G79">
+        <v>18.1</v>
+      </c>
+      <c r="H79">
+        <v>185.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K79">
+        <v>34.2</v>
+      </c>
+      <c r="L79">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M79">
+        <v>124.6311528</v>
+      </c>
+      <c r="N79">
+        <v>-75.66448613333333</v>
+      </c>
+      <c r="O79">
+        <v>-15.889542088</v>
+      </c>
+      <c r="P79">
+        <v>-59.77494404533333</v>
+      </c>
+      <c r="Q79">
+        <v>-25.57494404533332</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2165997826353425</v>
+      </c>
+      <c r="T79">
+        <v>3.04575593011714</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.08250746116824814</v>
+      </c>
+      <c r="W79">
+        <v>0.2190972182730224</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3928926722297531</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.220522808076356</v>
+      </c>
+      <c r="C80">
+        <v>-353.4056217089878</v>
+      </c>
+      <c r="D80">
+        <v>157.1783782910122</v>
+      </c>
+      <c r="E80">
+        <v>36.68400000000003</v>
+      </c>
+      <c r="F80">
+        <v>528.684</v>
+      </c>
+      <c r="G80">
+        <v>18.1</v>
+      </c>
+      <c r="H80">
+        <v>185.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K80">
+        <v>34.2</v>
+      </c>
+      <c r="L80">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M80">
+        <v>126.2497392</v>
+      </c>
+      <c r="N80">
+        <v>-77.28307253333332</v>
+      </c>
+      <c r="O80">
+        <v>-16.229445232</v>
+      </c>
+      <c r="P80">
+        <v>-61.05362730133333</v>
+      </c>
+      <c r="Q80">
+        <v>-26.85362730133333</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.224681590936949</v>
+      </c>
+      <c r="T80">
+        <v>3.184199381486101</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.08144967320455265</v>
+      </c>
+      <c r="W80">
+        <v>0.2193498180387528</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.387855586688346</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.222522808076356</v>
+      </c>
+      <c r="C81">
+        <v>-361.8946599838403</v>
+      </c>
+      <c r="D81">
+        <v>155.4673400161597</v>
+      </c>
+      <c r="E81">
+        <v>43.46200000000005</v>
+      </c>
+      <c r="F81">
+        <v>535.462</v>
+      </c>
+      <c r="G81">
+        <v>18.1</v>
+      </c>
+      <c r="H81">
+        <v>185.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K81">
+        <v>34.2</v>
+      </c>
+      <c r="L81">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M81">
+        <v>127.8683256</v>
+      </c>
+      <c r="N81">
+        <v>-78.90165893333334</v>
+      </c>
+      <c r="O81">
+        <v>-16.569348376</v>
+      </c>
+      <c r="P81">
+        <v>-62.33231055733334</v>
+      </c>
+      <c r="Q81">
+        <v>-28.13231055733333</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2335330952672799</v>
+      </c>
+      <c r="T81">
+        <v>3.33582792346163</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.08041866468297602</v>
+      </c>
+      <c r="W81">
+        <v>0.2195960228737054</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3829460222998858</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.224522808076356</v>
+      </c>
+      <c r="C82">
+        <v>-370.3468468177185</v>
+      </c>
+      <c r="D82">
+        <v>153.7931531822815</v>
+      </c>
+      <c r="E82">
+        <v>50.24000000000007</v>
+      </c>
+      <c r="F82">
+        <v>542.24</v>
+      </c>
+      <c r="G82">
+        <v>18.1</v>
+      </c>
+      <c r="H82">
+        <v>185.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K82">
+        <v>34.2</v>
+      </c>
+      <c r="L82">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M82">
+        <v>129.486912</v>
+      </c>
+      <c r="N82">
+        <v>-80.52024533333335</v>
+      </c>
+      <c r="O82">
+        <v>-16.90925152</v>
+      </c>
+      <c r="P82">
+        <v>-63.61099381333335</v>
+      </c>
+      <c r="Q82">
+        <v>-29.41099381333335</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2432697500306439</v>
+      </c>
+      <c r="T82">
+        <v>3.502619319634712</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07941343137443882</v>
+      </c>
+      <c r="W82">
+        <v>0.219836072587784</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3781591970211372</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.226522808076356</v>
+      </c>
+      <c r="C83">
+        <v>-378.7633600570872</v>
+      </c>
+      <c r="D83">
+        <v>152.1546399429129</v>
+      </c>
+      <c r="E83">
+        <v>57.01800000000009</v>
+      </c>
+      <c r="F83">
+        <v>549.018</v>
+      </c>
+      <c r="G83">
+        <v>18.1</v>
+      </c>
+      <c r="H83">
+        <v>185.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K83">
+        <v>34.2</v>
+      </c>
+      <c r="L83">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M83">
+        <v>131.1054984</v>
+      </c>
+      <c r="N83">
+        <v>-82.13883173333335</v>
+      </c>
+      <c r="O83">
+        <v>-17.249154664</v>
+      </c>
+      <c r="P83">
+        <v>-64.88967706933335</v>
+      </c>
+      <c r="Q83">
+        <v>-30.68967706933334</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2540313158217304</v>
+      </c>
+      <c r="T83">
+        <v>3.686967704878644</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07843301864142106</v>
+      </c>
+      <c r="W83">
+        <v>0.2200701951484287</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3734905649591479</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.228522808076356</v>
+      </c>
+      <c r="C84">
+        <v>-387.1453278824176</v>
+      </c>
+      <c r="D84">
+        <v>150.5506721175824</v>
+      </c>
+      <c r="E84">
+        <v>63.79600000000011</v>
+      </c>
+      <c r="F84">
+        <v>555.796</v>
+      </c>
+      <c r="G84">
+        <v>18.1</v>
+      </c>
+      <c r="H84">
+        <v>185.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K84">
+        <v>34.2</v>
+      </c>
+      <c r="L84">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M84">
+        <v>132.7240848</v>
+      </c>
+      <c r="N84">
+        <v>-83.75741813333335</v>
+      </c>
+      <c r="O84">
+        <v>-17.589057808</v>
+      </c>
+      <c r="P84">
+        <v>-66.16836032533334</v>
+      </c>
+      <c r="Q84">
+        <v>-31.96836032533334</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2659886111451599</v>
+      </c>
+      <c r="T84">
+        <v>3.891799244038569</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.07747651841408665</v>
+      </c>
+      <c r="W84">
+        <v>0.2202986074027161</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3689358019718413</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.230522808076356</v>
+      </c>
+      <c r="C85">
+        <v>-395.4938313986985</v>
+      </c>
+      <c r="D85">
+        <v>148.9801686013014</v>
+      </c>
+      <c r="E85">
+        <v>70.57400000000001</v>
+      </c>
+      <c r="F85">
+        <v>562.574</v>
+      </c>
+      <c r="G85">
+        <v>18.1</v>
+      </c>
+      <c r="H85">
+        <v>185.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K85">
+        <v>34.2</v>
+      </c>
+      <c r="L85">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M85">
+        <v>134.3426712</v>
+      </c>
+      <c r="N85">
+        <v>-85.37600453333332</v>
+      </c>
+      <c r="O85">
+        <v>-17.928960952</v>
+      </c>
+      <c r="P85">
+        <v>-67.44704358133332</v>
+      </c>
+      <c r="Q85">
+        <v>-33.24704358133332</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2793526470948752</v>
+      </c>
+      <c r="T85">
+        <v>4.120728611334956</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07654306638500129</v>
+      </c>
+      <c r="W85">
+        <v>0.2205215157472617</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.36449079230953</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.232522808076356</v>
+      </c>
+      <c r="C86">
+        <v>-403.8099070654788</v>
+      </c>
+      <c r="D86">
+        <v>147.4420929345212</v>
+      </c>
+      <c r="E86">
+        <v>77.35200000000003</v>
+      </c>
+      <c r="F86">
+        <v>569.352</v>
+      </c>
+      <c r="G86">
+        <v>18.1</v>
+      </c>
+      <c r="H86">
+        <v>185.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K86">
+        <v>34.2</v>
+      </c>
+      <c r="L86">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M86">
+        <v>135.9612576</v>
+      </c>
+      <c r="N86">
+        <v>-86.99459093333334</v>
+      </c>
+      <c r="O86">
+        <v>-18.268864096</v>
+      </c>
+      <c r="P86">
+        <v>-68.72572683733334</v>
+      </c>
+      <c r="Q86">
+        <v>-34.52572683733334</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2943871875383048</v>
+      </c>
+      <c r="T86">
+        <v>4.378274149543389</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07563183940422745</v>
+      </c>
+      <c r="W86">
+        <v>0.2207391167502705</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.360151616210607</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.234522808076356</v>
+      </c>
+      <c r="C87">
+        <v>-412.0945489779226</v>
+      </c>
+      <c r="D87">
+        <v>145.9354510220774</v>
+      </c>
+      <c r="E87">
+        <v>84.13000000000005</v>
+      </c>
+      <c r="F87">
+        <v>576.13</v>
+      </c>
+      <c r="G87">
+        <v>18.1</v>
+      </c>
+      <c r="H87">
+        <v>185.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K87">
+        <v>34.2</v>
+      </c>
+      <c r="L87">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M87">
+        <v>137.579844</v>
+      </c>
+      <c r="N87">
+        <v>-88.61317733333334</v>
+      </c>
+      <c r="O87">
+        <v>-18.60876724</v>
+      </c>
+      <c r="P87">
+        <v>-70.00441009333333</v>
+      </c>
+      <c r="Q87">
+        <v>-35.80441009333333</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3114263333741917</v>
+      </c>
+      <c r="T87">
+        <v>4.670159092846281</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.07474205305829537</v>
+      </c>
+      <c r="W87">
+        <v>0.2209515977296791</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.355914538372835</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.236522808076356</v>
+      </c>
+      <c r="C88">
+        <v>-420.3487110094239</v>
+      </c>
+      <c r="D88">
+        <v>144.459288990576</v>
+      </c>
+      <c r="E88">
+        <v>90.90799999999996</v>
+      </c>
+      <c r="F88">
+        <v>582.9079999999999</v>
+      </c>
+      <c r="G88">
+        <v>18.1</v>
+      </c>
+      <c r="H88">
+        <v>185.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K88">
+        <v>34.2</v>
+      </c>
+      <c r="L88">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M88">
+        <v>139.1984304</v>
+      </c>
+      <c r="N88">
+        <v>-90.23176373333331</v>
+      </c>
+      <c r="O88">
+        <v>-18.94867038399999</v>
+      </c>
+      <c r="P88">
+        <v>-71.28309334933331</v>
+      </c>
+      <c r="Q88">
+        <v>-37.08309334933331</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3308996429009197</v>
+      </c>
+      <c r="T88">
+        <v>5.003741885192444</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07387295941808264</v>
+      </c>
+      <c r="W88">
+        <v>0.2211591372909619</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.351775997228965</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.238522808076356</v>
+      </c>
+      <c r="C89">
+        <v>-428.5733088254866</v>
+      </c>
+      <c r="D89">
+        <v>143.0126911745133</v>
+      </c>
+      <c r="E89">
+        <v>97.68599999999998</v>
+      </c>
+      <c r="F89">
+        <v>589.6859999999999</v>
+      </c>
+      <c r="G89">
+        <v>18.1</v>
+      </c>
+      <c r="H89">
+        <v>185.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K89">
+        <v>34.2</v>
+      </c>
+      <c r="L89">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M89">
+        <v>140.8170168</v>
+      </c>
+      <c r="N89">
+        <v>-91.85035013333331</v>
+      </c>
+      <c r="O89">
+        <v>-19.28857352799999</v>
+      </c>
+      <c r="P89">
+        <v>-72.56177660533331</v>
+      </c>
+      <c r="Q89">
+        <v>-38.3617766053333</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3533688462009905</v>
+      </c>
+      <c r="T89">
+        <v>5.388645107130325</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.07302384494201274</v>
+      </c>
+      <c r="W89">
+        <v>0.2213619058278474</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3477325949619654</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.240522808076356</v>
+      </c>
+      <c r="C90">
+        <v>-436.7692217778026</v>
+      </c>
+      <c r="D90">
+        <v>141.5947782221973</v>
+      </c>
+      <c r="E90">
+        <v>104.464</v>
+      </c>
+      <c r="F90">
+        <v>596.4639999999999</v>
+      </c>
+      <c r="G90">
+        <v>18.1</v>
+      </c>
+      <c r="H90">
+        <v>185.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K90">
+        <v>34.2</v>
+      </c>
+      <c r="L90">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M90">
+        <v>142.4356032</v>
+      </c>
+      <c r="N90">
+        <v>-93.46893653333333</v>
+      </c>
+      <c r="O90">
+        <v>-19.628476672</v>
+      </c>
+      <c r="P90">
+        <v>-73.84045986133333</v>
+      </c>
+      <c r="Q90">
+        <v>-39.64045986133333</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3795829167177398</v>
+      </c>
+      <c r="T90">
+        <v>5.837698866057853</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.07219402852221712</v>
+      </c>
+      <c r="W90">
+        <v>0.2215600659888946</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3437810882010339</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.242522808076356</v>
+      </c>
+      <c r="C91">
+        <v>-444.9372946867636</v>
+      </c>
+      <c r="D91">
+        <v>140.2047053132364</v>
+      </c>
+      <c r="E91">
+        <v>111.242</v>
+      </c>
+      <c r="F91">
+        <v>603.242</v>
+      </c>
+      <c r="G91">
+        <v>18.1</v>
+      </c>
+      <c r="H91">
+        <v>185.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K91">
+        <v>34.2</v>
+      </c>
+      <c r="L91">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M91">
+        <v>144.0541896</v>
+      </c>
+      <c r="N91">
+        <v>-95.08752293333333</v>
+      </c>
+      <c r="O91">
+        <v>-19.968379816</v>
+      </c>
+      <c r="P91">
+        <v>-75.11914311733334</v>
+      </c>
+      <c r="Q91">
+        <v>-40.91914311733333</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.410563181873898</v>
+      </c>
+      <c r="T91">
+        <v>6.368398762972203</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.07138285966241693</v>
+      </c>
+      <c r="W91">
+        <v>0.2217537731126148</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3399183793448425</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.244522808076356</v>
+      </c>
+      <c r="C92">
+        <v>-453.0783395199957</v>
+      </c>
+      <c r="D92">
+        <v>138.8416604800043</v>
+      </c>
+      <c r="E92">
+        <v>118.02</v>
+      </c>
+      <c r="F92">
+        <v>610.02</v>
+      </c>
+      <c r="G92">
+        <v>18.1</v>
+      </c>
+      <c r="H92">
+        <v>185.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K92">
+        <v>34.2</v>
+      </c>
+      <c r="L92">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M92">
+        <v>145.672776</v>
+      </c>
+      <c r="N92">
+        <v>-96.70610933333333</v>
+      </c>
+      <c r="O92">
+        <v>-20.30828296</v>
+      </c>
+      <c r="P92">
+        <v>-76.39782637333333</v>
+      </c>
+      <c r="Q92">
+        <v>-42.19782637333333</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4477395000612878</v>
+      </c>
+      <c r="T92">
+        <v>7.005238639269423</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.07058971677727896</v>
+      </c>
+      <c r="W92">
+        <v>0.2219431756335858</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3361415084632332</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.246522808076356</v>
+      </c>
+      <c r="C93">
+        <v>-461.1931369739275</v>
+      </c>
+      <c r="D93">
+        <v>137.5048630260725</v>
+      </c>
+      <c r="E93">
+        <v>124.7980000000001</v>
+      </c>
+      <c r="F93">
+        <v>616.798</v>
+      </c>
+      <c r="G93">
+        <v>18.1</v>
+      </c>
+      <c r="H93">
+        <v>185.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K93">
+        <v>34.2</v>
+      </c>
+      <c r="L93">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M93">
+        <v>147.2913624</v>
+      </c>
+      <c r="N93">
+        <v>-98.32469573333333</v>
+      </c>
+      <c r="O93">
+        <v>-20.648186104</v>
+      </c>
+      <c r="P93">
+        <v>-77.67650962933334</v>
+      </c>
+      <c r="Q93">
+        <v>-43.47650962933334</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4931772222903198</v>
+      </c>
+      <c r="T93">
+        <v>7.783598488077138</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06981400560390226</v>
+      </c>
+      <c r="W93">
+        <v>0.2221284154617882</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.332447645732868</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.248522808076356</v>
+      </c>
+      <c r="C94">
+        <v>-469.2824379648622</v>
+      </c>
+      <c r="D94">
+        <v>136.1935620351378</v>
+      </c>
+      <c r="E94">
+        <v>131.5760000000001</v>
+      </c>
+      <c r="F94">
+        <v>623.576</v>
+      </c>
+      <c r="G94">
+        <v>18.1</v>
+      </c>
+      <c r="H94">
+        <v>185.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K94">
+        <v>34.2</v>
+      </c>
+      <c r="L94">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M94">
+        <v>148.9099488</v>
+      </c>
+      <c r="N94">
+        <v>-99.94328213333335</v>
+      </c>
+      <c r="O94">
+        <v>-20.988089248</v>
+      </c>
+      <c r="P94">
+        <v>-78.95519288533335</v>
+      </c>
+      <c r="Q94">
+        <v>-44.75519288533334</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.54997437507661</v>
+      </c>
+      <c r="T94">
+        <v>8.756548299086782</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06905515771690332</v>
+      </c>
+      <c r="W94">
+        <v>0.2223096283372035</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3288340843662063</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.250522808076356</v>
+      </c>
+      <c r="C95">
+        <v>-477.3469650355407</v>
+      </c>
+      <c r="D95">
+        <v>134.9070349644594</v>
+      </c>
+      <c r="E95">
+        <v>138.3540000000001</v>
+      </c>
+      <c r="F95">
+        <v>630.354</v>
+      </c>
+      <c r="G95">
+        <v>18.1</v>
+      </c>
+      <c r="H95">
+        <v>185.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K95">
+        <v>34.2</v>
+      </c>
+      <c r="L95">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M95">
+        <v>150.5285352</v>
+      </c>
+      <c r="N95">
+        <v>-101.5618685333334</v>
+      </c>
+      <c r="O95">
+        <v>-21.327992392</v>
+      </c>
+      <c r="P95">
+        <v>-80.23387614133335</v>
+      </c>
+      <c r="Q95">
+        <v>-46.03387614133335</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6229992858018398</v>
+      </c>
+      <c r="T95">
+        <v>10.00748377038489</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06831262913930222</v>
+      </c>
+      <c r="W95">
+        <v>0.2224869441615346</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3252982339966772</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.252522808076356</v>
+      </c>
+      <c r="C96">
+        <v>-485.3874136827272</v>
+      </c>
+      <c r="D96">
+        <v>133.6445863172727</v>
+      </c>
+      <c r="E96">
+        <v>145.132</v>
+      </c>
+      <c r="F96">
+        <v>637.1319999999999</v>
+      </c>
+      <c r="G96">
+        <v>18.1</v>
+      </c>
+      <c r="H96">
+        <v>185.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K96">
+        <v>34.2</v>
+      </c>
+      <c r="L96">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M96">
+        <v>152.1471216</v>
+      </c>
+      <c r="N96">
+        <v>-103.1804549333333</v>
+      </c>
+      <c r="O96">
+        <v>-21.667895536</v>
+      </c>
+      <c r="P96">
+        <v>-81.51255939733332</v>
+      </c>
+      <c r="Q96">
+        <v>-47.31255939733332</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7203658334354801</v>
+      </c>
+      <c r="T96">
+        <v>11.67539773211572</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06758589904207561</v>
+      </c>
+      <c r="W96">
+        <v>0.2226604873087524</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3218376144860743</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.254522808076356</v>
+      </c>
+      <c r="C97">
+        <v>-493.4044536109481</v>
+      </c>
+      <c r="D97">
+        <v>132.4055463890519</v>
+      </c>
+      <c r="E97">
+        <v>151.91</v>
+      </c>
+      <c r="F97">
+        <v>643.91</v>
+      </c>
+      <c r="G97">
+        <v>18.1</v>
+      </c>
+      <c r="H97">
+        <v>185.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K97">
+        <v>34.2</v>
+      </c>
+      <c r="L97">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M97">
+        <v>153.765708</v>
+      </c>
+      <c r="N97">
+        <v>-104.7990413333333</v>
+      </c>
+      <c r="O97">
+        <v>-22.00779868</v>
+      </c>
+      <c r="P97">
+        <v>-82.79124265333333</v>
+      </c>
+      <c r="Q97">
+        <v>-48.59124265333332</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8566790001225764</v>
+      </c>
+      <c r="T97">
+        <v>14.01047727853886</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06687446852584324</v>
+      </c>
+      <c r="W97">
+        <v>0.2228303769160286</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.318449850123063</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.256522808076356</v>
+      </c>
+      <c r="C98">
+        <v>-501.3987299171275</v>
+      </c>
+      <c r="D98">
+        <v>131.1892700828725</v>
+      </c>
+      <c r="E98">
+        <v>158.688</v>
+      </c>
+      <c r="F98">
+        <v>650.688</v>
+      </c>
+      <c r="G98">
+        <v>18.1</v>
+      </c>
+      <c r="H98">
+        <v>185.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K98">
+        <v>34.2</v>
+      </c>
+      <c r="L98">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M98">
+        <v>155.3842944</v>
+      </c>
+      <c r="N98">
+        <v>-106.4176277333333</v>
+      </c>
+      <c r="O98">
+        <v>-22.347701824</v>
+      </c>
+      <c r="P98">
+        <v>-84.06992590933335</v>
+      </c>
+      <c r="Q98">
+        <v>-49.86992590933335</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.061148750153218</v>
+      </c>
+      <c r="T98">
+        <v>17.51309659817354</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06617785947869902</v>
+      </c>
+      <c r="W98">
+        <v>0.2229967271564867</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3151326641842811</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.258522808076356</v>
+      </c>
+      <c r="C99">
+        <v>-509.3708642105257</v>
+      </c>
+      <c r="D99">
+        <v>129.9951357894742</v>
+      </c>
+      <c r="E99">
+        <v>165.466</v>
+      </c>
+      <c r="F99">
+        <v>657.4659999999999</v>
+      </c>
+      <c r="G99">
+        <v>18.1</v>
+      </c>
+      <c r="H99">
+        <v>185.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K99">
+        <v>34.2</v>
+      </c>
+      <c r="L99">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M99">
+        <v>157.0028808</v>
+      </c>
+      <c r="N99">
+        <v>-108.0362141333333</v>
+      </c>
+      <c r="O99">
+        <v>-22.687604968</v>
+      </c>
+      <c r="P99">
+        <v>-85.34860916533333</v>
+      </c>
+      <c r="Q99">
+        <v>-51.14860916533333</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.401931666870958</v>
+      </c>
+      <c r="T99">
+        <v>23.35079546423139</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06549561350469182</v>
+      </c>
+      <c r="W99">
+        <v>0.2231596474950796</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3118838738318659</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.260522808076356</v>
+      </c>
+      <c r="C100">
+        <v>-517.3214556720654</v>
+      </c>
+      <c r="D100">
+        <v>128.8225443279345</v>
+      </c>
+      <c r="E100">
+        <v>172.244</v>
+      </c>
+      <c r="F100">
+        <v>664.2439999999999</v>
+      </c>
+      <c r="G100">
+        <v>18.1</v>
+      </c>
+      <c r="H100">
+        <v>185.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K100">
+        <v>34.2</v>
+      </c>
+      <c r="L100">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M100">
+        <v>158.6214672</v>
+      </c>
+      <c r="N100">
+        <v>-109.6548005333333</v>
+      </c>
+      <c r="O100">
+        <v>-23.027508112</v>
+      </c>
+      <c r="P100">
+        <v>-86.62729242133332</v>
+      </c>
+      <c r="Q100">
+        <v>-52.42729242133332</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.083497500306437</v>
+      </c>
+      <c r="T100">
+        <v>35.02619319634708</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06482729091790926</v>
+      </c>
+      <c r="W100">
+        <v>0.2233192429288033</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3087013853233774</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.262522808076356</v>
+      </c>
+      <c r="C101">
+        <v>-525.2510820568368</v>
+      </c>
+      <c r="D101">
+        <v>127.6709179431631</v>
+      </c>
+      <c r="E101">
+        <v>179.022</v>
+      </c>
+      <c r="F101">
+        <v>671.0219999999999</v>
+      </c>
+      <c r="G101">
+        <v>18.1</v>
+      </c>
+      <c r="H101">
+        <v>185.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>83.16666666666667</v>
+      </c>
+      <c r="K101">
+        <v>34.2</v>
+      </c>
+      <c r="L101">
+        <v>48.96666666666667</v>
+      </c>
+      <c r="M101">
+        <v>160.2400536</v>
+      </c>
+      <c r="N101">
+        <v>-111.2733869333333</v>
+      </c>
+      <c r="O101">
+        <v>-23.36741125599999</v>
+      </c>
+      <c r="P101">
+        <v>-87.90597567733332</v>
+      </c>
+      <c r="Q101">
+        <v>-53.70597567733331</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.128195000612873</v>
+      </c>
+      <c r="T101">
+        <v>70.05238639269416</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06417246979752633</v>
+      </c>
+      <c r="W101">
+        <v>0.2234756142123507</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3055831895120302</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/slovakia/slovakia_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/slovakia/slovakia_hotel_gaming.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09016442288214344</v>
+        <v>0.09001062759409094</v>
       </c>
       <c r="C2">
-        <v>745.8173845488693</v>
+        <v>740.8808041407236</v>
       </c>
       <c r="D2">
-        <v>727.1173845488693</v>
+        <v>729.6468041407236</v>
       </c>
       <c r="E2">
-        <v>-476.9</v>
+        <v>-469.434</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.465999999999999</v>
       </c>
       <c r="G2">
         <v>18.7</v>
@@ -1439,28 +1439,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3755397999999999</v>
       </c>
       <c r="N2">
-        <v>53.36666666666667</v>
+        <v>52.99112686666668</v>
       </c>
       <c r="O2">
-        <v>11.207</v>
+        <v>11.128136642</v>
       </c>
       <c r="P2">
-        <v>42.15966666666667</v>
+        <v>41.86299022466667</v>
       </c>
       <c r="Q2">
-        <v>75.45966666666666</v>
+        <v>75.16299022466667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09016442288214344</v>
+        <v>0.09051844201423327</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7540171758400865</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>142.1065534642844</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09001062759409094</v>
+        <v>0.08985683230603844</v>
       </c>
       <c r="C3">
-        <v>740.8808041407236</v>
+        <v>735.9618833233553</v>
       </c>
       <c r="D3">
-        <v>729.6468041407236</v>
+        <v>732.1938833233553</v>
       </c>
       <c r="E3">
-        <v>-469.434</v>
+        <v>-461.968</v>
       </c>
       <c r="F3">
-        <v>7.465999999999999</v>
+        <v>14.932</v>
       </c>
       <c r="G3">
         <v>18.7</v>
@@ -1521,28 +1521,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M3">
-        <v>0.3755397999999999</v>
+        <v>0.7510795999999998</v>
       </c>
       <c r="N3">
-        <v>52.99112686666668</v>
+        <v>52.61558706666668</v>
       </c>
       <c r="O3">
-        <v>11.128136642</v>
+        <v>11.049273284</v>
       </c>
       <c r="P3">
-        <v>41.86299022466667</v>
+        <v>41.56631378266668</v>
       </c>
       <c r="Q3">
-        <v>75.16299022466667</v>
+        <v>74.86631378266668</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09051844201423327</v>
+        <v>0.09087968602656984</v>
       </c>
       <c r="T3">
-        <v>0.7540171758400865</v>
+        <v>0.7601082688590353</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.1065534642844</v>
+        <v>71.05327673214222</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08985683230603844</v>
+        <v>0.08970303701798593</v>
       </c>
       <c r="C4">
-        <v>735.9618833233553</v>
+        <v>731.0608076849633</v>
       </c>
       <c r="D4">
-        <v>732.1938833233553</v>
+        <v>734.7588076849632</v>
       </c>
       <c r="E4">
-        <v>-461.968</v>
+        <v>-454.502</v>
       </c>
       <c r="F4">
-        <v>14.932</v>
+        <v>22.398</v>
       </c>
       <c r="G4">
         <v>18.7</v>
@@ -1603,28 +1603,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M4">
-        <v>0.7510795999999998</v>
+        <v>1.1266194</v>
       </c>
       <c r="N4">
-        <v>52.61558706666668</v>
+        <v>52.24004726666667</v>
       </c>
       <c r="O4">
-        <v>11.049273284</v>
+        <v>10.970409926</v>
       </c>
       <c r="P4">
-        <v>41.56631378266668</v>
+        <v>41.26963734066667</v>
       </c>
       <c r="Q4">
-        <v>74.86631378266668</v>
+        <v>74.56963734066667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09087968602656984</v>
+        <v>0.09124837836905766</v>
       </c>
       <c r="T4">
-        <v>0.7601082688590353</v>
+        <v>0.7663249514247662</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.05327673214222</v>
+        <v>47.36885115476147</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08970303701798593</v>
+        <v>0.08954924172993343</v>
       </c>
       <c r="C5">
-        <v>731.0608076849633</v>
+        <v>726.1777654233987</v>
       </c>
       <c r="D5">
-        <v>734.7588076849632</v>
+        <v>737.3417654233987</v>
       </c>
       <c r="E5">
-        <v>-454.502</v>
+        <v>-447.036</v>
       </c>
       <c r="F5">
-        <v>22.398</v>
+        <v>29.864</v>
       </c>
       <c r="G5">
         <v>18.7</v>
@@ -1685,28 +1685,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M5">
-        <v>1.1266194</v>
+        <v>1.5021592</v>
       </c>
       <c r="N5">
-        <v>52.24004726666667</v>
+        <v>51.86450746666667</v>
       </c>
       <c r="O5">
-        <v>10.970409926</v>
+        <v>10.891546568</v>
       </c>
       <c r="P5">
-        <v>41.26963734066667</v>
+        <v>40.97296089866667</v>
       </c>
       <c r="Q5">
-        <v>74.56963734066667</v>
+        <v>74.27296089866667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09124837836905766</v>
+        <v>0.09162475180201399</v>
       </c>
       <c r="T5">
-        <v>0.7663249514247662</v>
+        <v>0.7726711482106168</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.36885115476147</v>
+        <v>35.52663836607111</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08954924172993343</v>
+        <v>0.08939544644188094</v>
       </c>
       <c r="C6">
-        <v>726.1777654233987</v>
+        <v>721.3129473921992</v>
       </c>
       <c r="D6">
-        <v>737.3417654233987</v>
+        <v>739.9429473921992</v>
       </c>
       <c r="E6">
-        <v>-447.036</v>
+        <v>-439.57</v>
       </c>
       <c r="F6">
-        <v>29.864</v>
+        <v>37.33</v>
       </c>
       <c r="G6">
         <v>18.7</v>
@@ -1767,28 +1767,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M6">
-        <v>1.5021592</v>
+        <v>1.877699</v>
       </c>
       <c r="N6">
-        <v>51.86450746666667</v>
+        <v>51.48896766666667</v>
       </c>
       <c r="O6">
-        <v>10.891546568</v>
+        <v>10.81268321</v>
       </c>
       <c r="P6">
-        <v>40.97296089866667</v>
+        <v>40.67628445666667</v>
       </c>
       <c r="Q6">
-        <v>74.27296089866667</v>
+        <v>73.97628445666666</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09162475180201399</v>
+        <v>0.09200904888619046</v>
       </c>
       <c r="T6">
-        <v>0.7726711482106168</v>
+        <v>0.7791509491393274</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.52663836607111</v>
+        <v>28.42131069285688</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08939544644188094</v>
+        <v>0.08924165115382843</v>
       </c>
       <c r="C7">
-        <v>721.3129473921992</v>
+        <v>716.4665471475961</v>
       </c>
       <c r="D7">
-        <v>739.9429473921992</v>
+        <v>742.5625471475961</v>
       </c>
       <c r="E7">
-        <v>-439.57</v>
+        <v>-432.104</v>
       </c>
       <c r="F7">
-        <v>37.33</v>
+        <v>44.796</v>
       </c>
       <c r="G7">
         <v>18.7</v>
@@ -1849,28 +1849,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M7">
-        <v>1.877699</v>
+        <v>2.2532388</v>
       </c>
       <c r="N7">
-        <v>51.48896766666667</v>
+        <v>51.11342786666668</v>
       </c>
       <c r="O7">
-        <v>10.81268321</v>
+        <v>10.733819852</v>
       </c>
       <c r="P7">
-        <v>40.67628445666667</v>
+        <v>40.37960801466667</v>
       </c>
       <c r="Q7">
-        <v>73.97628445666666</v>
+        <v>73.67960801466667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09200904888619046</v>
+        <v>0.0924015225040728</v>
       </c>
       <c r="T7">
-        <v>0.7791509491393274</v>
+        <v>0.785768618172904</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.42131069285688</v>
+        <v>23.68442557738074</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08924165115382843</v>
+        <v>0.08908785586577593</v>
       </c>
       <c r="C8">
-        <v>716.4665471475962</v>
+        <v>711.6387609965259</v>
       </c>
       <c r="D8">
-        <v>742.5625471475961</v>
+        <v>745.2007609965258</v>
       </c>
       <c r="E8">
-        <v>-432.104</v>
+        <v>-424.638</v>
       </c>
       <c r="F8">
-        <v>44.79599999999999</v>
+        <v>52.26199999999999</v>
       </c>
       <c r="G8">
         <v>18.7</v>
@@ -1931,28 +1931,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M8">
-        <v>2.2532388</v>
+        <v>2.628778599999999</v>
       </c>
       <c r="N8">
-        <v>51.11342786666668</v>
+        <v>50.73788806666668</v>
       </c>
       <c r="O8">
-        <v>10.733819852</v>
+        <v>10.654956494</v>
       </c>
       <c r="P8">
-        <v>40.37960801466667</v>
+        <v>40.08293157266667</v>
       </c>
       <c r="Q8">
-        <v>73.67960801466667</v>
+        <v>73.38293157266668</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0924015225040728</v>
+        <v>0.09280243641481283</v>
       </c>
       <c r="T8">
-        <v>0.785768618172904</v>
+        <v>0.7925286026695684</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.68442557738074</v>
+        <v>20.30093620918349</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08908785586577592</v>
+        <v>0.08893406057772342</v>
       </c>
       <c r="C9">
-        <v>711.6387609965259</v>
+        <v>706.8297880456694</v>
       </c>
       <c r="D9">
-        <v>745.2007609965259</v>
+        <v>747.8577880456693</v>
       </c>
       <c r="E9">
-        <v>-424.638</v>
+        <v>-417.172</v>
       </c>
       <c r="F9">
-        <v>52.262</v>
+        <v>59.72799999999999</v>
       </c>
       <c r="G9">
         <v>18.7</v>
@@ -2013,28 +2013,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M9">
-        <v>2.6287786</v>
+        <v>3.004318399999999</v>
       </c>
       <c r="N9">
-        <v>50.73788806666668</v>
+        <v>50.36234826666667</v>
       </c>
       <c r="O9">
-        <v>10.654956494</v>
+        <v>10.576093136</v>
       </c>
       <c r="P9">
-        <v>40.08293157266667</v>
+        <v>39.78625513066667</v>
       </c>
       <c r="Q9">
-        <v>73.38293157266668</v>
+        <v>73.08625513066667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09280243641481283</v>
+        <v>0.09321206584535155</v>
       </c>
       <c r="T9">
-        <v>0.7925286026695684</v>
+        <v>0.7994355433509428</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.30093620918349</v>
+        <v>17.76331918303555</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08893406057772342</v>
+        <v>0.08878026528967092</v>
       </c>
       <c r="C10">
-        <v>706.8297880456694</v>
+        <v>702.0398302515428</v>
       </c>
       <c r="D10">
-        <v>747.8577880456693</v>
+        <v>750.5338302515427</v>
       </c>
       <c r="E10">
-        <v>-417.172</v>
+        <v>-409.706</v>
       </c>
       <c r="F10">
-        <v>59.72799999999999</v>
+        <v>67.19399999999999</v>
       </c>
       <c r="G10">
         <v>18.7</v>
@@ -2095,28 +2095,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M10">
-        <v>3.004318399999999</v>
+        <v>3.379858199999999</v>
       </c>
       <c r="N10">
-        <v>50.36234826666667</v>
+        <v>49.98680846666667</v>
       </c>
       <c r="O10">
-        <v>10.576093136</v>
+        <v>10.497229778</v>
       </c>
       <c r="P10">
-        <v>39.78625513066667</v>
+        <v>39.48957868866667</v>
       </c>
       <c r="Q10">
-        <v>73.08625513066667</v>
+        <v>72.78957868866667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09321206584535155</v>
+        <v>0.0936306981205175</v>
       </c>
       <c r="T10">
-        <v>0.7994355433509428</v>
+        <v>0.8064942849264134</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.76331918303555</v>
+        <v>15.78961705158716</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08878026528967092</v>
+        <v>0.08862647000161843</v>
       </c>
       <c r="C11">
-        <v>702.0398302515428</v>
+        <v>697.2690924716676</v>
       </c>
       <c r="D11">
-        <v>750.5338302515427</v>
+        <v>753.2290924716675</v>
       </c>
       <c r="E11">
-        <v>-409.706</v>
+        <v>-402.24</v>
       </c>
       <c r="F11">
-        <v>67.19399999999999</v>
+        <v>74.65999999999998</v>
       </c>
       <c r="G11">
         <v>18.7</v>
@@ -2177,28 +2177,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M11">
-        <v>3.379858199999999</v>
+        <v>3.755397999999999</v>
       </c>
       <c r="N11">
-        <v>49.98680846666667</v>
+        <v>49.61126866666667</v>
       </c>
       <c r="O11">
-        <v>10.497229778</v>
+        <v>10.41836642</v>
       </c>
       <c r="P11">
-        <v>39.48957868866667</v>
+        <v>39.19290224666668</v>
       </c>
       <c r="Q11">
-        <v>72.78957868866667</v>
+        <v>72.49290224666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0936306981205175</v>
+        <v>0.09405863333513159</v>
       </c>
       <c r="T11">
-        <v>0.8064942849264134</v>
+        <v>0.8137098874257833</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.78961705158716</v>
+        <v>14.21065534642844</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08862647000161843</v>
+        <v>0.08847267471356592</v>
       </c>
       <c r="C12">
-        <v>697.2690924716676</v>
+        <v>692.5177825168497</v>
       </c>
       <c r="D12">
-        <v>753.2290924716675</v>
+        <v>755.9437825168496</v>
       </c>
       <c r="E12">
-        <v>-402.24</v>
+        <v>-394.774</v>
       </c>
       <c r="F12">
-        <v>74.66</v>
+        <v>82.12599999999999</v>
       </c>
       <c r="G12">
         <v>18.7</v>
@@ -2259,28 +2259,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M12">
-        <v>3.755398</v>
+        <v>4.130937799999999</v>
       </c>
       <c r="N12">
-        <v>49.61126866666667</v>
+        <v>49.23572886666668</v>
       </c>
       <c r="O12">
-        <v>10.41836642</v>
+        <v>10.339503062</v>
       </c>
       <c r="P12">
-        <v>39.19290224666668</v>
+        <v>38.89622580466667</v>
       </c>
       <c r="Q12">
-        <v>72.49290224666667</v>
+        <v>72.19622580466667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09405863333513159</v>
+        <v>0.09449618507142238</v>
       </c>
       <c r="T12">
-        <v>0.8137098874257833</v>
+        <v>0.8210876382959256</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.21065534642844</v>
+        <v>12.91877758766222</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08847267471356592</v>
+        <v>0.08846107942551341</v>
       </c>
       <c r="C13">
-        <v>692.5177825168497</v>
+        <v>685.2572481550337</v>
       </c>
       <c r="D13">
-        <v>755.9437825168496</v>
+        <v>756.1492481550337</v>
       </c>
       <c r="E13">
-        <v>-394.774</v>
+        <v>-387.308</v>
       </c>
       <c r="F13">
-        <v>82.12599999999999</v>
+        <v>89.59199999999998</v>
       </c>
       <c r="G13">
         <v>18.7</v>
@@ -2341,45 +2341,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M13">
-        <v>4.130937799999999</v>
+        <v>4.640865599999999</v>
       </c>
       <c r="N13">
-        <v>49.23572886666668</v>
+        <v>48.72580106666668</v>
       </c>
       <c r="O13">
-        <v>10.339503062</v>
+        <v>10.232418224</v>
       </c>
       <c r="P13">
-        <v>38.89622580466667</v>
+        <v>38.49338284266668</v>
       </c>
       <c r="Q13">
-        <v>72.19622580466667</v>
+        <v>71.79338284266667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09449618507142238</v>
+        <v>0.09494368116535616</v>
       </c>
       <c r="T13">
-        <v>0.8210876382959256</v>
+        <v>0.8286330653222075</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.21</v>
       </c>
       <c r="W13">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>12.91877758766222</v>
+        <v>11.49929156894065</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08846107942551341</v>
+        <v>0.08831913413746093</v>
       </c>
       <c r="C14">
-        <v>685.2572481550337</v>
+        <v>680.3155663241912</v>
       </c>
       <c r="D14">
-        <v>756.1492481550337</v>
+        <v>758.6735663241911</v>
       </c>
       <c r="E14">
-        <v>-387.308</v>
+        <v>-379.842</v>
       </c>
       <c r="F14">
-        <v>89.59199999999998</v>
+        <v>97.05799999999999</v>
       </c>
       <c r="G14">
         <v>18.7</v>
@@ -2423,28 +2423,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M14">
-        <v>4.640865599999999</v>
+        <v>5.0276044</v>
       </c>
       <c r="N14">
-        <v>48.72580106666668</v>
+        <v>48.33906226666667</v>
       </c>
       <c r="O14">
-        <v>10.232418224</v>
+        <v>10.151203076</v>
       </c>
       <c r="P14">
-        <v>38.49338284266668</v>
+        <v>38.18785919066667</v>
       </c>
       <c r="Q14">
-        <v>71.79338284266667</v>
+        <v>71.48785919066667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09494368116535616</v>
+        <v>0.09540146452581716</v>
       </c>
       <c r="T14">
-        <v>0.8286330653222075</v>
+        <v>0.8363519504410477</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.49929156894065</v>
+        <v>10.61473067902214</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08831913413746093</v>
+        <v>0.08817718884940841</v>
       </c>
       <c r="C15">
-        <v>680.3155663241912</v>
+        <v>675.3907952455434</v>
       </c>
       <c r="D15">
-        <v>758.6735663241911</v>
+        <v>761.2147952455433</v>
       </c>
       <c r="E15">
-        <v>-379.842</v>
+        <v>-372.376</v>
       </c>
       <c r="F15">
-        <v>97.05799999999999</v>
+        <v>104.524</v>
       </c>
       <c r="G15">
         <v>18.7</v>
@@ -2505,28 +2505,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M15">
-        <v>5.0276044</v>
+        <v>5.4143432</v>
       </c>
       <c r="N15">
-        <v>48.33906226666667</v>
+        <v>47.95232346666668</v>
       </c>
       <c r="O15">
-        <v>10.151203076</v>
+        <v>10.069987928</v>
       </c>
       <c r="P15">
-        <v>38.18785919066667</v>
+        <v>37.88233553866667</v>
       </c>
       <c r="Q15">
-        <v>71.48785919066667</v>
+        <v>71.18233553866668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09540146452581716</v>
+        <v>0.09586989401094001</v>
       </c>
       <c r="T15">
-        <v>0.8363519504410477</v>
+        <v>0.8442503445161398</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.61473067902214</v>
+        <v>9.856535630520554</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08817718884940841</v>
+        <v>0.08823669356135591</v>
       </c>
       <c r="C16">
-        <v>675.3907952455434</v>
+        <v>666.857420214174</v>
       </c>
       <c r="D16">
-        <v>761.2147952455433</v>
+        <v>760.147420214174</v>
       </c>
       <c r="E16">
-        <v>-372.376</v>
+        <v>-364.91</v>
       </c>
       <c r="F16">
-        <v>104.524</v>
+        <v>111.99</v>
       </c>
       <c r="G16">
         <v>18.7</v>
@@ -2587,45 +2587,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M16">
-        <v>5.4143432</v>
+        <v>5.991465000000001</v>
       </c>
       <c r="N16">
-        <v>47.95232346666668</v>
+        <v>47.37520166666668</v>
       </c>
       <c r="O16">
-        <v>10.069987928</v>
+        <v>9.948792350000002</v>
       </c>
       <c r="P16">
-        <v>37.88233553866667</v>
+        <v>37.42640931666668</v>
       </c>
       <c r="Q16">
-        <v>71.18233553866668</v>
+        <v>70.72640931666668</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09586989401094001</v>
+        <v>0.09634934536630108</v>
       </c>
       <c r="T16">
-        <v>0.8442503445161398</v>
+        <v>0.8523345831577047</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.21</v>
       </c>
       <c r="W16">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.856535630520554</v>
+        <v>8.907114815269166</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08823669356135591</v>
+        <v>0.08810817827330342</v>
       </c>
       <c r="C17">
-        <v>666.857420214174</v>
+        <v>661.7004434020815</v>
       </c>
       <c r="D17">
-        <v>760.147420214174</v>
+        <v>762.4564434020815</v>
       </c>
       <c r="E17">
-        <v>-364.91</v>
+        <v>-357.444</v>
       </c>
       <c r="F17">
-        <v>111.99</v>
+        <v>119.456</v>
       </c>
       <c r="G17">
         <v>18.7</v>
@@ -2669,28 +2669,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M17">
-        <v>5.991464999999999</v>
+        <v>6.390896</v>
       </c>
       <c r="N17">
-        <v>47.37520166666668</v>
+        <v>46.97577066666668</v>
       </c>
       <c r="O17">
-        <v>9.948792350000002</v>
+        <v>9.864911840000001</v>
       </c>
       <c r="P17">
-        <v>37.42640931666668</v>
+        <v>37.11085882666667</v>
       </c>
       <c r="Q17">
-        <v>70.72640931666668</v>
+        <v>70.41085882666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09634934536630108</v>
+        <v>0.09684021223012312</v>
       </c>
       <c r="T17">
-        <v>0.8523345831577047</v>
+        <v>0.8606113036716879</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.907114815269168</v>
+        <v>8.350420139314844</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08810817827330342</v>
+        <v>0.08797966298525092</v>
       </c>
       <c r="C18">
-        <v>661.7004434020815</v>
+        <v>656.5575371045031</v>
       </c>
       <c r="D18">
-        <v>762.4564434020815</v>
+        <v>764.7795371045031</v>
       </c>
       <c r="E18">
-        <v>-357.444</v>
+        <v>-349.978</v>
       </c>
       <c r="F18">
-        <v>119.456</v>
+        <v>126.922</v>
       </c>
       <c r="G18">
         <v>18.7</v>
@@ -2751,28 +2751,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M18">
-        <v>6.390896</v>
+        <v>6.790327</v>
       </c>
       <c r="N18">
-        <v>46.97577066666668</v>
+        <v>46.57633966666668</v>
       </c>
       <c r="O18">
-        <v>9.864911840000001</v>
+        <v>9.781031330000001</v>
       </c>
       <c r="P18">
-        <v>37.11085882666667</v>
+        <v>36.79530833666668</v>
       </c>
       <c r="Q18">
-        <v>70.41085882666667</v>
+        <v>70.09530833666668</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09684021223012312</v>
+        <v>0.09734290721114569</v>
       </c>
       <c r="T18">
-        <v>0.8606113036716879</v>
+        <v>0.8690874632342008</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.350420139314844</v>
+        <v>7.859218954649265</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08797966298525092</v>
+        <v>0.08796490769719842</v>
       </c>
       <c r="C19">
-        <v>656.5575371045031</v>
+        <v>649.3591658740875</v>
       </c>
       <c r="D19">
-        <v>764.7795371045031</v>
+        <v>765.0471658740875</v>
       </c>
       <c r="E19">
-        <v>-349.978</v>
+        <v>-342.5119999999999</v>
       </c>
       <c r="F19">
-        <v>126.922</v>
+        <v>134.388</v>
       </c>
       <c r="G19">
         <v>18.7</v>
@@ -2833,45 +2833,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M19">
-        <v>6.790327</v>
+        <v>7.2972684</v>
       </c>
       <c r="N19">
-        <v>46.57633966666668</v>
+        <v>46.06939826666667</v>
       </c>
       <c r="O19">
-        <v>9.781031330000001</v>
+        <v>9.674573636000002</v>
       </c>
       <c r="P19">
-        <v>36.79530833666668</v>
+        <v>36.39482463066668</v>
       </c>
       <c r="Q19">
-        <v>70.09530833666668</v>
+        <v>69.69482463066667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09734290721114569</v>
+        <v>0.09785786304536392</v>
       </c>
       <c r="T19">
-        <v>0.8690874632342008</v>
+        <v>0.8777703583957993</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.859218954649265</v>
+        <v>7.313238836969005</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08796490769719842</v>
+        <v>0.08784271240914593</v>
       </c>
       <c r="C20">
-        <v>649.3591658740875</v>
+        <v>644.1167416961696</v>
       </c>
       <c r="D20">
-        <v>765.0471658740875</v>
+        <v>767.2707416961695</v>
       </c>
       <c r="E20">
-        <v>-342.512</v>
+        <v>-335.046</v>
       </c>
       <c r="F20">
-        <v>134.388</v>
+        <v>141.854</v>
       </c>
       <c r="G20">
         <v>18.7</v>
@@ -2915,28 +2915,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M20">
-        <v>7.297268399999999</v>
+        <v>7.702672199999999</v>
       </c>
       <c r="N20">
-        <v>46.06939826666667</v>
+        <v>45.66399446666667</v>
       </c>
       <c r="O20">
-        <v>9.674573636000002</v>
+        <v>9.589438838000001</v>
       </c>
       <c r="P20">
-        <v>36.39482463066668</v>
+        <v>36.07455562866667</v>
       </c>
       <c r="Q20">
-        <v>69.69482463066667</v>
+        <v>69.37455562866667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09785786304536392</v>
+        <v>0.09838553383845175</v>
       </c>
       <c r="T20">
-        <v>0.8777703583957993</v>
+        <v>0.8866676460305239</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.313238836969006</v>
+        <v>6.92833152976011</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08784271240914593</v>
+        <v>0.08772051712109342</v>
       </c>
       <c r="C21">
-        <v>644.1167416961696</v>
+        <v>638.8872806449854</v>
       </c>
       <c r="D21">
-        <v>767.2707416961695</v>
+        <v>769.5072806449853</v>
       </c>
       <c r="E21">
-        <v>-335.046</v>
+        <v>-327.58</v>
       </c>
       <c r="F21">
-        <v>141.854</v>
+        <v>149.32</v>
       </c>
       <c r="G21">
         <v>18.7</v>
@@ -2997,28 +2997,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M21">
-        <v>7.702672199999999</v>
+        <v>8.108076000000001</v>
       </c>
       <c r="N21">
-        <v>45.66399446666667</v>
+        <v>45.25859066666668</v>
       </c>
       <c r="O21">
-        <v>9.589438838000001</v>
+        <v>9.504304040000003</v>
       </c>
       <c r="P21">
-        <v>36.07455562866667</v>
+        <v>35.75428662666668</v>
       </c>
       <c r="Q21">
-        <v>69.37455562866667</v>
+        <v>69.05428662666668</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09838553383845175</v>
+        <v>0.09892639640136677</v>
       </c>
       <c r="T21">
-        <v>0.8866676460305239</v>
+        <v>0.8957873658561164</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.92833152976011</v>
+        <v>6.581914953272105</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08772051712109342</v>
+        <v>0.08759832183304092</v>
       </c>
       <c r="C22">
-        <v>638.8872806449854</v>
+        <v>633.6708964116781</v>
       </c>
       <c r="D22">
-        <v>769.5072806449853</v>
+        <v>771.7568964116781</v>
       </c>
       <c r="E22">
-        <v>-327.58</v>
+        <v>-320.114</v>
       </c>
       <c r="F22">
-        <v>149.32</v>
+        <v>156.786</v>
       </c>
       <c r="G22">
         <v>18.7</v>
@@ -3079,28 +3079,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M22">
-        <v>8.108076000000001</v>
+        <v>8.513479800000001</v>
       </c>
       <c r="N22">
-        <v>45.25859066666668</v>
+        <v>44.85318686666668</v>
       </c>
       <c r="O22">
-        <v>9.504304040000003</v>
+        <v>9.419169242000001</v>
       </c>
       <c r="P22">
-        <v>35.75428662666668</v>
+        <v>35.43401762466667</v>
       </c>
       <c r="Q22">
-        <v>69.05428662666668</v>
+        <v>68.73401762466668</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09892639640136677</v>
+        <v>0.09948095168739356</v>
       </c>
       <c r="T22">
-        <v>0.8957873658561164</v>
+        <v>0.9051379646646354</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.581914953272105</v>
+        <v>6.268490431687718</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08759832183304092</v>
+        <v>0.0876499265449884</v>
       </c>
       <c r="C23">
-        <v>633.6708964116782</v>
+        <v>625.2532509580119</v>
       </c>
       <c r="D23">
-        <v>771.7568964116781</v>
+        <v>770.8052509580118</v>
       </c>
       <c r="E23">
-        <v>-320.114</v>
+        <v>-312.648</v>
       </c>
       <c r="F23">
-        <v>156.786</v>
+        <v>164.252</v>
       </c>
       <c r="G23">
         <v>18.7</v>
@@ -3161,45 +3161,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M23">
-        <v>8.513479799999999</v>
+        <v>9.083135599999999</v>
       </c>
       <c r="N23">
-        <v>44.85318686666668</v>
+        <v>44.28353106666668</v>
       </c>
       <c r="O23">
-        <v>9.419169242000001</v>
+        <v>9.299541524000002</v>
       </c>
       <c r="P23">
-        <v>35.43401762466667</v>
+        <v>34.98398954266668</v>
       </c>
       <c r="Q23">
-        <v>68.73401762466668</v>
+        <v>68.28398954266667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09948095168739356</v>
+        <v>0.1000497263397287</v>
       </c>
       <c r="T23">
-        <v>0.9051379646646354</v>
+        <v>0.9147283224169624</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.21</v>
       </c>
       <c r="W23">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.268490431687719</v>
+        <v>5.875357257318352</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0876499265449884</v>
+        <v>0.08753563125693591</v>
       </c>
       <c r="C24">
-        <v>625.2532509580119</v>
+        <v>619.8981429114186</v>
       </c>
       <c r="D24">
-        <v>770.8052509580118</v>
+        <v>772.9161429114185</v>
       </c>
       <c r="E24">
-        <v>-312.648</v>
+        <v>-305.182</v>
       </c>
       <c r="F24">
-        <v>164.252</v>
+        <v>171.718</v>
       </c>
       <c r="G24">
         <v>18.7</v>
@@ -3243,28 +3243,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M24">
-        <v>9.083135599999999</v>
+        <v>9.4960054</v>
       </c>
       <c r="N24">
-        <v>44.28353106666668</v>
+        <v>43.87066126666667</v>
       </c>
       <c r="O24">
-        <v>9.299541524000002</v>
+        <v>9.212838866</v>
       </c>
       <c r="P24">
-        <v>34.98398954266668</v>
+        <v>34.65782240066667</v>
       </c>
       <c r="Q24">
-        <v>68.28398954266667</v>
+        <v>67.95782240066667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1000497263397287</v>
+        <v>0.100633274359657</v>
       </c>
       <c r="T24">
-        <v>0.9147283224169624</v>
+        <v>0.9245677803706488</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.875357257318352</v>
+        <v>5.61990694178277</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08753563125693591</v>
+        <v>0.08742133596888341</v>
       </c>
       <c r="C25">
-        <v>619.8981429114186</v>
+        <v>614.5546281978239</v>
       </c>
       <c r="D25">
-        <v>772.9161429114185</v>
+        <v>775.0386281978239</v>
       </c>
       <c r="E25">
-        <v>-305.182</v>
+        <v>-297.716</v>
       </c>
       <c r="F25">
-        <v>171.718</v>
+        <v>179.184</v>
       </c>
       <c r="G25">
         <v>18.7</v>
@@ -3325,28 +3325,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M25">
-        <v>9.4960054</v>
+        <v>9.908875200000001</v>
       </c>
       <c r="N25">
-        <v>43.87066126666667</v>
+        <v>43.45779146666668</v>
       </c>
       <c r="O25">
-        <v>9.212838866</v>
+        <v>9.126136208000002</v>
       </c>
       <c r="P25">
-        <v>34.65782240066667</v>
+        <v>34.33165525866667</v>
       </c>
       <c r="Q25">
-        <v>67.95782240066667</v>
+        <v>67.63165525866667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.100633274359657</v>
+        <v>0.1012321789064255</v>
       </c>
       <c r="T25">
-        <v>0.9245677803706488</v>
+        <v>0.9346661714283794</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.61990694178277</v>
+        <v>5.385744152541822</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08742133596888341</v>
+        <v>0.08730704068083092</v>
       </c>
       <c r="C26">
-        <v>614.5546281978239</v>
+        <v>609.2228025886902</v>
       </c>
       <c r="D26">
-        <v>775.0386281978239</v>
+        <v>777.1728025886902</v>
       </c>
       <c r="E26">
-        <v>-297.716</v>
+        <v>-290.25</v>
       </c>
       <c r="F26">
-        <v>179.184</v>
+        <v>186.65</v>
       </c>
       <c r="G26">
         <v>18.7</v>
@@ -3407,28 +3407,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M26">
-        <v>9.908875199999999</v>
+        <v>10.321745</v>
       </c>
       <c r="N26">
-        <v>43.45779146666668</v>
+        <v>43.04492166666667</v>
       </c>
       <c r="O26">
-        <v>9.126136208000002</v>
+        <v>9.039433550000002</v>
       </c>
       <c r="P26">
-        <v>34.33165525866667</v>
+        <v>34.00548811666667</v>
       </c>
       <c r="Q26">
-        <v>67.63165525866667</v>
+        <v>67.30548811666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1012321789064255</v>
+        <v>0.1018470542411079</v>
       </c>
       <c r="T26">
-        <v>0.9346661714283794</v>
+        <v>0.9450338529143162</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.385744152541823</v>
+        <v>5.170314386440149</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08730704068083092</v>
+        <v>0.0871927453927784</v>
       </c>
       <c r="C27">
-        <v>609.2228025886902</v>
+        <v>603.9027629132731</v>
       </c>
       <c r="D27">
-        <v>777.1728025886902</v>
+        <v>779.3187629132731</v>
       </c>
       <c r="E27">
-        <v>-290.25</v>
+        <v>-282.784</v>
       </c>
       <c r="F27">
-        <v>186.65</v>
+        <v>194.116</v>
       </c>
       <c r="G27">
         <v>18.7</v>
@@ -3489,28 +3489,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M27">
-        <v>10.321745</v>
+        <v>10.7346148</v>
       </c>
       <c r="N27">
-        <v>43.04492166666667</v>
+        <v>42.63205186666667</v>
       </c>
       <c r="O27">
-        <v>9.039433550000002</v>
+        <v>8.952730892</v>
       </c>
       <c r="P27">
-        <v>34.00548811666667</v>
+        <v>33.67932097466667</v>
       </c>
       <c r="Q27">
-        <v>67.30548811666667</v>
+        <v>66.97932097466668</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1018470542411079</v>
+        <v>0.1024785478280789</v>
       </c>
       <c r="T27">
-        <v>0.9450338529143162</v>
+        <v>0.9556817420079811</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.170314386440149</v>
+        <v>4.971456140807835</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0871927453927784</v>
+        <v>0.08707845010472591</v>
       </c>
       <c r="C28">
-        <v>603.9027629132731</v>
+        <v>598.5946070732621</v>
       </c>
       <c r="D28">
-        <v>779.3187629132731</v>
+        <v>781.476607073262</v>
       </c>
       <c r="E28">
-        <v>-282.784</v>
+        <v>-275.318</v>
       </c>
       <c r="F28">
-        <v>194.116</v>
+        <v>201.582</v>
       </c>
       <c r="G28">
         <v>18.7</v>
@@ -3571,28 +3571,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M28">
-        <v>10.7346148</v>
+        <v>11.1474846</v>
       </c>
       <c r="N28">
-        <v>42.63205186666667</v>
+        <v>42.21918206666668</v>
       </c>
       <c r="O28">
-        <v>8.952730892</v>
+        <v>8.866028234000002</v>
       </c>
       <c r="P28">
-        <v>33.67932097466667</v>
+        <v>33.35315383266668</v>
       </c>
       <c r="Q28">
-        <v>66.97932097466668</v>
+        <v>66.65315383266667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1024785478280789</v>
+        <v>0.1031273426092136</v>
       </c>
       <c r="T28">
-        <v>0.9556817420079811</v>
+        <v>0.9666213540905135</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.971456140807835</v>
+        <v>4.78732813559273</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08707845010472591</v>
+        <v>0.0869641548166734</v>
       </c>
       <c r="C29">
-        <v>598.5946070732621</v>
+        <v>593.2984340576743</v>
       </c>
       <c r="D29">
-        <v>781.476607073262</v>
+        <v>783.6464340576742</v>
       </c>
       <c r="E29">
-        <v>-275.318</v>
+        <v>-267.852</v>
       </c>
       <c r="F29">
-        <v>201.582</v>
+        <v>209.048</v>
       </c>
       <c r="G29">
         <v>18.7</v>
@@ -3653,28 +3653,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M29">
-        <v>11.1474846</v>
+        <v>11.5603544</v>
       </c>
       <c r="N29">
-        <v>42.21918206666668</v>
+        <v>41.80631226666667</v>
       </c>
       <c r="O29">
-        <v>8.866028234000002</v>
+        <v>8.779325576000002</v>
       </c>
       <c r="P29">
-        <v>33.35315383266668</v>
+        <v>33.02698669066667</v>
       </c>
       <c r="Q29">
-        <v>66.65315383266667</v>
+        <v>66.32698669066667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1031273426092136</v>
+        <v>0.103794159467602</v>
       </c>
       <c r="T29">
-        <v>0.9666213540905135</v>
+        <v>0.9778648442864496</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.78732813559273</v>
+        <v>4.616352130750133</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0869641548166734</v>
+        <v>0.0874226095286209</v>
       </c>
       <c r="C30">
-        <v>593.2984340576743</v>
+        <v>577.2009137310222</v>
       </c>
       <c r="D30">
-        <v>783.6464340576742</v>
+        <v>775.0149137310221</v>
       </c>
       <c r="E30">
-        <v>-267.852</v>
+        <v>-260.386</v>
       </c>
       <c r="F30">
-        <v>209.048</v>
+        <v>216.514</v>
       </c>
       <c r="G30">
         <v>18.7</v>
@@ -3735,45 +3735,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M30">
-        <v>11.5603544</v>
+        <v>12.5145092</v>
       </c>
       <c r="N30">
-        <v>41.80631226666667</v>
+        <v>40.85215746666668</v>
       </c>
       <c r="O30">
-        <v>8.779325576000002</v>
+        <v>8.578953068000002</v>
       </c>
       <c r="P30">
-        <v>33.02698669066667</v>
+        <v>32.27320439866667</v>
       </c>
       <c r="Q30">
-        <v>66.32698669066667</v>
+        <v>65.57320439866666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.103794159467602</v>
+        <v>0.1044797598994661</v>
       </c>
       <c r="T30">
-        <v>0.9778648442864496</v>
+        <v>0.9894250525160739</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.21</v>
       </c>
       <c r="W30">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.616352130750133</v>
+        <v>4.264383509875614</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0874226095286209</v>
+        <v>0.0873280642405684</v>
       </c>
       <c r="C31">
-        <v>577.2009137310222</v>
+        <v>571.4993592837745</v>
       </c>
       <c r="D31">
-        <v>775.0149137310221</v>
+        <v>776.7793592837744</v>
       </c>
       <c r="E31">
-        <v>-260.386</v>
+        <v>-252.92</v>
       </c>
       <c r="F31">
-        <v>216.514</v>
+        <v>223.98</v>
       </c>
       <c r="G31">
         <v>18.7</v>
@@ -3817,28 +3817,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M31">
-        <v>12.5145092</v>
+        <v>12.946044</v>
       </c>
       <c r="N31">
-        <v>40.85215746666668</v>
+        <v>40.42062266666667</v>
       </c>
       <c r="O31">
-        <v>8.578953068000002</v>
+        <v>8.488330760000002</v>
       </c>
       <c r="P31">
-        <v>32.27320439866667</v>
+        <v>31.93229190666667</v>
       </c>
       <c r="Q31">
-        <v>65.57320439866666</v>
+        <v>65.23229190666666</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1044797598994661</v>
+        <v>0.1051849489150977</v>
       </c>
       <c r="T31">
-        <v>0.9894250525160739</v>
+        <v>1.001315552409402</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.264383509875616</v>
+        <v>4.122237392879761</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0873280642405684</v>
+        <v>0.0880906689525159</v>
       </c>
       <c r="C32">
-        <v>571.4993592837745</v>
+        <v>550.0261181072756</v>
       </c>
       <c r="D32">
-        <v>776.7793592837744</v>
+        <v>762.7721181072756</v>
       </c>
       <c r="E32">
-        <v>-252.92</v>
+        <v>-245.454</v>
       </c>
       <c r="F32">
-        <v>223.98</v>
+        <v>231.446</v>
       </c>
       <c r="G32">
         <v>18.7</v>
@@ -3899,45 +3899,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M32">
-        <v>12.946044</v>
+        <v>14.1876398</v>
       </c>
       <c r="N32">
-        <v>40.42062266666667</v>
+        <v>39.17902686666667</v>
       </c>
       <c r="O32">
-        <v>8.488330760000002</v>
+        <v>8.227595642000001</v>
       </c>
       <c r="P32">
-        <v>31.93229190666667</v>
+        <v>30.95143122466667</v>
       </c>
       <c r="Q32">
-        <v>65.23229190666666</v>
+        <v>64.25143122466667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1051849489150977</v>
+        <v>0.105910578192052</v>
       </c>
       <c r="T32">
-        <v>1.001315552409402</v>
+        <v>1.013550704473551</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.21</v>
       </c>
       <c r="W32">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.122237392879761</v>
+        <v>3.761490101170082</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0880906689525159</v>
+        <v>0.08802377366446341</v>
       </c>
       <c r="C33">
-        <v>550.0261181072756</v>
+        <v>543.7685809264606</v>
       </c>
       <c r="D33">
-        <v>762.7721181072756</v>
+        <v>763.9805809264604</v>
       </c>
       <c r="E33">
-        <v>-245.454</v>
+        <v>-237.988</v>
       </c>
       <c r="F33">
-        <v>231.446</v>
+        <v>238.912</v>
       </c>
       <c r="G33">
         <v>18.7</v>
@@ -3981,28 +3981,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M33">
-        <v>14.1876398</v>
+        <v>14.6453056</v>
       </c>
       <c r="N33">
-        <v>39.17902686666667</v>
+        <v>38.72136106666667</v>
       </c>
       <c r="O33">
-        <v>8.227595642000001</v>
+        <v>8.131485824000002</v>
       </c>
       <c r="P33">
-        <v>30.95143122466667</v>
+        <v>30.58987524266667</v>
       </c>
       <c r="Q33">
-        <v>64.25143122466667</v>
+        <v>63.88987524266667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.105910578192052</v>
+        <v>0.1066575495065638</v>
       </c>
       <c r="T33">
-        <v>1.013550704473551</v>
+        <v>1.026145713951351</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.761490101170082</v>
+        <v>3.643943535508517</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08802377366446341</v>
+        <v>0.08795687837641089</v>
       </c>
       <c r="C34">
-        <v>543.7685809264606</v>
+        <v>537.5148789664456</v>
       </c>
       <c r="D34">
-        <v>763.9805809264604</v>
+        <v>765.1928789664455</v>
       </c>
       <c r="E34">
-        <v>-237.988</v>
+        <v>-230.522</v>
       </c>
       <c r="F34">
-        <v>238.912</v>
+        <v>246.378</v>
       </c>
       <c r="G34">
         <v>18.7</v>
@@ -4063,28 +4063,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M34">
-        <v>14.6453056</v>
+        <v>15.1029714</v>
       </c>
       <c r="N34">
-        <v>38.72136106666667</v>
+        <v>38.26369526666667</v>
       </c>
       <c r="O34">
-        <v>8.131485824000002</v>
+        <v>8.035376006000002</v>
       </c>
       <c r="P34">
-        <v>30.58987524266667</v>
+        <v>30.22831926066667</v>
       </c>
       <c r="Q34">
-        <v>63.88987524266667</v>
+        <v>63.52831926066667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1066575495065638</v>
+        <v>0.1074268184722551</v>
       </c>
       <c r="T34">
-        <v>1.026145713951351</v>
+        <v>1.039116693861325</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.643943535508517</v>
+        <v>3.53352100412947</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08795687837641089</v>
+        <v>0.08864206308835838</v>
       </c>
       <c r="C35">
-        <v>537.5148789664456</v>
+        <v>517.8109421220511</v>
       </c>
       <c r="D35">
-        <v>765.1928789664455</v>
+        <v>752.9549421220511</v>
       </c>
       <c r="E35">
-        <v>-230.522</v>
+        <v>-223.056</v>
       </c>
       <c r="F35">
-        <v>246.378</v>
+        <v>253.844</v>
       </c>
       <c r="G35">
         <v>18.7</v>
@@ -4145,45 +4145,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M35">
-        <v>15.1029714</v>
+        <v>16.2714004</v>
       </c>
       <c r="N35">
-        <v>38.26369526666667</v>
+        <v>37.09526626666667</v>
       </c>
       <c r="O35">
-        <v>8.035376006000002</v>
+        <v>7.790005916</v>
       </c>
       <c r="P35">
-        <v>30.22831926066667</v>
+        <v>29.30526035066667</v>
       </c>
       <c r="Q35">
-        <v>63.52831926066667</v>
+        <v>62.60526035066667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1074268184722551</v>
+        <v>0.1082193986187248</v>
       </c>
       <c r="T35">
-        <v>1.039116693861325</v>
+        <v>1.052480733768571</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.21</v>
       </c>
       <c r="W35">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.53352100412947</v>
+        <v>3.279783261105582</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08864206308835838</v>
+        <v>0.0885972878003059</v>
       </c>
       <c r="C36">
-        <v>517.8109421220511</v>
+        <v>511.1326970513205</v>
       </c>
       <c r="D36">
-        <v>752.9549421220511</v>
+        <v>753.7426970513204</v>
       </c>
       <c r="E36">
-        <v>-223.056</v>
+        <v>-215.59</v>
       </c>
       <c r="F36">
-        <v>253.844</v>
+        <v>261.31</v>
       </c>
       <c r="G36">
         <v>18.7</v>
@@ -4227,28 +4227,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M36">
-        <v>16.2714004</v>
+        <v>16.749971</v>
       </c>
       <c r="N36">
-        <v>37.09526626666667</v>
+        <v>36.61669566666667</v>
       </c>
       <c r="O36">
-        <v>7.790005916</v>
+        <v>7.689506090000001</v>
       </c>
       <c r="P36">
-        <v>29.30526035066667</v>
+        <v>28.92718957666667</v>
       </c>
       <c r="Q36">
-        <v>62.60526035066667</v>
+        <v>62.22718957666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1082193986187248</v>
+        <v>0.1090363658466245</v>
       </c>
       <c r="T36">
-        <v>1.052480733768571</v>
+        <v>1.066255974903731</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.279783261105582</v>
+        <v>3.186075167931137</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0885972878003059</v>
+        <v>0.08855251251225338</v>
       </c>
       <c r="C37">
-        <v>511.1326970513205</v>
+        <v>504.4561020335023</v>
       </c>
       <c r="D37">
-        <v>753.7426970513204</v>
+        <v>754.5321020335023</v>
       </c>
       <c r="E37">
-        <v>-215.59</v>
+        <v>-208.124</v>
       </c>
       <c r="F37">
-        <v>261.31</v>
+        <v>268.776</v>
       </c>
       <c r="G37">
         <v>18.7</v>
@@ -4309,28 +4309,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M37">
-        <v>16.749971</v>
+        <v>17.2285416</v>
       </c>
       <c r="N37">
-        <v>36.61669566666667</v>
+        <v>36.13812506666667</v>
       </c>
       <c r="O37">
-        <v>7.689506090000001</v>
+        <v>7.589006264000002</v>
       </c>
       <c r="P37">
-        <v>28.92718957666667</v>
+        <v>28.54911880266667</v>
       </c>
       <c r="Q37">
-        <v>62.22718957666667</v>
+        <v>61.84911880266667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1090363658466245</v>
+        <v>0.1098788633003959</v>
       </c>
       <c r="T37">
-        <v>1.066255974903731</v>
+        <v>1.080461692324366</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.186075167931137</v>
+        <v>3.09757307993305</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08855251251225339</v>
+        <v>0.0885077372242009</v>
       </c>
       <c r="C38">
-        <v>504.456102033502</v>
+        <v>497.7811622583987</v>
       </c>
       <c r="D38">
-        <v>754.5321020335019</v>
+        <v>755.3231622583986</v>
       </c>
       <c r="E38">
-        <v>-208.124</v>
+        <v>-200.658</v>
       </c>
       <c r="F38">
-        <v>268.776</v>
+        <v>276.242</v>
       </c>
       <c r="G38">
         <v>18.7</v>
@@ -4391,28 +4391,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M38">
-        <v>17.2285416</v>
+        <v>17.7071122</v>
       </c>
       <c r="N38">
-        <v>36.13812506666667</v>
+        <v>35.65955446666668</v>
       </c>
       <c r="O38">
-        <v>7.589006264000002</v>
+        <v>7.488506438000002</v>
       </c>
       <c r="P38">
-        <v>28.54911880266667</v>
+        <v>28.17104802866668</v>
       </c>
       <c r="Q38">
-        <v>61.84911880266667</v>
+        <v>61.47104802866667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1098788633003959</v>
+        <v>0.1107481067050808</v>
       </c>
       <c r="T38">
-        <v>1.080461692324366</v>
+        <v>1.095118384901211</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.09757307993305</v>
+        <v>3.013854888583508</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0885077372242009</v>
+        <v>0.09080452193614839</v>
       </c>
       <c r="C39">
-        <v>497.7811622583987</v>
+        <v>451.7675982132511</v>
       </c>
       <c r="D39">
-        <v>755.3231622583986</v>
+        <v>716.775598213251</v>
       </c>
       <c r="E39">
-        <v>-200.658</v>
+        <v>-193.192</v>
       </c>
       <c r="F39">
-        <v>276.242</v>
+        <v>283.708</v>
       </c>
       <c r="G39">
         <v>18.7</v>
@@ -4473,45 +4473,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M39">
-        <v>17.7071122</v>
+        <v>20.3986052</v>
       </c>
       <c r="N39">
-        <v>35.65955446666668</v>
+        <v>32.96806146666668</v>
       </c>
       <c r="O39">
-        <v>7.488506438000002</v>
+        <v>6.923292908000001</v>
       </c>
       <c r="P39">
-        <v>28.17104802866668</v>
+        <v>26.04476855866668</v>
       </c>
       <c r="Q39">
-        <v>61.47104802866667</v>
+        <v>59.34476855866667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1107481067050808</v>
+        <v>0.1116453902195942</v>
       </c>
       <c r="T39">
-        <v>1.095118384901211</v>
+        <v>1.110247874012793</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.21</v>
       </c>
       <c r="W39">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.013854888583508</v>
+        <v>2.616191947607608</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09080452193614839</v>
+        <v>0.0908213666480959</v>
       </c>
       <c r="C40">
-        <v>451.7675982132511</v>
+        <v>444.0334171387565</v>
       </c>
       <c r="D40">
-        <v>716.775598213251</v>
+        <v>716.5074171387564</v>
       </c>
       <c r="E40">
-        <v>-193.192</v>
+        <v>-185.726</v>
       </c>
       <c r="F40">
-        <v>283.708</v>
+        <v>291.174</v>
       </c>
       <c r="G40">
         <v>18.7</v>
@@ -4555,28 +4555,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M40">
-        <v>20.3986052</v>
+        <v>20.9354106</v>
       </c>
       <c r="N40">
-        <v>32.96806146666668</v>
+        <v>32.43125606666668</v>
       </c>
       <c r="O40">
-        <v>6.923292908000001</v>
+        <v>6.810563774000002</v>
       </c>
       <c r="P40">
-        <v>26.04476855866668</v>
+        <v>25.62069229266667</v>
       </c>
       <c r="Q40">
-        <v>59.34476855866667</v>
+        <v>58.92069229266667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1116453902195942</v>
+        <v>0.112572092865731</v>
       </c>
       <c r="T40">
-        <v>1.110247874012793</v>
+        <v>1.125873411947706</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.616191947607608</v>
+        <v>2.549110102797156</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0908213666480959</v>
+        <v>0.09207061136004338</v>
       </c>
       <c r="C41">
-        <v>444.0334171387565</v>
+        <v>417.2226737774295</v>
       </c>
       <c r="D41">
-        <v>716.5074171387564</v>
+        <v>697.1626737774294</v>
       </c>
       <c r="E41">
-        <v>-185.726</v>
+        <v>-178.26</v>
       </c>
       <c r="F41">
-        <v>291.174</v>
+        <v>298.64</v>
       </c>
       <c r="G41">
         <v>18.7</v>
@@ -4637,45 +4637,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M41">
-        <v>20.9354106</v>
+        <v>22.636912</v>
       </c>
       <c r="N41">
-        <v>32.43125606666668</v>
+        <v>30.72975466666667</v>
       </c>
       <c r="O41">
-        <v>6.810563774000002</v>
+        <v>6.453248480000001</v>
       </c>
       <c r="P41">
-        <v>25.62069229266667</v>
+        <v>24.27650618666667</v>
       </c>
       <c r="Q41">
-        <v>58.92069229266667</v>
+        <v>57.57650618666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.112572092865731</v>
+        <v>0.1135296856000723</v>
       </c>
       <c r="T41">
-        <v>1.125873411947706</v>
+        <v>1.142019801147116</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.21</v>
       </c>
       <c r="W41">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.549110102797156</v>
+        <v>2.357506477326354</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09207061136004338</v>
+        <v>0.09211826607199089</v>
       </c>
       <c r="C42">
-        <v>417.2226737774295</v>
+        <v>409.039395493571</v>
       </c>
       <c r="D42">
-        <v>697.1626737774294</v>
+        <v>696.4453954935709</v>
       </c>
       <c r="E42">
-        <v>-178.26</v>
+        <v>-170.794</v>
       </c>
       <c r="F42">
-        <v>298.64</v>
+        <v>306.106</v>
       </c>
       <c r="G42">
         <v>18.7</v>
@@ -4719,28 +4719,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M42">
-        <v>22.636912</v>
+        <v>23.2028348</v>
       </c>
       <c r="N42">
-        <v>30.72975466666667</v>
+        <v>30.16383186666667</v>
       </c>
       <c r="O42">
-        <v>6.453248480000001</v>
+        <v>6.334404692000001</v>
       </c>
       <c r="P42">
-        <v>24.27650618666667</v>
+        <v>23.82942717466667</v>
       </c>
       <c r="Q42">
-        <v>57.57650618666667</v>
+        <v>57.12942717466667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1135296856000723</v>
+        <v>0.1145197391050693</v>
       </c>
       <c r="T42">
-        <v>1.142019801147116</v>
+        <v>1.158713525573624</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.357506477326354</v>
+        <v>2.300006319342784</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09211826607199089</v>
+        <v>0.0921659207839384</v>
       </c>
       <c r="C43">
-        <v>409.039395493571</v>
+        <v>400.8575916413392</v>
       </c>
       <c r="D43">
-        <v>696.4453954935709</v>
+        <v>695.7295916413392</v>
       </c>
       <c r="E43">
-        <v>-170.794</v>
+        <v>-163.328</v>
       </c>
       <c r="F43">
-        <v>306.106</v>
+        <v>313.572</v>
       </c>
       <c r="G43">
         <v>18.7</v>
@@ -4801,28 +4801,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M43">
-        <v>23.2028348</v>
+        <v>23.7687576</v>
       </c>
       <c r="N43">
-        <v>30.16383186666667</v>
+        <v>29.59790906666667</v>
       </c>
       <c r="O43">
-        <v>6.334404692000001</v>
+        <v>6.215560904000001</v>
       </c>
       <c r="P43">
-        <v>23.82942717466667</v>
+        <v>23.38234816266667</v>
       </c>
       <c r="Q43">
-        <v>57.12942717466667</v>
+        <v>56.68234816266667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1145197391050693</v>
+        <v>0.1155439323861007</v>
       </c>
       <c r="T43">
-        <v>1.158713525573624</v>
+        <v>1.175982895670012</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.300006319342784</v>
+        <v>2.245244264120337</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09216592078393838</v>
+        <v>0.09221357549588588</v>
       </c>
       <c r="C44">
-        <v>400.8575916413395</v>
+        <v>392.6772576791573</v>
       </c>
       <c r="D44">
-        <v>695.7295916413394</v>
+        <v>695.0152576791572</v>
       </c>
       <c r="E44">
-        <v>-163.328</v>
+        <v>-155.862</v>
       </c>
       <c r="F44">
-        <v>313.5719999999999</v>
+        <v>321.038</v>
       </c>
       <c r="G44">
         <v>18.7</v>
@@ -4883,28 +4883,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M44">
-        <v>23.7687576</v>
+        <v>24.3346804</v>
       </c>
       <c r="N44">
-        <v>29.59790906666668</v>
+        <v>29.03198626666667</v>
       </c>
       <c r="O44">
-        <v>6.215560904000002</v>
+        <v>6.096717116000002</v>
       </c>
       <c r="P44">
-        <v>23.38234816266667</v>
+        <v>22.93526915066667</v>
       </c>
       <c r="Q44">
-        <v>56.68234816266667</v>
+        <v>56.23526915066667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1155439323861007</v>
+        <v>0.116604062273484</v>
       </c>
       <c r="T44">
-        <v>1.175982895670012</v>
+        <v>1.1938582085768</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.245244264120338</v>
+        <v>2.193029281233818</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09221357549588588</v>
+        <v>0.09226123020783339</v>
       </c>
       <c r="C45">
-        <v>392.6772576791573</v>
+        <v>384.49838908408</v>
       </c>
       <c r="D45">
-        <v>695.0152576791572</v>
+        <v>694.3023890840799</v>
       </c>
       <c r="E45">
-        <v>-155.862</v>
+        <v>-148.396</v>
       </c>
       <c r="F45">
-        <v>321.038</v>
+        <v>328.504</v>
       </c>
       <c r="G45">
         <v>18.7</v>
@@ -4965,28 +4965,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M45">
-        <v>24.3346804</v>
+        <v>24.9006032</v>
       </c>
       <c r="N45">
-        <v>29.03198626666667</v>
+        <v>28.46606346666668</v>
       </c>
       <c r="O45">
-        <v>6.096717116000002</v>
+        <v>5.977873328000001</v>
       </c>
       <c r="P45">
-        <v>22.93526915066667</v>
+        <v>22.48819013866667</v>
       </c>
       <c r="Q45">
-        <v>56.23526915066667</v>
+        <v>55.78819013866667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.116604062273484</v>
+        <v>0.1177020539425596</v>
       </c>
       <c r="T45">
-        <v>1.1938582085768</v>
+        <v>1.212371925515973</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.193029281233818</v>
+        <v>2.143187706660322</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09226123020783339</v>
+        <v>0.0923088849197809</v>
       </c>
       <c r="C46">
-        <v>384.49838908408</v>
+        <v>376.3209813517007</v>
       </c>
       <c r="D46">
-        <v>694.3023890840799</v>
+        <v>693.5909813517006</v>
       </c>
       <c r="E46">
-        <v>-148.396</v>
+        <v>-140.93</v>
       </c>
       <c r="F46">
-        <v>328.504</v>
+        <v>335.97</v>
       </c>
       <c r="G46">
         <v>18.7</v>
@@ -5047,28 +5047,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M46">
-        <v>24.9006032</v>
+        <v>25.466526</v>
       </c>
       <c r="N46">
-        <v>28.46606346666668</v>
+        <v>27.90014066666668</v>
       </c>
       <c r="O46">
-        <v>5.977873328000001</v>
+        <v>5.859029540000002</v>
       </c>
       <c r="P46">
-        <v>22.48819013866667</v>
+        <v>22.04111112666667</v>
       </c>
       <c r="Q46">
-        <v>55.78819013866667</v>
+        <v>55.34111112666668</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1177020539425596</v>
+        <v>0.1188399725814198</v>
       </c>
       <c r="T46">
-        <v>1.212371925515973</v>
+        <v>1.231558868525661</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.143187706660322</v>
+        <v>2.095561313178981</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0923088849197809</v>
+        <v>0.09235653963172838</v>
       </c>
       <c r="C47">
-        <v>376.3209813517007</v>
+        <v>368.1450299960557</v>
       </c>
       <c r="D47">
-        <v>693.5909813517006</v>
+        <v>692.8810299960556</v>
       </c>
       <c r="E47">
-        <v>-140.93</v>
+        <v>-133.464</v>
       </c>
       <c r="F47">
-        <v>335.97</v>
+        <v>343.436</v>
       </c>
       <c r="G47">
         <v>18.7</v>
@@ -5129,28 +5129,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M47">
-        <v>25.466526</v>
+        <v>26.0324488</v>
       </c>
       <c r="N47">
-        <v>27.90014066666668</v>
+        <v>27.33421786666667</v>
       </c>
       <c r="O47">
-        <v>5.859029540000002</v>
+        <v>5.740185752000001</v>
       </c>
       <c r="P47">
-        <v>22.04111112666667</v>
+        <v>21.59403211466667</v>
       </c>
       <c r="Q47">
-        <v>55.34111112666668</v>
+        <v>54.89403211466667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1188399725814198</v>
+        <v>0.1200200363550525</v>
       </c>
       <c r="T47">
-        <v>1.231558868525661</v>
+        <v>1.251456439054226</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.095561313178981</v>
+        <v>2.050005632457699</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09235653963172838</v>
+        <v>0.09240419434367589</v>
       </c>
       <c r="C48">
-        <v>368.1450299960557</v>
+        <v>359.9705305495282</v>
       </c>
       <c r="D48">
-        <v>692.8810299960556</v>
+        <v>692.1725305495281</v>
       </c>
       <c r="E48">
-        <v>-133.464</v>
+        <v>-125.998</v>
       </c>
       <c r="F48">
-        <v>343.436</v>
+        <v>350.902</v>
       </c>
       <c r="G48">
         <v>18.7</v>
@@ -5211,28 +5211,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M48">
-        <v>26.0324488</v>
+        <v>26.5983716</v>
       </c>
       <c r="N48">
-        <v>27.33421786666667</v>
+        <v>26.76829506666667</v>
       </c>
       <c r="O48">
-        <v>5.740185752000001</v>
+        <v>5.621341964000002</v>
       </c>
       <c r="P48">
-        <v>21.59403211466667</v>
+        <v>21.14695310266667</v>
       </c>
       <c r="Q48">
-        <v>54.89403211466667</v>
+        <v>54.44695310266667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1200200363550525</v>
+        <v>0.1212446308371243</v>
       </c>
       <c r="T48">
-        <v>1.251456439054226</v>
+        <v>1.272104861300851</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.050005632457699</v>
+        <v>2.006388491341578</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09240419434367589</v>
+        <v>0.09783648905562339</v>
       </c>
       <c r="C49">
-        <v>359.9705305495282</v>
+        <v>280.2459050023616</v>
       </c>
       <c r="D49">
-        <v>692.1725305495281</v>
+        <v>619.9139050023615</v>
       </c>
       <c r="E49">
-        <v>-125.998</v>
+        <v>-118.532</v>
       </c>
       <c r="F49">
-        <v>350.902</v>
+        <v>358.368</v>
       </c>
       <c r="G49">
         <v>18.7</v>
@@ -5293,45 +5293,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M49">
-        <v>26.5983716</v>
+        <v>32.25312</v>
       </c>
       <c r="N49">
-        <v>26.76829506666667</v>
+        <v>21.11354666666668</v>
       </c>
       <c r="O49">
-        <v>5.621341964000002</v>
+        <v>4.433844800000002</v>
       </c>
       <c r="P49">
-        <v>21.14695310266667</v>
+        <v>16.67970186666668</v>
       </c>
       <c r="Q49">
-        <v>54.44695310266667</v>
+        <v>49.97970186666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1212446308371243</v>
+        <v>0.1225163251069681</v>
       </c>
       <c r="T49">
-        <v>1.272104861300851</v>
+        <v>1.293547453633885</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0.21</v>
       </c>
       <c r="W49">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.006388491341578</v>
+        <v>1.654620286864238</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09783648905562337</v>
+        <v>0.09799632376757088</v>
       </c>
       <c r="C50">
-        <v>280.245905002362</v>
+        <v>270.8816149833267</v>
       </c>
       <c r="D50">
-        <v>619.9139050023618</v>
+        <v>618.0156149833266</v>
       </c>
       <c r="E50">
-        <v>-118.532</v>
+        <v>-111.066</v>
       </c>
       <c r="F50">
-        <v>358.3679999999999</v>
+        <v>365.8339999999999</v>
       </c>
       <c r="G50">
         <v>18.7</v>
@@ -5375,28 +5375,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M50">
-        <v>32.25312</v>
+        <v>32.92505999999999</v>
       </c>
       <c r="N50">
-        <v>21.11354666666668</v>
+        <v>20.44160666666668</v>
       </c>
       <c r="O50">
-        <v>4.433844800000002</v>
+        <v>4.292737400000003</v>
       </c>
       <c r="P50">
-        <v>16.67970186666668</v>
+        <v>16.14886926666668</v>
       </c>
       <c r="Q50">
-        <v>49.97970186666667</v>
+        <v>49.44886926666668</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.122516325106968</v>
+        <v>0.123837889740335</v>
       </c>
       <c r="T50">
-        <v>1.293547453633884</v>
+        <v>1.315830931940762</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.654620286864238</v>
+        <v>1.620852525907825</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09799632376757088</v>
+        <v>0.09815615847951838</v>
       </c>
       <c r="C51">
-        <v>270.8816149833267</v>
+        <v>261.5289152966307</v>
       </c>
       <c r="D51">
-        <v>618.0156149833266</v>
+        <v>616.1289152966306</v>
       </c>
       <c r="E51">
-        <v>-111.066</v>
+        <v>-103.6</v>
       </c>
       <c r="F51">
-        <v>365.8339999999999</v>
+        <v>373.3</v>
       </c>
       <c r="G51">
         <v>18.7</v>
@@ -5457,28 +5457,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M51">
-        <v>32.92505999999999</v>
+        <v>33.59699999999999</v>
       </c>
       <c r="N51">
-        <v>20.44160666666668</v>
+        <v>19.76966666666668</v>
       </c>
       <c r="O51">
-        <v>4.292737400000003</v>
+        <v>4.151630000000003</v>
       </c>
       <c r="P51">
-        <v>16.14886926666668</v>
+        <v>15.61803666666668</v>
       </c>
       <c r="Q51">
-        <v>49.44886926666668</v>
+        <v>48.91803666666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.123837889740335</v>
+        <v>0.1252123169590368</v>
       </c>
       <c r="T51">
-        <v>1.315830931940762</v>
+        <v>1.339005749379915</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.620852525907825</v>
+        <v>1.588435475389668</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09815615847951838</v>
+        <v>0.09831599319146588</v>
       </c>
       <c r="C52">
-        <v>261.5289152966307</v>
+        <v>252.1877001152301</v>
       </c>
       <c r="D52">
-        <v>616.1289152966306</v>
+        <v>614.25370011523</v>
       </c>
       <c r="E52">
-        <v>-103.6</v>
+        <v>-96.13400000000001</v>
       </c>
       <c r="F52">
-        <v>373.3</v>
+        <v>380.766</v>
       </c>
       <c r="G52">
         <v>18.7</v>
@@ -5539,28 +5539,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M52">
-        <v>33.59699999999999</v>
+        <v>34.26893999999999</v>
       </c>
       <c r="N52">
-        <v>19.76966666666668</v>
+        <v>19.09772666666668</v>
       </c>
       <c r="O52">
-        <v>4.151630000000003</v>
+        <v>4.010522600000002</v>
       </c>
       <c r="P52">
-        <v>15.61803666666668</v>
+        <v>15.08720406666668</v>
       </c>
       <c r="Q52">
-        <v>48.91803666666667</v>
+        <v>48.38720406666668</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1252123169590368</v>
+        <v>0.1266428432478895</v>
       </c>
       <c r="T52">
-        <v>1.339005749379915</v>
+        <v>1.363126477734952</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.588435475389668</v>
+        <v>1.557289681754577</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09831599319146588</v>
+        <v>0.09847582790341336</v>
       </c>
       <c r="C53">
-        <v>252.1877001152301</v>
+        <v>242.8578648965295</v>
       </c>
       <c r="D53">
-        <v>614.25370011523</v>
+        <v>612.3898648965294</v>
       </c>
       <c r="E53">
-        <v>-96.13400000000001</v>
+        <v>-88.66800000000001</v>
       </c>
       <c r="F53">
-        <v>380.766</v>
+        <v>388.232</v>
       </c>
       <c r="G53">
         <v>18.7</v>
@@ -5621,28 +5621,28 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M53">
-        <v>34.26893999999999</v>
+        <v>34.94087999999999</v>
       </c>
       <c r="N53">
-        <v>19.09772666666668</v>
+        <v>18.42578666666668</v>
       </c>
       <c r="O53">
-        <v>4.010522600000002</v>
+        <v>3.869415200000003</v>
       </c>
       <c r="P53">
-        <v>15.08720406666668</v>
+        <v>14.55637146666668</v>
       </c>
       <c r="Q53">
-        <v>48.38720406666668</v>
+        <v>47.85637146666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1266428432478895</v>
+        <v>0.1281329747987779</v>
       </c>
       <c r="T53">
-        <v>1.363126477734952</v>
+        <v>1.388252236438115</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.557289681754577</v>
+        <v>1.527341803259296</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09847582790341336</v>
+        <v>0.1241473199096109</v>
       </c>
       <c r="C54">
-        <v>242.8578648965295</v>
+        <v>34.73456686125672</v>
       </c>
       <c r="D54">
-        <v>612.3898648965294</v>
+        <v>411.7325668612567</v>
       </c>
       <c r="E54">
-        <v>-88.66800000000001</v>
+        <v>-81.202</v>
       </c>
       <c r="F54">
-        <v>388.232</v>
+        <v>395.698</v>
       </c>
       <c r="G54">
         <v>18.7</v>
@@ -5703,45 +5703,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M54">
-        <v>34.94087999999999</v>
+        <v>58.0884664</v>
       </c>
       <c r="N54">
-        <v>18.42578666666668</v>
+        <v>-4.721799733333327</v>
       </c>
       <c r="O54">
-        <v>3.869415200000003</v>
+        <v>-0.9915779439999987</v>
       </c>
       <c r="P54">
-        <v>14.55637146666668</v>
+        <v>-3.730221789333329</v>
       </c>
       <c r="Q54">
-        <v>47.85637146666667</v>
+        <v>29.56977821066667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1281329747987779</v>
+        <v>0.1305405003234963</v>
       </c>
       <c r="T54">
-        <v>1.388252236438115</v>
+        <v>1.428846575488061</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.21</v>
+        <v>0.1929298653338178</v>
       </c>
       <c r="W54">
-        <v>0.0711</v>
+        <v>0.1184778957689955</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.527341803259296</v>
+        <v>0.9187136444467515</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1241473199096109</v>
+        <v>0.1251573199096109</v>
       </c>
       <c r="C55">
-        <v>34.73456686125672</v>
+        <v>22.0283458834877</v>
       </c>
       <c r="D55">
-        <v>411.7325668612567</v>
+        <v>406.4923458834877</v>
       </c>
       <c r="E55">
-        <v>-81.202</v>
+        <v>-73.73599999999999</v>
       </c>
       <c r="F55">
-        <v>395.698</v>
+        <v>403.164</v>
       </c>
       <c r="G55">
         <v>18.7</v>
@@ -5785,37 +5785,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M55">
-        <v>58.0884664</v>
+        <v>59.1844752</v>
       </c>
       <c r="N55">
-        <v>-4.721799733333327</v>
+        <v>-5.817808533333327</v>
       </c>
       <c r="O55">
-        <v>-0.9915779439999987</v>
+        <v>-1.221739791999999</v>
       </c>
       <c r="P55">
-        <v>-3.730221789333329</v>
+        <v>-4.596068741333329</v>
       </c>
       <c r="Q55">
-        <v>29.56977821066667</v>
+        <v>28.70393125866667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1305405003234963</v>
+        <v>0.1323826851131375</v>
       </c>
       <c r="T55">
-        <v>1.428846575488061</v>
+        <v>1.459908457563888</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1929298653338178</v>
+        <v>0.1893570900498582</v>
       </c>
       <c r="W55">
-        <v>0.1184778957689955</v>
+        <v>0.1190023791806808</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9187136444467515</v>
+        <v>0.9017004288088487</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1251573199096109</v>
+        <v>0.1261673199096109</v>
       </c>
       <c r="C56">
-        <v>22.0283458834877</v>
+        <v>9.453835735282325</v>
       </c>
       <c r="D56">
-        <v>406.4923458834877</v>
+        <v>401.3838357352823</v>
       </c>
       <c r="E56">
-        <v>-73.73599999999999</v>
+        <v>-66.26999999999998</v>
       </c>
       <c r="F56">
-        <v>403.164</v>
+        <v>410.63</v>
       </c>
       <c r="G56">
         <v>18.7</v>
@@ -5867,37 +5867,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M56">
-        <v>59.1844752</v>
+        <v>60.28048400000001</v>
       </c>
       <c r="N56">
-        <v>-5.817808533333327</v>
+        <v>-6.913817333333334</v>
       </c>
       <c r="O56">
-        <v>-1.221739791999999</v>
+        <v>-1.45190164</v>
       </c>
       <c r="P56">
-        <v>-4.596068741333329</v>
+        <v>-5.461915693333334</v>
       </c>
       <c r="Q56">
-        <v>28.70393125866667</v>
+        <v>27.83808430666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1323826851131375</v>
+        <v>0.1343067447823184</v>
       </c>
       <c r="T56">
-        <v>1.459908457563888</v>
+        <v>1.492350867731975</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1893570900498582</v>
+        <v>0.1859142338671335</v>
       </c>
       <c r="W56">
-        <v>0.1190023791806808</v>
+        <v>0.1195077904683048</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9017004288088487</v>
+        <v>0.8853058755577786</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1261673199096109</v>
+        <v>0.1271773199096109</v>
       </c>
       <c r="C57">
-        <v>9.453835735282325</v>
+        <v>-2.993867699322493</v>
       </c>
       <c r="D57">
-        <v>401.3838357352823</v>
+        <v>396.4021323006775</v>
       </c>
       <c r="E57">
-        <v>-66.26999999999998</v>
+        <v>-58.80399999999997</v>
       </c>
       <c r="F57">
-        <v>410.63</v>
+        <v>418.096</v>
       </c>
       <c r="G57">
         <v>18.7</v>
@@ -5949,37 +5949,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M57">
-        <v>60.28048400000001</v>
+        <v>61.37649280000001</v>
       </c>
       <c r="N57">
-        <v>-6.913817333333334</v>
+        <v>-8.009826133333334</v>
       </c>
       <c r="O57">
-        <v>-1.45190164</v>
+        <v>-1.682063488</v>
       </c>
       <c r="P57">
-        <v>-5.461915693333334</v>
+        <v>-6.327762645333334</v>
       </c>
       <c r="Q57">
-        <v>27.83808430666666</v>
+        <v>26.97223735466666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1343067447823184</v>
+        <v>0.1363182617091892</v>
       </c>
       <c r="T57">
-        <v>1.492350867731975</v>
+        <v>1.526267932907701</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1859142338671335</v>
+        <v>0.1825943368337918</v>
       </c>
       <c r="W57">
-        <v>0.1195077904683048</v>
+        <v>0.1199951513527994</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8853058755577786</v>
+        <v>0.8694968420656755</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1271773199096109</v>
+        <v>0.1281873199096109</v>
       </c>
       <c r="C58">
-        <v>-2.993867699322493</v>
+        <v>-15.31942805476234</v>
       </c>
       <c r="D58">
-        <v>396.4021323006775</v>
+        <v>391.5425719452377</v>
       </c>
       <c r="E58">
-        <v>-58.80399999999997</v>
+        <v>-51.33799999999997</v>
       </c>
       <c r="F58">
-        <v>418.096</v>
+        <v>425.562</v>
       </c>
       <c r="G58">
         <v>18.7</v>
@@ -6031,37 +6031,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M58">
-        <v>61.37649280000001</v>
+        <v>62.47250160000001</v>
       </c>
       <c r="N58">
-        <v>-8.009826133333334</v>
+        <v>-9.105834933333334</v>
       </c>
       <c r="O58">
-        <v>-1.682063488</v>
+        <v>-1.912225336</v>
       </c>
       <c r="P58">
-        <v>-6.327762645333334</v>
+        <v>-7.193609597333333</v>
       </c>
       <c r="Q58">
-        <v>26.97223735466666</v>
+        <v>26.10639040266666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1363182617091892</v>
+        <v>0.1384233375628913</v>
       </c>
       <c r="T58">
-        <v>1.526267932907701</v>
+        <v>1.561762535998578</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1825943368337918</v>
+        <v>0.1793909274156552</v>
       </c>
       <c r="W58">
-        <v>0.1199951513527994</v>
+        <v>0.1204654118553818</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8694968420656755</v>
+        <v>0.8542425115031198</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1281873199096109</v>
+        <v>0.1291973199096109</v>
       </c>
       <c r="C59">
-        <v>-15.31942805476234</v>
+        <v>-27.52728304594558</v>
       </c>
       <c r="D59">
-        <v>391.5425719452377</v>
+        <v>386.8007169540545</v>
       </c>
       <c r="E59">
-        <v>-51.33799999999997</v>
+        <v>-43.87199999999996</v>
       </c>
       <c r="F59">
-        <v>425.562</v>
+        <v>433.028</v>
       </c>
       <c r="G59">
         <v>18.7</v>
@@ -6113,37 +6113,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M59">
-        <v>62.47250160000001</v>
+        <v>63.56851040000001</v>
       </c>
       <c r="N59">
-        <v>-9.105834933333334</v>
+        <v>-10.20184373333333</v>
       </c>
       <c r="O59">
-        <v>-1.912225336</v>
+        <v>-2.142387184</v>
       </c>
       <c r="P59">
-        <v>-7.193609597333333</v>
+        <v>-8.059456549333333</v>
       </c>
       <c r="Q59">
-        <v>26.10639040266666</v>
+        <v>25.24054345066666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1384233375628913</v>
+        <v>0.1406286551239125</v>
       </c>
       <c r="T59">
-        <v>1.561762535998578</v>
+        <v>1.598947358284259</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1793909274156552</v>
+        <v>0.1762979803912473</v>
       </c>
       <c r="W59">
-        <v>0.1204654118553818</v>
+        <v>0.1209194564785649</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8542425115031198</v>
+        <v>0.8395141923392728</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1291973199096109</v>
+        <v>0.1302073199096109</v>
       </c>
       <c r="C60">
-        <v>-27.52728304594541</v>
+        <v>-39.62165798477719</v>
       </c>
       <c r="D60">
-        <v>386.8007169540545</v>
+        <v>382.1723420152227</v>
       </c>
       <c r="E60">
-        <v>-43.87200000000007</v>
+        <v>-36.40600000000006</v>
       </c>
       <c r="F60">
-        <v>433.0279999999999</v>
+        <v>440.4939999999999</v>
       </c>
       <c r="G60">
         <v>18.7</v>
@@ -6195,37 +6195,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M60">
-        <v>63.56851039999999</v>
+        <v>64.66451919999999</v>
       </c>
       <c r="N60">
-        <v>-10.20184373333332</v>
+        <v>-11.29785253333331</v>
       </c>
       <c r="O60">
-        <v>-2.142387183999997</v>
+        <v>-2.372549031999995</v>
       </c>
       <c r="P60">
-        <v>-8.059456549333323</v>
+        <v>-8.925303501333318</v>
       </c>
       <c r="Q60">
-        <v>25.24054345066667</v>
+        <v>24.37469649866668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1406286551239125</v>
+        <v>0.142941549151325</v>
       </c>
       <c r="T60">
-        <v>1.598947358284258</v>
+        <v>1.637946074339972</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1762979803912473</v>
+        <v>0.1733098790286838</v>
       </c>
       <c r="W60">
-        <v>0.1209194564785649</v>
+        <v>0.1213581097585892</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.839514192339273</v>
+        <v>0.8252851382318278</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1302073199096109</v>
+        <v>0.1312173199096109</v>
       </c>
       <c r="C61">
-        <v>-39.62165798477719</v>
+        <v>-51.60657833774337</v>
       </c>
       <c r="D61">
-        <v>382.1723420152227</v>
+        <v>377.6534216622566</v>
       </c>
       <c r="E61">
-        <v>-36.40600000000006</v>
+        <v>-28.94000000000005</v>
       </c>
       <c r="F61">
-        <v>440.4939999999999</v>
+        <v>447.9599999999999</v>
       </c>
       <c r="G61">
         <v>18.7</v>
@@ -6277,37 +6277,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M61">
-        <v>64.66451919999999</v>
+        <v>65.76052799999999</v>
       </c>
       <c r="N61">
-        <v>-11.29785253333331</v>
+        <v>-12.39386133333332</v>
       </c>
       <c r="O61">
-        <v>-2.372549031999995</v>
+        <v>-2.602710879999997</v>
       </c>
       <c r="P61">
-        <v>-8.925303501333318</v>
+        <v>-9.791150453333323</v>
       </c>
       <c r="Q61">
-        <v>24.37469649866668</v>
+        <v>23.50884954666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.142941549151325</v>
+        <v>0.1453700878801082</v>
       </c>
       <c r="T61">
-        <v>1.637946074339972</v>
+        <v>1.678894726198471</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1733098790286838</v>
+        <v>0.1704213810448724</v>
       </c>
       <c r="W61">
-        <v>0.1213581097585892</v>
+        <v>0.1217821412626127</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8252851382318278</v>
+        <v>0.8115303859279639</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1312173199096109</v>
+        <v>0.1663872648171079</v>
       </c>
       <c r="C62">
-        <v>-51.60657833774337</v>
+        <v>-169.2172943169466</v>
       </c>
       <c r="D62">
-        <v>377.6534216622566</v>
+        <v>267.5087056830533</v>
       </c>
       <c r="E62">
-        <v>-28.94000000000005</v>
+        <v>-21.47400000000005</v>
       </c>
       <c r="F62">
-        <v>447.9599999999999</v>
+        <v>455.4259999999999</v>
       </c>
       <c r="G62">
         <v>18.7</v>
@@ -6359,45 +6359,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M62">
-        <v>65.76052799999999</v>
+        <v>91.44954079999999</v>
       </c>
       <c r="N62">
-        <v>-12.39386133333332</v>
+        <v>-38.08287413333332</v>
       </c>
       <c r="O62">
-        <v>-2.602710879999997</v>
+        <v>-7.997403567999997</v>
       </c>
       <c r="P62">
-        <v>-9.791150453333323</v>
+        <v>-30.08547056533332</v>
       </c>
       <c r="Q62">
-        <v>23.50884954666667</v>
+        <v>3.214529434666673</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1453700878801082</v>
+        <v>0.1510512309218983</v>
       </c>
       <c r="T62">
-        <v>1.678894726198471</v>
+        <v>1.774686959535909</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1704213810448724</v>
+        <v>0.1225484557053129</v>
       </c>
       <c r="W62">
-        <v>0.1217821412626127</v>
+        <v>0.1761922700943732</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8115303859279639</v>
+        <v>0.5835640747872042</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1663872648171079</v>
+        <v>0.167937264817108</v>
       </c>
       <c r="C63">
-        <v>-169.2172943169466</v>
+        <v>-180.0781508697737</v>
       </c>
       <c r="D63">
-        <v>267.5087056830533</v>
+        <v>264.1138491302262</v>
       </c>
       <c r="E63">
-        <v>-21.47400000000005</v>
+        <v>-14.00800000000004</v>
       </c>
       <c r="F63">
-        <v>455.4259999999999</v>
+        <v>462.8919999999999</v>
       </c>
       <c r="G63">
         <v>18.7</v>
@@ -6441,37 +6441,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M63">
-        <v>91.44954079999999</v>
+        <v>92.94871359999999</v>
       </c>
       <c r="N63">
-        <v>-38.08287413333332</v>
+        <v>-39.58204693333332</v>
       </c>
       <c r="O63">
-        <v>-7.997403567999997</v>
+        <v>-8.312229855999997</v>
       </c>
       <c r="P63">
-        <v>-30.08547056533332</v>
+        <v>-31.26981707733332</v>
       </c>
       <c r="Q63">
-        <v>3.214529434666673</v>
+        <v>2.030182922666675</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1510512309218983</v>
+        <v>0.153821000156685</v>
       </c>
       <c r="T63">
-        <v>1.774686959535909</v>
+        <v>1.821389247944749</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1225484557053129</v>
+        <v>0.1205718677100659</v>
       </c>
       <c r="W63">
-        <v>0.1761922700943732</v>
+        <v>0.1765891689638188</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5835640747872042</v>
+        <v>0.5741517510003138</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.167937264817108</v>
+        <v>0.1694872648171079</v>
       </c>
       <c r="C64">
-        <v>-180.0781508697737</v>
+        <v>-190.8539214169451</v>
       </c>
       <c r="D64">
-        <v>264.1138491302262</v>
+        <v>260.8040785830549</v>
       </c>
       <c r="E64">
-        <v>-14.00800000000004</v>
+        <v>-6.54200000000003</v>
       </c>
       <c r="F64">
-        <v>462.8919999999999</v>
+        <v>470.3579999999999</v>
       </c>
       <c r="G64">
         <v>18.7</v>
@@ -6523,37 +6523,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M64">
-        <v>92.94871359999999</v>
+        <v>94.44788639999999</v>
       </c>
       <c r="N64">
-        <v>-39.58204693333332</v>
+        <v>-41.08121973333331</v>
       </c>
       <c r="O64">
-        <v>-8.312229855999997</v>
+        <v>-8.627056143999996</v>
       </c>
       <c r="P64">
-        <v>-31.26981707733332</v>
+        <v>-32.45416358933332</v>
       </c>
       <c r="Q64">
-        <v>2.030182922666675</v>
+        <v>0.8458364106666778</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.153821000156685</v>
+        <v>0.1567404866474063</v>
       </c>
       <c r="T64">
-        <v>1.821389247944749</v>
+        <v>1.870615984375688</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1205718677100659</v>
+        <v>0.1186580285400649</v>
       </c>
       <c r="W64">
-        <v>0.1765891689638188</v>
+        <v>0.176973467869155</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5741517510003138</v>
+        <v>0.565038231143166</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1694872648171079</v>
+        <v>0.171037264817108</v>
       </c>
       <c r="C65">
-        <v>-190.8539214169451</v>
+        <v>-201.5477651613297</v>
       </c>
       <c r="D65">
-        <v>260.8040785830549</v>
+        <v>257.5762348386703</v>
       </c>
       <c r="E65">
-        <v>-6.54200000000003</v>
+        <v>0.9239999999999782</v>
       </c>
       <c r="F65">
-        <v>470.3579999999999</v>
+        <v>477.824</v>
       </c>
       <c r="G65">
         <v>18.7</v>
@@ -6605,37 +6605,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M65">
-        <v>94.44788639999999</v>
+        <v>95.9470592</v>
       </c>
       <c r="N65">
-        <v>-41.08121973333331</v>
+        <v>-42.58039253333332</v>
       </c>
       <c r="O65">
-        <v>-8.627056143999996</v>
+        <v>-8.941882431999998</v>
       </c>
       <c r="P65">
-        <v>-32.45416358933332</v>
+        <v>-33.63851010133332</v>
       </c>
       <c r="Q65">
-        <v>0.8458364106666778</v>
+        <v>-0.3385101013333269</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1567404866474063</v>
+        <v>0.1598221668320564</v>
       </c>
       <c r="T65">
-        <v>1.870615984375688</v>
+        <v>1.922577539497235</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1186580285400649</v>
+        <v>0.1168039968441263</v>
       </c>
       <c r="W65">
-        <v>0.176973467869155</v>
+        <v>0.1773457574336994</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.565038231143166</v>
+        <v>0.556209508781554</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.171037264817108</v>
+        <v>0.172587264817108</v>
       </c>
       <c r="C66">
-        <v>-201.5477651613297</v>
+        <v>-212.1626868182157</v>
       </c>
       <c r="D66">
-        <v>257.5762348386703</v>
+        <v>254.4273131817843</v>
       </c>
       <c r="E66">
-        <v>0.9239999999999782</v>
+        <v>8.389999999999986</v>
       </c>
       <c r="F66">
-        <v>477.824</v>
+        <v>485.29</v>
       </c>
       <c r="G66">
         <v>18.7</v>
@@ -6687,37 +6687,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M66">
-        <v>95.9470592</v>
+        <v>97.44623199999999</v>
       </c>
       <c r="N66">
-        <v>-42.58039253333332</v>
+        <v>-44.07956533333332</v>
       </c>
       <c r="O66">
-        <v>-8.941882431999998</v>
+        <v>-9.256708719999997</v>
       </c>
       <c r="P66">
-        <v>-33.63851010133332</v>
+        <v>-34.82285661333332</v>
       </c>
       <c r="Q66">
-        <v>-0.3385101013333269</v>
+        <v>-1.522856613333325</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1598221668320564</v>
+        <v>0.1630799430272581</v>
       </c>
       <c r="T66">
-        <v>1.922577539497235</v>
+        <v>1.977508326340014</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1168039968441263</v>
+        <v>0.1150070122772936</v>
       </c>
       <c r="W66">
-        <v>0.1773457574336994</v>
+        <v>0.1777065919347194</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.556209508781554</v>
+        <v>0.5476524394156839</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.172587264817108</v>
+        <v>0.174137264817108</v>
       </c>
       <c r="C67">
-        <v>-212.1626868182157</v>
+        <v>-222.70154594447</v>
       </c>
       <c r="D67">
-        <v>254.4273131817843</v>
+        <v>251.35445405553</v>
       </c>
       <c r="E67">
-        <v>8.389999999999986</v>
+        <v>15.85599999999999</v>
       </c>
       <c r="F67">
-        <v>485.29</v>
+        <v>492.756</v>
       </c>
       <c r="G67">
         <v>18.7</v>
@@ -6769,37 +6769,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M67">
-        <v>97.44623199999999</v>
+        <v>98.94540479999999</v>
       </c>
       <c r="N67">
-        <v>-44.07956533333332</v>
+        <v>-45.57873813333332</v>
       </c>
       <c r="O67">
-        <v>-9.256708719999997</v>
+        <v>-9.571535007999996</v>
       </c>
       <c r="P67">
-        <v>-34.82285661333332</v>
+        <v>-36.00720312533332</v>
       </c>
       <c r="Q67">
-        <v>-1.522856613333325</v>
+        <v>-2.707203125333322</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1630799430272581</v>
+        <v>0.166529353116295</v>
       </c>
       <c r="T67">
-        <v>1.977508326340014</v>
+        <v>2.035670335938249</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1150070122772936</v>
+        <v>0.1132644817882437</v>
       </c>
       <c r="W67">
-        <v>0.1777065919347194</v>
+        <v>0.1780564920569206</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5476524394156839</v>
+        <v>0.539354675182113</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.174137264817108</v>
+        <v>0.175687264817108</v>
       </c>
       <c r="C68">
-        <v>-222.70154594447</v>
+        <v>-233.1670655997239</v>
       </c>
       <c r="D68">
-        <v>251.35445405553</v>
+        <v>248.3549344002761</v>
       </c>
       <c r="E68">
-        <v>15.85599999999999</v>
+        <v>23.322</v>
       </c>
       <c r="F68">
-        <v>492.756</v>
+        <v>500.222</v>
       </c>
       <c r="G68">
         <v>18.7</v>
@@ -6851,37 +6851,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M68">
-        <v>98.94540479999999</v>
+        <v>100.4445776</v>
       </c>
       <c r="N68">
-        <v>-45.57873813333332</v>
+        <v>-47.07791093333333</v>
       </c>
       <c r="O68">
-        <v>-9.571535007999996</v>
+        <v>-9.886361295999999</v>
       </c>
       <c r="P68">
-        <v>-36.00720312533332</v>
+        <v>-37.19154963733333</v>
       </c>
       <c r="Q68">
-        <v>-2.707203125333322</v>
+        <v>-3.891549637333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.166529353116295</v>
+        <v>0.1701878183622434</v>
       </c>
       <c r="T68">
-        <v>2.035670335938249</v>
+        <v>2.097357315815166</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1132644817882437</v>
+        <v>0.1115739671346878</v>
       </c>
       <c r="W68">
-        <v>0.1780564920569206</v>
+        <v>0.1783959473993547</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.539354675182113</v>
+        <v>0.5313046054032754</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.175687264817108</v>
+        <v>0.177237264817108</v>
       </c>
       <c r="C69">
-        <v>-233.1670655997239</v>
+        <v>-243.5618403947266</v>
       </c>
       <c r="D69">
-        <v>248.3549344002761</v>
+        <v>245.4261596052734</v>
       </c>
       <c r="E69">
-        <v>23.322</v>
+        <v>30.78800000000001</v>
       </c>
       <c r="F69">
-        <v>500.222</v>
+        <v>507.688</v>
       </c>
       <c r="G69">
         <v>18.7</v>
@@ -6933,37 +6933,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M69">
-        <v>100.4445776</v>
+        <v>101.9437504</v>
       </c>
       <c r="N69">
-        <v>-47.07791093333333</v>
+        <v>-48.57708373333332</v>
       </c>
       <c r="O69">
-        <v>-9.886361295999999</v>
+        <v>-10.201187584</v>
       </c>
       <c r="P69">
-        <v>-37.19154963733333</v>
+        <v>-38.37589614933333</v>
       </c>
       <c r="Q69">
-        <v>-3.891549637333334</v>
+        <v>-5.075896149333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1701878183622434</v>
+        <v>0.1740749376860635</v>
       </c>
       <c r="T69">
-        <v>2.097357315815166</v>
+        <v>2.16289973193439</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1115739671346878</v>
+        <v>0.1099331735003542</v>
       </c>
       <c r="W69">
-        <v>0.1783959473993547</v>
+        <v>0.1787254187611289</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5313046054032754</v>
+        <v>0.523491302382639</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.177237264817108</v>
+        <v>0.178787264817108</v>
       </c>
       <c r="C70">
-        <v>-243.5618403947266</v>
+        <v>-253.8883439768653</v>
       </c>
       <c r="D70">
-        <v>245.4261596052734</v>
+        <v>242.5656560231347</v>
       </c>
       <c r="E70">
-        <v>30.78800000000001</v>
+        <v>38.25400000000002</v>
       </c>
       <c r="F70">
-        <v>507.688</v>
+        <v>515.154</v>
       </c>
       <c r="G70">
         <v>18.7</v>
@@ -7015,37 +7015,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M70">
-        <v>101.9437504</v>
+        <v>103.4429232</v>
       </c>
       <c r="N70">
-        <v>-48.57708373333332</v>
+        <v>-50.07625653333332</v>
       </c>
       <c r="O70">
-        <v>-10.201187584</v>
+        <v>-10.516013872</v>
       </c>
       <c r="P70">
-        <v>-38.37589614933333</v>
+        <v>-39.56024266133333</v>
       </c>
       <c r="Q70">
-        <v>-5.075896149333332</v>
+        <v>-6.260242661333329</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1740749376860635</v>
+        <v>0.178212838901743</v>
       </c>
       <c r="T70">
-        <v>2.16289973193439</v>
+        <v>2.232670691029048</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1099331735003542</v>
+        <v>0.1083399391017983</v>
       </c>
       <c r="W70">
-        <v>0.1787254187611289</v>
+        <v>0.1790453402283589</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.523491302382639</v>
+        <v>0.5159044719133254</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.178787264817108</v>
+        <v>0.1803372648171079</v>
       </c>
       <c r="C71">
-        <v>-253.8883439768653</v>
+        <v>-264.1489359982428</v>
       </c>
       <c r="D71">
-        <v>242.5656560231347</v>
+        <v>239.7710640017572</v>
       </c>
       <c r="E71">
-        <v>38.25400000000002</v>
+        <v>45.72000000000003</v>
       </c>
       <c r="F71">
-        <v>515.154</v>
+        <v>522.62</v>
       </c>
       <c r="G71">
         <v>18.7</v>
@@ -7097,37 +7097,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M71">
-        <v>103.4429232</v>
+        <v>104.942096</v>
       </c>
       <c r="N71">
-        <v>-50.07625653333332</v>
+        <v>-51.57542933333333</v>
       </c>
       <c r="O71">
-        <v>-10.516013872</v>
+        <v>-10.83084016</v>
       </c>
       <c r="P71">
-        <v>-39.56024266133333</v>
+        <v>-40.74458917333333</v>
       </c>
       <c r="Q71">
-        <v>-6.260242661333329</v>
+        <v>-7.444589173333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.178212838901743</v>
+        <v>0.1826266001984678</v>
       </c>
       <c r="T71">
-        <v>2.232670691029048</v>
+        <v>2.307093047396683</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1083399391017983</v>
+        <v>0.1067922256860584</v>
       </c>
       <c r="W71">
-        <v>0.1790453402283589</v>
+        <v>0.1793561210822395</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5159044719133254</v>
+        <v>0.5085344080288492</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1803372648171079</v>
+        <v>0.181887264817108</v>
       </c>
       <c r="C72">
-        <v>-264.1489359982428</v>
+        <v>-274.3458686075668</v>
       </c>
       <c r="D72">
-        <v>239.7710640017572</v>
+        <v>237.0401313924332</v>
       </c>
       <c r="E72">
-        <v>45.72000000000003</v>
+        <v>53.18600000000004</v>
       </c>
       <c r="F72">
-        <v>522.62</v>
+        <v>530.086</v>
       </c>
       <c r="G72">
         <v>18.7</v>
@@ -7179,37 +7179,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M72">
-        <v>104.942096</v>
+        <v>106.4412688</v>
       </c>
       <c r="N72">
-        <v>-51.57542933333333</v>
+        <v>-53.07460213333333</v>
       </c>
       <c r="O72">
-        <v>-10.83084016</v>
+        <v>-11.145666448</v>
       </c>
       <c r="P72">
-        <v>-40.74458917333333</v>
+        <v>-41.92893568533333</v>
       </c>
       <c r="Q72">
-        <v>-7.444589173333334</v>
+        <v>-8.628935685333332</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1826266001984678</v>
+        <v>0.1873447588260012</v>
       </c>
       <c r="T72">
-        <v>2.307093047396683</v>
+        <v>2.386647980065534</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1067922256860584</v>
+        <v>0.1052881098313251</v>
       </c>
       <c r="W72">
-        <v>0.1793561210822395</v>
+        <v>0.1796581475458699</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5085344080288492</v>
+        <v>0.5013719515777387</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1818872648171079</v>
+        <v>0.2091295273225834</v>
       </c>
       <c r="C73">
-        <v>-274.3458686075665</v>
+        <v>-321.3485622451548</v>
       </c>
       <c r="D73">
-        <v>237.0401313924334</v>
+        <v>197.5034377548452</v>
       </c>
       <c r="E73">
-        <v>53.18599999999992</v>
+        <v>60.65199999999993</v>
       </c>
       <c r="F73">
-        <v>530.0859999999999</v>
+        <v>537.5519999999999</v>
       </c>
       <c r="G73">
         <v>18.7</v>
@@ -7261,45 +7261,45 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M73">
-        <v>106.4412688</v>
+        <v>126.7547616</v>
       </c>
       <c r="N73">
-        <v>-53.07460213333331</v>
+        <v>-73.38809493333331</v>
       </c>
       <c r="O73">
-        <v>-11.145666448</v>
+        <v>-15.41149993599999</v>
       </c>
       <c r="P73">
-        <v>-41.92893568533331</v>
+        <v>-57.97659499733332</v>
       </c>
       <c r="Q73">
-        <v>-8.628935685333317</v>
+        <v>-24.67659499733332</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1873447588260011</v>
+        <v>0.1941580091607706</v>
       </c>
       <c r="T73">
-        <v>2.386647980065533</v>
+        <v>2.501529168772405</v>
       </c>
       <c r="U73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1052881098313252</v>
+        <v>0.08841482448892872</v>
       </c>
       <c r="W73">
-        <v>0.1796581475458699</v>
+        <v>0.2149517843855106</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5013719515777388</v>
+        <v>0.4210229737568035</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2091295273225834</v>
+        <v>0.2110295273225834</v>
       </c>
       <c r="C74">
-        <v>-321.3485622451548</v>
+        <v>-331.0856849543638</v>
       </c>
       <c r="D74">
-        <v>197.5034377548452</v>
+        <v>195.2323150456361</v>
       </c>
       <c r="E74">
-        <v>60.65199999999993</v>
+        <v>68.11799999999994</v>
       </c>
       <c r="F74">
-        <v>537.5519999999999</v>
+        <v>545.0179999999999</v>
       </c>
       <c r="G74">
         <v>18.7</v>
@@ -7343,37 +7343,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M74">
-        <v>126.7547616</v>
+        <v>128.5152444</v>
       </c>
       <c r="N74">
-        <v>-73.38809493333331</v>
+        <v>-75.1485777333333</v>
       </c>
       <c r="O74">
-        <v>-15.41149993599999</v>
+        <v>-15.78120132399999</v>
       </c>
       <c r="P74">
-        <v>-57.97659499733332</v>
+        <v>-59.3673764093333</v>
       </c>
       <c r="Q74">
-        <v>-24.67659499733332</v>
+        <v>-26.06737640933331</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1941580091607706</v>
+        <v>0.1996527502407991</v>
       </c>
       <c r="T74">
-        <v>2.501529168772405</v>
+        <v>2.594178397245456</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08841482448892872</v>
+        <v>0.08720366250962834</v>
       </c>
       <c r="W74">
-        <v>0.2149517843855106</v>
+        <v>0.2152373763802297</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4210229737568035</v>
+        <v>0.415255535760135</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2110295273225834</v>
+        <v>0.2129295273225834</v>
       </c>
       <c r="C75">
-        <v>-331.0856849543638</v>
+        <v>-340.771169473522</v>
       </c>
       <c r="D75">
-        <v>195.2323150456361</v>
+        <v>193.0128305264779</v>
       </c>
       <c r="E75">
-        <v>68.11799999999994</v>
+        <v>75.58399999999995</v>
       </c>
       <c r="F75">
-        <v>545.0179999999999</v>
+        <v>552.4839999999999</v>
       </c>
       <c r="G75">
         <v>18.7</v>
@@ -7425,37 +7425,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M75">
-        <v>128.5152444</v>
+        <v>130.2757272</v>
       </c>
       <c r="N75">
-        <v>-75.1485777333333</v>
+        <v>-76.9090605333333</v>
       </c>
       <c r="O75">
-        <v>-15.78120132399999</v>
+        <v>-16.15090271199999</v>
       </c>
       <c r="P75">
-        <v>-59.3673764093333</v>
+        <v>-60.75815782133331</v>
       </c>
       <c r="Q75">
-        <v>-26.06737640933331</v>
+        <v>-27.45815782133332</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1996527502407991</v>
+        <v>0.2055701637115991</v>
       </c>
       <c r="T75">
-        <v>2.594178397245456</v>
+        <v>2.693954489447205</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08720366250962834</v>
+        <v>0.0860252346378766</v>
       </c>
       <c r="W75">
-        <v>0.2152373763802297</v>
+        <v>0.2155152496723887</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.415255535760135</v>
+        <v>0.409643974466079</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2129295273225834</v>
+        <v>0.2148295273225834</v>
       </c>
       <c r="C76">
-        <v>-340.771169473522</v>
+        <v>-350.4067571414828</v>
       </c>
       <c r="D76">
-        <v>193.0128305264779</v>
+        <v>190.8432428585171</v>
       </c>
       <c r="E76">
-        <v>75.58399999999995</v>
+        <v>83.04999999999995</v>
       </c>
       <c r="F76">
-        <v>552.4839999999999</v>
+        <v>559.9499999999999</v>
       </c>
       <c r="G76">
         <v>18.7</v>
@@ -7507,37 +7507,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M76">
-        <v>130.2757272</v>
+        <v>132.03621</v>
       </c>
       <c r="N76">
-        <v>-76.9090605333333</v>
+        <v>-78.66954333333331</v>
       </c>
       <c r="O76">
-        <v>-16.15090271199999</v>
+        <v>-16.52060409999999</v>
       </c>
       <c r="P76">
-        <v>-60.75815782133331</v>
+        <v>-62.14893923333332</v>
       </c>
       <c r="Q76">
-        <v>-27.45815782133332</v>
+        <v>-28.84893923333332</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2055701637115991</v>
+        <v>0.2119609702600631</v>
       </c>
       <c r="T76">
-        <v>2.693954489447205</v>
+        <v>2.801712669025093</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0860252346378766</v>
+        <v>0.08487823150937159</v>
       </c>
       <c r="W76">
-        <v>0.2155152496723887</v>
+        <v>0.2157857130100902</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.409643974466079</v>
+        <v>0.4041820548065314</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2148295273225834</v>
+        <v>0.2167295273225834</v>
       </c>
       <c r="C77">
-        <v>-350.4067571414828</v>
+        <v>-359.9941118723532</v>
       </c>
       <c r="D77">
-        <v>190.8432428585171</v>
+        <v>188.7218881276468</v>
       </c>
       <c r="E77">
-        <v>83.04999999999995</v>
+        <v>90.51599999999996</v>
       </c>
       <c r="F77">
-        <v>559.9499999999999</v>
+        <v>567.4159999999999</v>
       </c>
       <c r="G77">
         <v>18.7</v>
@@ -7589,37 +7589,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M77">
-        <v>132.03621</v>
+        <v>133.7966928</v>
       </c>
       <c r="N77">
-        <v>-78.66954333333331</v>
+        <v>-80.43002613333331</v>
       </c>
       <c r="O77">
-        <v>-16.52060409999999</v>
+        <v>-16.890305488</v>
       </c>
       <c r="P77">
-        <v>-62.14893923333332</v>
+        <v>-63.53972064533332</v>
       </c>
       <c r="Q77">
-        <v>-28.84893923333332</v>
+        <v>-30.23972064533332</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2119609702600631</v>
+        <v>0.218884344020899</v>
       </c>
       <c r="T77">
-        <v>2.801712669025093</v>
+        <v>2.918450696901139</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08487823150937159</v>
+        <v>0.08376141267372195</v>
       </c>
       <c r="W77">
-        <v>0.2157857130100902</v>
+        <v>0.2160490588915364</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4041820548065314</v>
+        <v>0.3988638698748664</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2167295273225834</v>
+        <v>0.2186295273225834</v>
       </c>
       <c r="C78">
-        <v>-359.9941118723532</v>
+        <v>-369.5348244113353</v>
       </c>
       <c r="D78">
-        <v>188.7218881276468</v>
+        <v>186.6471755886647</v>
       </c>
       <c r="E78">
-        <v>90.51599999999996</v>
+        <v>97.98199999999997</v>
       </c>
       <c r="F78">
-        <v>567.4159999999999</v>
+        <v>574.8819999999999</v>
       </c>
       <c r="G78">
         <v>18.7</v>
@@ -7671,37 +7671,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M78">
-        <v>133.7966928</v>
+        <v>135.5571756</v>
       </c>
       <c r="N78">
-        <v>-80.43002613333331</v>
+        <v>-82.19050893333332</v>
       </c>
       <c r="O78">
-        <v>-16.890305488</v>
+        <v>-17.26000687599999</v>
       </c>
       <c r="P78">
-        <v>-63.53972064533332</v>
+        <v>-64.93050205733333</v>
       </c>
       <c r="Q78">
-        <v>-30.23972064533332</v>
+        <v>-31.63050205733333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.218884344020899</v>
+        <v>0.2264097502826772</v>
       </c>
       <c r="T78">
-        <v>2.918450696901139</v>
+        <v>3.04533985763597</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08376141267372195</v>
+        <v>0.08267360211951776</v>
       </c>
       <c r="W78">
-        <v>0.2160490588915364</v>
+        <v>0.2163055646202177</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3988638698748664</v>
+        <v>0.3936838196167513</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2186295273225834</v>
+        <v>0.2205295273225834</v>
       </c>
       <c r="C79">
-        <v>-369.5348244113353</v>
+        <v>-379.0304163129019</v>
       </c>
       <c r="D79">
-        <v>186.6471755886647</v>
+        <v>184.6175836870981</v>
       </c>
       <c r="E79">
-        <v>97.98199999999997</v>
+        <v>105.448</v>
       </c>
       <c r="F79">
-        <v>574.8819999999999</v>
+        <v>582.348</v>
       </c>
       <c r="G79">
         <v>18.7</v>
@@ -7753,37 +7753,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M79">
-        <v>135.5571756</v>
+        <v>137.3176584</v>
       </c>
       <c r="N79">
-        <v>-82.19050893333332</v>
+        <v>-83.95099173333332</v>
       </c>
       <c r="O79">
-        <v>-17.26000687599999</v>
+        <v>-17.629708264</v>
       </c>
       <c r="P79">
-        <v>-64.93050205733333</v>
+        <v>-66.32128346933332</v>
       </c>
       <c r="Q79">
-        <v>-31.63050205733333</v>
+        <v>-33.02128346933333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2264097502826772</v>
+        <v>0.2346192843864353</v>
       </c>
       <c r="T79">
-        <v>3.04533985763597</v>
+        <v>3.183764396619424</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08267360211951776</v>
+        <v>0.08161368414362651</v>
       </c>
       <c r="W79">
-        <v>0.2163055646202177</v>
+        <v>0.2165554932789329</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3936838196167513</v>
+        <v>0.3886365911601263</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2205295273225834</v>
+        <v>0.2224295273225834</v>
       </c>
       <c r="C80">
-        <v>-379.0304163129019</v>
+        <v>-388.4823436622112</v>
       </c>
       <c r="D80">
-        <v>184.6175836870981</v>
+        <v>182.6316563377888</v>
       </c>
       <c r="E80">
-        <v>105.448</v>
+        <v>112.914</v>
       </c>
       <c r="F80">
-        <v>582.348</v>
+        <v>589.814</v>
       </c>
       <c r="G80">
         <v>18.7</v>
@@ -7835,37 +7835,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M80">
-        <v>137.3176584</v>
+        <v>139.0781412</v>
       </c>
       <c r="N80">
-        <v>-83.95099173333332</v>
+        <v>-85.71147453333333</v>
       </c>
       <c r="O80">
-        <v>-17.629708264</v>
+        <v>-17.999409652</v>
       </c>
       <c r="P80">
-        <v>-66.32128346933332</v>
+        <v>-67.71206488133333</v>
       </c>
       <c r="Q80">
-        <v>-33.02128346933333</v>
+        <v>-34.41206488133334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2346192843864353</v>
+        <v>0.2436106788810275</v>
       </c>
       <c r="T80">
-        <v>3.183764396619424</v>
+        <v>3.335372225029873</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08161368414362651</v>
+        <v>0.08058059953421351</v>
       </c>
       <c r="W80">
-        <v>0.2165554932789329</v>
+        <v>0.2167990946298325</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3886365911601263</v>
+        <v>0.383717140639112</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2224295273225834</v>
+        <v>0.2243295273225834</v>
       </c>
       <c r="C81">
-        <v>-388.4823436622112</v>
+        <v>-397.8920005588925</v>
       </c>
       <c r="D81">
-        <v>182.6316563377888</v>
+        <v>180.6879994411075</v>
       </c>
       <c r="E81">
-        <v>112.914</v>
+        <v>120.38</v>
       </c>
       <c r="F81">
-        <v>589.814</v>
+        <v>597.28</v>
       </c>
       <c r="G81">
         <v>18.7</v>
@@ -7917,37 +7917,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M81">
-        <v>139.0781412</v>
+        <v>140.838624</v>
       </c>
       <c r="N81">
-        <v>-85.71147453333333</v>
+        <v>-87.47195733333334</v>
       </c>
       <c r="O81">
-        <v>-17.999409652</v>
+        <v>-18.36911104</v>
       </c>
       <c r="P81">
-        <v>-67.71206488133333</v>
+        <v>-69.10284629333333</v>
       </c>
       <c r="Q81">
-        <v>-34.41206488133334</v>
+        <v>-35.80284629333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2436106788810275</v>
+        <v>0.2535012128250788</v>
       </c>
       <c r="T81">
-        <v>3.335372225029873</v>
+        <v>3.502140836281367</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08058059953421351</v>
+        <v>0.07957334204003584</v>
       </c>
       <c r="W81">
-        <v>0.2167990946298325</v>
+        <v>0.2170366059469596</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.383717140639112</v>
+        <v>0.378920676381123</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2243295273225834</v>
+        <v>0.2262295273225834</v>
       </c>
       <c r="C82">
-        <v>-397.8920005588925</v>
+        <v>-407.2607223807166</v>
       </c>
       <c r="D82">
-        <v>180.6879994411075</v>
+        <v>178.7852776192833</v>
       </c>
       <c r="E82">
-        <v>120.38</v>
+        <v>127.846</v>
       </c>
       <c r="F82">
-        <v>597.28</v>
+        <v>604.746</v>
       </c>
       <c r="G82">
         <v>18.7</v>
@@ -7999,37 +7999,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M82">
-        <v>140.838624</v>
+        <v>142.5991068</v>
       </c>
       <c r="N82">
-        <v>-87.47195733333334</v>
+        <v>-89.23244013333334</v>
       </c>
       <c r="O82">
-        <v>-18.36911104</v>
+        <v>-18.738812428</v>
       </c>
       <c r="P82">
-        <v>-69.10284629333333</v>
+        <v>-70.49362770533334</v>
       </c>
       <c r="Q82">
-        <v>-35.80284629333333</v>
+        <v>-37.19362770533334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2535012128250788</v>
+        <v>0.2644328556053461</v>
       </c>
       <c r="T82">
-        <v>3.502140836281367</v>
+        <v>3.686464038190913</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07957334204003584</v>
+        <v>0.07859095510126997</v>
       </c>
       <c r="W82">
-        <v>0.2170366059469596</v>
+        <v>0.2172682527871205</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.378920676381123</v>
+        <v>0.3742426433393807</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2262295273225834</v>
+        <v>0.2281295273225834</v>
       </c>
       <c r="C83">
-        <v>-407.2607223807166</v>
+        <v>-416.5897888432082</v>
       </c>
       <c r="D83">
-        <v>178.7852776192833</v>
+        <v>176.9222111567917</v>
       </c>
       <c r="E83">
-        <v>127.846</v>
+        <v>135.312</v>
       </c>
       <c r="F83">
-        <v>604.746</v>
+        <v>612.212</v>
       </c>
       <c r="G83">
         <v>18.7</v>
@@ -8081,37 +8081,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M83">
-        <v>142.5991068</v>
+        <v>144.3595896</v>
       </c>
       <c r="N83">
-        <v>-89.23244013333334</v>
+        <v>-90.99292293333332</v>
       </c>
       <c r="O83">
-        <v>-18.738812428</v>
+        <v>-19.10851381599999</v>
       </c>
       <c r="P83">
-        <v>-70.49362770533334</v>
+        <v>-71.88440911733332</v>
       </c>
       <c r="Q83">
-        <v>-37.19362770533334</v>
+        <v>-38.58440911733332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2644328556053461</v>
+        <v>0.2765791253611987</v>
       </c>
       <c r="T83">
-        <v>3.686464038190913</v>
+        <v>3.891267595868186</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07859095510126997</v>
+        <v>0.07763252881954717</v>
       </c>
       <c r="W83">
-        <v>0.2172682527871205</v>
+        <v>0.2174942497043508</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3742426433393807</v>
+        <v>0.3696787086645104</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2281295273225834</v>
+        <v>0.2300295273225834</v>
       </c>
       <c r="C84">
-        <v>-416.5897888432082</v>
+        <v>-425.8804268699308</v>
       </c>
       <c r="D84">
-        <v>176.9222111567917</v>
+        <v>175.0975731300692</v>
       </c>
       <c r="E84">
-        <v>135.312</v>
+        <v>142.778</v>
       </c>
       <c r="F84">
-        <v>612.212</v>
+        <v>619.678</v>
       </c>
       <c r="G84">
         <v>18.7</v>
@@ -8163,37 +8163,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M84">
-        <v>144.3595896</v>
+        <v>146.1200724</v>
       </c>
       <c r="N84">
-        <v>-90.99292293333332</v>
+        <v>-92.75340573333332</v>
       </c>
       <c r="O84">
-        <v>-19.10851381599999</v>
+        <v>-19.478215204</v>
       </c>
       <c r="P84">
-        <v>-71.88440911733332</v>
+        <v>-73.27519052933333</v>
       </c>
       <c r="Q84">
-        <v>-38.58440911733332</v>
+        <v>-39.97519052933333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2765791253611987</v>
+        <v>0.2901543680295046</v>
       </c>
       <c r="T84">
-        <v>3.891267595868186</v>
+        <v>4.120165689742786</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07763252881954717</v>
+        <v>0.0766971971470225</v>
       </c>
       <c r="W84">
-        <v>0.2174942497043508</v>
+        <v>0.2177148009127321</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3696787086645104</v>
+        <v>0.3652247483191547</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2300295273225834</v>
+        <v>0.2319295273225834</v>
       </c>
       <c r="C85">
-        <v>-425.8804268699308</v>
+        <v>-435.1338132869744</v>
       </c>
       <c r="D85">
-        <v>175.0975731300692</v>
+        <v>173.3101867130256</v>
       </c>
       <c r="E85">
-        <v>142.778</v>
+        <v>150.244</v>
       </c>
       <c r="F85">
-        <v>619.678</v>
+        <v>627.144</v>
       </c>
       <c r="G85">
         <v>18.7</v>
@@ -8245,37 +8245,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M85">
-        <v>146.1200724</v>
+        <v>147.8805552</v>
       </c>
       <c r="N85">
-        <v>-92.75340573333332</v>
+        <v>-94.51388853333333</v>
       </c>
       <c r="O85">
-        <v>-19.478215204</v>
+        <v>-19.847916592</v>
       </c>
       <c r="P85">
-        <v>-73.27519052933333</v>
+        <v>-74.66597194133334</v>
       </c>
       <c r="Q85">
-        <v>-39.97519052933333</v>
+        <v>-41.36597194133334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2901543680295046</v>
+        <v>0.3054265160313487</v>
       </c>
       <c r="T85">
-        <v>4.120165689742786</v>
+        <v>4.377676045351711</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0766971971470225</v>
+        <v>0.07578413527622462</v>
       </c>
       <c r="W85">
-        <v>0.2177148009127321</v>
+        <v>0.2179301009018662</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3652247483191547</v>
+        <v>0.3608768346486887</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2319295273225834</v>
+        <v>0.2338295273225834</v>
       </c>
       <c r="C86">
-        <v>-435.1338132869743</v>
+        <v>-444.3510773540791</v>
       </c>
       <c r="D86">
-        <v>173.3101867130256</v>
+        <v>171.5589226459208</v>
       </c>
       <c r="E86">
-        <v>150.2439999999999</v>
+        <v>157.7099999999999</v>
       </c>
       <c r="F86">
-        <v>627.1439999999999</v>
+        <v>634.6099999999999</v>
       </c>
       <c r="G86">
         <v>18.7</v>
@@ -8327,37 +8327,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M86">
-        <v>147.8805552</v>
+        <v>149.641038</v>
       </c>
       <c r="N86">
-        <v>-94.5138885333333</v>
+        <v>-96.27437133333331</v>
       </c>
       <c r="O86">
-        <v>-19.84791659199999</v>
+        <v>-20.21761797999999</v>
       </c>
       <c r="P86">
-        <v>-74.66597194133331</v>
+        <v>-76.05675335333331</v>
       </c>
       <c r="Q86">
-        <v>-41.36597194133331</v>
+        <v>-42.75675335333331</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3054265160313485</v>
+        <v>0.3227349504334384</v>
       </c>
       <c r="T86">
-        <v>4.377676045351707</v>
+        <v>4.669521115041821</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07578413527622463</v>
+        <v>0.0748925572141514</v>
       </c>
       <c r="W86">
-        <v>0.2179301009018662</v>
+        <v>0.2181403350089031</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3608768346486887</v>
+        <v>0.3566312248292923</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2338295273225834</v>
+        <v>0.2357295273225834</v>
       </c>
       <c r="C87">
-        <v>-444.3510773540791</v>
+        <v>-453.5333031438354</v>
       </c>
       <c r="D87">
-        <v>171.5589226459208</v>
+        <v>169.8426968561645</v>
       </c>
       <c r="E87">
-        <v>157.7099999999999</v>
+        <v>165.1759999999999</v>
       </c>
       <c r="F87">
-        <v>634.6099999999999</v>
+        <v>642.0759999999999</v>
       </c>
       <c r="G87">
         <v>18.7</v>
@@ -8409,37 +8409,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M87">
-        <v>149.641038</v>
+        <v>151.4015208</v>
       </c>
       <c r="N87">
-        <v>-96.27437133333331</v>
+        <v>-98.03485413333331</v>
       </c>
       <c r="O87">
-        <v>-20.21761797999999</v>
+        <v>-20.587319368</v>
       </c>
       <c r="P87">
-        <v>-76.05675335333331</v>
+        <v>-77.44753476533332</v>
       </c>
       <c r="Q87">
-        <v>-42.75675335333331</v>
+        <v>-44.14753476533332</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3227349504334384</v>
+        <v>0.3425160183215412</v>
       </c>
       <c r="T87">
-        <v>4.669521115041821</v>
+        <v>5.003058337544809</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0748925572141514</v>
+        <v>0.07402171352561475</v>
       </c>
       <c r="W87">
-        <v>0.2181403350089031</v>
+        <v>0.2183456799506601</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3566312248292923</v>
+        <v>0.352484350121975</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2357295273225834</v>
+        <v>0.2376295273225834</v>
       </c>
       <c r="C88">
-        <v>-453.5333031438354</v>
+        <v>-462.681531779493</v>
       </c>
       <c r="D88">
-        <v>169.8426968561645</v>
+        <v>168.1604682205069</v>
       </c>
       <c r="E88">
-        <v>165.1759999999999</v>
+        <v>172.6419999999999</v>
       </c>
       <c r="F88">
-        <v>642.0759999999999</v>
+        <v>649.5419999999999</v>
       </c>
       <c r="G88">
         <v>18.7</v>
@@ -8491,37 +8491,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M88">
-        <v>151.4015208</v>
+        <v>153.1620036</v>
       </c>
       <c r="N88">
-        <v>-98.03485413333331</v>
+        <v>-99.79533693333332</v>
       </c>
       <c r="O88">
-        <v>-20.587319368</v>
+        <v>-20.957020756</v>
       </c>
       <c r="P88">
-        <v>-77.44753476533332</v>
+        <v>-78.83831617733333</v>
       </c>
       <c r="Q88">
-        <v>-44.14753476533332</v>
+        <v>-45.53831617733333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3425160183215412</v>
+        <v>0.3653403274231981</v>
       </c>
       <c r="T88">
-        <v>5.003058337544809</v>
+        <v>5.387908978894409</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07402171352561475</v>
+        <v>0.07317088923221687</v>
       </c>
       <c r="W88">
-        <v>0.2183456799506601</v>
+        <v>0.2185463043190433</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.352484350121975</v>
+        <v>0.3484328058676994</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2376295273225834</v>
+        <v>0.2395295273225834</v>
       </c>
       <c r="C89">
-        <v>-462.681531779493</v>
+        <v>-471.7967635410869</v>
       </c>
       <c r="D89">
-        <v>168.1604682205069</v>
+        <v>166.511236458913</v>
       </c>
       <c r="E89">
-        <v>172.6419999999999</v>
+        <v>180.1079999999999</v>
       </c>
       <c r="F89">
-        <v>649.5419999999999</v>
+        <v>657.0079999999999</v>
       </c>
       <c r="G89">
         <v>18.7</v>
@@ -8573,37 +8573,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M89">
-        <v>153.1620036</v>
+        <v>154.9224864</v>
       </c>
       <c r="N89">
-        <v>-99.79533693333332</v>
+        <v>-101.5558197333333</v>
       </c>
       <c r="O89">
-        <v>-20.957020756</v>
+        <v>-21.326722144</v>
       </c>
       <c r="P89">
-        <v>-78.83831617733333</v>
+        <v>-80.22909758933332</v>
       </c>
       <c r="Q89">
-        <v>-45.53831617733333</v>
+        <v>-46.92909758933332</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3653403274231981</v>
+        <v>0.3919686880417981</v>
       </c>
       <c r="T89">
-        <v>5.387908978894409</v>
+        <v>5.836901393802278</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07317088923221687</v>
+        <v>0.07233940185457804</v>
       </c>
       <c r="W89">
-        <v>0.2185463043190433</v>
+        <v>0.2187423690426905</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3484328058676994</v>
+        <v>0.3444733421646573</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2395295273225834</v>
+        <v>0.2414295273225834</v>
       </c>
       <c r="C90">
-        <v>-471.7967635410869</v>
+        <v>-480.8799598488317</v>
       </c>
       <c r="D90">
-        <v>166.511236458913</v>
+        <v>164.8940401511683</v>
       </c>
       <c r="E90">
-        <v>180.1079999999999</v>
+        <v>187.574</v>
       </c>
       <c r="F90">
-        <v>657.0079999999999</v>
+        <v>664.4739999999999</v>
       </c>
       <c r="G90">
         <v>18.7</v>
@@ -8655,37 +8655,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M90">
-        <v>154.9224864</v>
+        <v>156.6829692</v>
       </c>
       <c r="N90">
-        <v>-101.5558197333333</v>
+        <v>-103.3163025333333</v>
       </c>
       <c r="O90">
-        <v>-21.326722144</v>
+        <v>-21.696423532</v>
       </c>
       <c r="P90">
-        <v>-80.22909758933332</v>
+        <v>-81.61987900133333</v>
       </c>
       <c r="Q90">
-        <v>-46.92909758933332</v>
+        <v>-48.31987900133333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3919686880417981</v>
+        <v>0.4234385687728706</v>
       </c>
       <c r="T90">
-        <v>5.836901393802278</v>
+        <v>6.367528793238849</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07233940185457804</v>
+        <v>0.07152659958654907</v>
       </c>
       <c r="W90">
-        <v>0.2187423690426905</v>
+        <v>0.2189340278174917</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3444733421646573</v>
+        <v>0.3406028551740432</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2414295273225834</v>
+        <v>0.2433295273225834</v>
       </c>
       <c r="C91">
-        <v>-480.8799598488317</v>
+        <v>-489.932045132049</v>
       </c>
       <c r="D91">
-        <v>164.8940401511683</v>
+        <v>163.307954867951</v>
       </c>
       <c r="E91">
-        <v>187.574</v>
+        <v>195.04</v>
       </c>
       <c r="F91">
-        <v>664.4739999999999</v>
+        <v>671.9399999999999</v>
       </c>
       <c r="G91">
         <v>18.7</v>
@@ -8737,37 +8737,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M91">
-        <v>156.6829692</v>
+        <v>158.443452</v>
       </c>
       <c r="N91">
-        <v>-103.3163025333333</v>
+        <v>-105.0767853333333</v>
       </c>
       <c r="O91">
-        <v>-21.696423532</v>
+        <v>-22.06612491999999</v>
       </c>
       <c r="P91">
-        <v>-81.61987900133333</v>
+        <v>-83.01066041333331</v>
       </c>
       <c r="Q91">
-        <v>-48.31987900133333</v>
+        <v>-49.71066041333331</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4234385687728706</v>
+        <v>0.4612024256501577</v>
       </c>
       <c r="T91">
-        <v>6.367528793238849</v>
+        <v>7.004281672562733</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07152659958654907</v>
+        <v>0.07073185959114298</v>
       </c>
       <c r="W91">
-        <v>0.2189340278174917</v>
+        <v>0.2191214275084085</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3406028551740432</v>
+        <v>0.3368183790054428</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2433295273225834</v>
+        <v>0.2452295273225834</v>
       </c>
       <c r="C92">
-        <v>-489.932045132049</v>
+        <v>-498.9539085912609</v>
       </c>
       <c r="D92">
-        <v>163.307954867951</v>
+        <v>161.7520914087391</v>
       </c>
       <c r="E92">
-        <v>195.04</v>
+        <v>202.506</v>
       </c>
       <c r="F92">
-        <v>671.9399999999999</v>
+        <v>679.4059999999999</v>
       </c>
       <c r="G92">
         <v>18.7</v>
@@ -8819,37 +8819,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M92">
-        <v>158.443452</v>
+        <v>160.2039348</v>
       </c>
       <c r="N92">
-        <v>-105.0767853333333</v>
+        <v>-106.8372681333333</v>
       </c>
       <c r="O92">
-        <v>-22.06612491999999</v>
+        <v>-22.435826308</v>
       </c>
       <c r="P92">
-        <v>-83.01066041333331</v>
+        <v>-84.40144182533331</v>
       </c>
       <c r="Q92">
-        <v>-49.71066041333331</v>
+        <v>-51.10144182533331</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4612024256501577</v>
+        <v>0.5073582507223975</v>
       </c>
       <c r="T92">
-        <v>7.004281672562733</v>
+        <v>7.782535191736372</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07073185959114298</v>
+        <v>0.06995458640882272</v>
       </c>
       <c r="W92">
-        <v>0.2191214275084085</v>
+        <v>0.2193047085247996</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3368183790054428</v>
+        <v>0.3331170781372511</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2452295273225834</v>
+        <v>0.2471295273225834</v>
       </c>
       <c r="C93">
-        <v>-498.9539085912609</v>
+        <v>-507.9464058605074</v>
       </c>
       <c r="D93">
-        <v>161.7520914087391</v>
+        <v>160.2255941394926</v>
       </c>
       <c r="E93">
-        <v>202.506</v>
+        <v>209.972</v>
       </c>
       <c r="F93">
-        <v>679.4059999999999</v>
+        <v>686.872</v>
       </c>
       <c r="G93">
         <v>18.7</v>
@@ -8901,37 +8901,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M93">
-        <v>160.2039348</v>
+        <v>161.9644176</v>
       </c>
       <c r="N93">
-        <v>-106.8372681333333</v>
+        <v>-108.5977509333333</v>
       </c>
       <c r="O93">
-        <v>-22.435826308</v>
+        <v>-22.805527696</v>
       </c>
       <c r="P93">
-        <v>-84.40144182533331</v>
+        <v>-85.79222323733332</v>
       </c>
       <c r="Q93">
-        <v>-51.10144182533331</v>
+        <v>-52.49222323733332</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5073582507223975</v>
+        <v>0.5650530320626973</v>
       </c>
       <c r="T93">
-        <v>7.782535191736372</v>
+        <v>8.755352090703422</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06995458640882272</v>
+        <v>0.0691942104695964</v>
       </c>
       <c r="W93">
-        <v>0.2193047085247996</v>
+        <v>0.2194840051712692</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3331170781372511</v>
+        <v>0.3294962403314114</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2471295273225834</v>
+        <v>0.2490295273225834</v>
       </c>
       <c r="C94">
-        <v>-507.9464058605074</v>
+        <v>-516.9103605764174</v>
       </c>
       <c r="D94">
-        <v>160.2255941394926</v>
+        <v>158.7276394235826</v>
       </c>
       <c r="E94">
-        <v>209.972</v>
+        <v>217.438</v>
       </c>
       <c r="F94">
-        <v>686.872</v>
+        <v>694.338</v>
       </c>
       <c r="G94">
         <v>18.7</v>
@@ -8983,37 +8983,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M94">
-        <v>161.9644176</v>
+        <v>163.7249004</v>
       </c>
       <c r="N94">
-        <v>-108.5977509333333</v>
+        <v>-110.3582337333333</v>
       </c>
       <c r="O94">
-        <v>-22.805527696</v>
+        <v>-23.175229084</v>
       </c>
       <c r="P94">
-        <v>-85.79222323733332</v>
+        <v>-87.18300464933333</v>
       </c>
       <c r="Q94">
-        <v>-52.49222323733332</v>
+        <v>-53.88300464933333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5650530320626973</v>
+        <v>0.6392320366430826</v>
       </c>
       <c r="T94">
-        <v>8.755352090703422</v>
+        <v>10.00611667508962</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0691942104695964</v>
+        <v>0.06845018670110611</v>
       </c>
       <c r="W94">
-        <v>0.2194840051712692</v>
+        <v>0.2196594459758792</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3294962403314114</v>
+        <v>0.3259532700052672</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2490295273225834</v>
+        <v>0.2509295273225834</v>
       </c>
       <c r="C95">
-        <v>-516.9103605764174</v>
+        <v>-525.8465658600796</v>
       </c>
       <c r="D95">
-        <v>158.7276394235826</v>
+        <v>157.2574341399203</v>
       </c>
       <c r="E95">
-        <v>217.438</v>
+        <v>224.904</v>
       </c>
       <c r="F95">
-        <v>694.338</v>
+        <v>701.804</v>
       </c>
       <c r="G95">
         <v>18.7</v>
@@ -9065,37 +9065,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M95">
-        <v>163.7249004</v>
+        <v>165.4853832</v>
       </c>
       <c r="N95">
-        <v>-110.3582337333333</v>
+        <v>-112.1187165333333</v>
       </c>
       <c r="O95">
-        <v>-23.175229084</v>
+        <v>-23.544930472</v>
       </c>
       <c r="P95">
-        <v>-87.18300464933333</v>
+        <v>-88.57378606133332</v>
       </c>
       <c r="Q95">
-        <v>-53.88300464933333</v>
+        <v>-55.27378606133333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6392320366430826</v>
+        <v>0.7381373760835966</v>
       </c>
       <c r="T95">
-        <v>10.00611667508962</v>
+        <v>11.67380278760456</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06845018670110611</v>
+        <v>0.06772199322556242</v>
       </c>
       <c r="W95">
-        <v>0.2196594459758792</v>
+        <v>0.2198311539974124</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3259532700052672</v>
+        <v>0.3224856820264878</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2509295273225834</v>
+        <v>0.2528295273225834</v>
       </c>
       <c r="C96">
-        <v>-525.8465658600796</v>
+        <v>-534.7557857173143</v>
       </c>
       <c r="D96">
-        <v>157.2574341399203</v>
+        <v>155.8142142826856</v>
       </c>
       <c r="E96">
-        <v>224.904</v>
+        <v>232.37</v>
       </c>
       <c r="F96">
-        <v>701.804</v>
+        <v>709.27</v>
       </c>
       <c r="G96">
         <v>18.7</v>
@@ -9147,37 +9147,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M96">
-        <v>165.4853832</v>
+        <v>167.245866</v>
       </c>
       <c r="N96">
-        <v>-112.1187165333333</v>
+        <v>-113.8791993333333</v>
       </c>
       <c r="O96">
-        <v>-23.544930472</v>
+        <v>-23.91463186</v>
       </c>
       <c r="P96">
-        <v>-88.57378606133332</v>
+        <v>-89.96456747333333</v>
       </c>
       <c r="Q96">
-        <v>-55.27378606133333</v>
+        <v>-56.66456747333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7381373760835966</v>
+        <v>0.8766048513003163</v>
       </c>
       <c r="T96">
-        <v>11.67380278760456</v>
+        <v>14.00856334512548</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06772199322556242</v>
+        <v>0.06700913013897755</v>
       </c>
       <c r="W96">
-        <v>0.2198311539974124</v>
+        <v>0.2199992471132291</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3224856820264878</v>
+        <v>0.3190910958998932</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2528295273225834</v>
+        <v>0.2547295273225834</v>
       </c>
       <c r="C97">
-        <v>-534.7557857173143</v>
+        <v>-543.6387563625406</v>
       </c>
       <c r="D97">
-        <v>155.8142142826856</v>
+        <v>154.3972436374594</v>
       </c>
       <c r="E97">
-        <v>232.37</v>
+        <v>239.836</v>
       </c>
       <c r="F97">
-        <v>709.27</v>
+        <v>716.736</v>
       </c>
       <c r="G97">
         <v>18.7</v>
@@ -9229,37 +9229,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M97">
-        <v>167.245866</v>
+        <v>169.0063488</v>
       </c>
       <c r="N97">
-        <v>-113.8791993333333</v>
+        <v>-115.6396821333333</v>
       </c>
       <c r="O97">
-        <v>-23.91463186</v>
+        <v>-24.284333248</v>
       </c>
       <c r="P97">
-        <v>-89.96456747333333</v>
+        <v>-91.35534888533334</v>
       </c>
       <c r="Q97">
-        <v>-56.66456747333334</v>
+        <v>-58.05534888533334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8766048513003163</v>
+        <v>1.084306064125396</v>
       </c>
       <c r="T97">
-        <v>14.00856334512548</v>
+        <v>17.51070418140687</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06700913013897755</v>
+        <v>0.06631111836669654</v>
       </c>
       <c r="W97">
-        <v>0.2199992471132291</v>
+        <v>0.220163838289133</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3190910958998932</v>
+        <v>0.3157672303176026</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2547295273225834</v>
+        <v>0.2566295273225834</v>
       </c>
       <c r="C98">
-        <v>-543.6387563625406</v>
+        <v>-552.4961874710604</v>
       </c>
       <c r="D98">
-        <v>154.3972436374594</v>
+        <v>153.0058125289395</v>
       </c>
       <c r="E98">
-        <v>239.8359999999999</v>
+        <v>247.3019999999999</v>
       </c>
       <c r="F98">
-        <v>716.7359999999999</v>
+        <v>724.2019999999999</v>
       </c>
       <c r="G98">
         <v>18.7</v>
@@ -9311,37 +9311,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M98">
-        <v>169.0063488</v>
+        <v>170.7668316</v>
       </c>
       <c r="N98">
-        <v>-115.6396821333333</v>
+        <v>-117.4001649333333</v>
       </c>
       <c r="O98">
-        <v>-24.284333248</v>
+        <v>-24.654034636</v>
       </c>
       <c r="P98">
-        <v>-91.35534888533331</v>
+        <v>-92.74613029733332</v>
       </c>
       <c r="Q98">
-        <v>-58.05534888533332</v>
+        <v>-59.44613029733333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.084306064125393</v>
+        <v>1.430474752167191</v>
       </c>
       <c r="T98">
-        <v>17.51070418140682</v>
+        <v>23.34760557520909</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06631111836669655</v>
+        <v>0.06562749858972029</v>
       </c>
       <c r="W98">
-        <v>0.220163838289133</v>
+        <v>0.220325035832544</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3157672303176026</v>
+        <v>0.3125118980462871</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2566295273225834</v>
+        <v>0.2585295273225834</v>
       </c>
       <c r="C99">
-        <v>-552.4961874710604</v>
+        <v>-561.3287633642327</v>
       </c>
       <c r="D99">
-        <v>153.0058125289395</v>
+        <v>151.6392366357672</v>
       </c>
       <c r="E99">
-        <v>247.3019999999999</v>
+        <v>254.7679999999999</v>
       </c>
       <c r="F99">
-        <v>724.2019999999999</v>
+        <v>731.6679999999999</v>
       </c>
       <c r="G99">
         <v>18.7</v>
@@ -9393,37 +9393,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M99">
-        <v>170.7668316</v>
+        <v>172.5273144</v>
       </c>
       <c r="N99">
-        <v>-117.4001649333333</v>
+        <v>-119.1606477333333</v>
       </c>
       <c r="O99">
-        <v>-24.654034636</v>
+        <v>-25.023736024</v>
       </c>
       <c r="P99">
-        <v>-92.74613029733332</v>
+        <v>-94.13691170933332</v>
       </c>
       <c r="Q99">
-        <v>-59.44613029733333</v>
+        <v>-60.83691170933332</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.430474752167191</v>
+        <v>2.122812128250786</v>
       </c>
       <c r="T99">
-        <v>23.34760557520909</v>
+        <v>35.02140836281363</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06562749858972029</v>
+        <v>0.06495783023676396</v>
       </c>
       <c r="W99">
-        <v>0.220325035832544</v>
+        <v>0.2204829436301711</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3125118980462871</v>
+        <v>0.3093230011274474</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2585295273225834</v>
+        <v>0.2604295273225834</v>
       </c>
       <c r="C100">
-        <v>-561.3287633642327</v>
+        <v>-570.1371441316977</v>
       </c>
       <c r="D100">
-        <v>151.6392366357672</v>
+        <v>150.2968558683022</v>
       </c>
       <c r="E100">
-        <v>254.7679999999999</v>
+        <v>262.2339999999999</v>
       </c>
       <c r="F100">
-        <v>731.6679999999999</v>
+        <v>739.1339999999999</v>
       </c>
       <c r="G100">
         <v>18.7</v>
@@ -9475,37 +9475,37 @@
         <v>53.36666666666667</v>
       </c>
       <c r="M100">
-        <v>172.5273144</v>
+        <v>174.2877972</v>
       </c>
       <c r="N100">
-        <v>-119.1606477333333</v>
+        <v>-120.9211305333333</v>
       </c>
       <c r="O100">
-        <v>-25.023736024</v>
+        <v>-25.39343741199999</v>
       </c>
       <c r="P100">
-        <v>-94.13691170933332</v>
+        <v>-95.5276931213333</v>
       </c>
       <c r="Q100">
-        <v>-60.83691170933332</v>
+        <v>-62.2276931213333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.122812128250786</v>
+        <v>4.199824256501572</v>
       </c>
       <c r="T100">
-        <v>35.02140836281363</v>
+        <v>70.04281672562726</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06495783023676396</v>
+        <v>0.06430169053740271</v>
       </c>
       <c r="W100">
-        <v>0.2204829436301711</v>
+        <v>0.2206376613712804</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3093230011274474</v>
+        <v>0.3061985263685844</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2604295273225834</v>
-      </c>
-      <c r="C101">
-        <v>-570.1371441316977</v>
-      </c>
-      <c r="D101">
-        <v>150.2968558683022</v>
-      </c>
-      <c r="E101">
-        <v>262.2339999999999</v>
-      </c>
-      <c r="F101">
-        <v>739.1339999999999</v>
-      </c>
-      <c r="G101">
-        <v>18.7</v>
-      </c>
-      <c r="H101">
-        <v>269.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>86.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>33.3</v>
-      </c>
-      <c r="L101">
-        <v>53.36666666666667</v>
-      </c>
-      <c r="M101">
-        <v>174.2877972</v>
-      </c>
-      <c r="N101">
-        <v>-120.9211305333333</v>
-      </c>
-      <c r="O101">
-        <v>-25.39343741199999</v>
-      </c>
-      <c r="P101">
-        <v>-95.5276931213333</v>
-      </c>
-      <c r="Q101">
-        <v>-62.2276931213333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.199824256501572</v>
-      </c>
-      <c r="T101">
-        <v>70.04281672562726</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06430169053740271</v>
-      </c>
-      <c r="W101">
-        <v>0.2206376613712804</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3061985263685844</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
